--- a/各種資料/contact 7().xlsx
+++ b/各種資料/contact 7().xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guest04\Desktop\高橋研三\03_knowledge\各種資料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\50_knowledge\各種資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{67C4AA8E-AE59-46E2-9308-788B72A38BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEEC766-9ED0-4962-8039-E9332F061FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3140" yWindow="0" windowWidth="21870" windowHeight="16010" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17325" yWindow="840" windowWidth="20490" windowHeight="14505" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="① インストール" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,15 @@
     <sheet name="④ フォームテンプレートの書き方" sheetId="4" r:id="rId4"/>
     <sheet name="（メニューの設定）メニューのどこに表示されるかの確認" sheetId="5" r:id="rId5"/>
     <sheet name="メニューをクリックした時のリンク先（メニューの増やし方）" sheetId="6" r:id="rId6"/>
+    <sheet name="自分が作成したファイルをメニューに表示したい時" sheetId="7" r:id="rId7"/>
+    <sheet name="Custom Post Type UI（不明な場所だけ抜粋" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="96">
   <si>
     <t>① インストール</t>
   </si>
@@ -246,16 +247,6 @@
     </rPh>
     <rPh sb="8" eb="10">
       <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>どこの画面の紐づいているのか？</t>
-    <rPh sb="3" eb="5">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ヒモ</t>
     </rPh>
     <phoneticPr fontId="9"/>
   </si>
@@ -431,12 +422,177 @@
     </rPh>
     <phoneticPr fontId="9"/>
   </si>
+  <si>
+    <t>このエラーは、IDがまちがっているだけ。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>設定➡表示設定</t>
+    <rPh sb="0" eb="2">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>ということは /（トップページ）にアクセスすると投稿一覧が表示される設定です。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>ただ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>今のテーマは front-page.php があるので、/ にアクセスすると front-page.php が優先されてしまいます。</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>対処法</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>カスタムリンクのURLを /category/[カテゴリースラッグ]/ に変更してください</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>。例：カテゴリースラッグが news ならhttp://newtesthome.local/category/news</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>カテゴリーのスラッグの見方</t>
+    <rPh sb="11" eb="13">
+      <t>ミカタ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>お知らせ➡カテゴリ</t>
+    <rPh sb="1" eb="2">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>このスラッグで表示すれば、すべての投稿一覧　archive.phpが表示される</t>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>ことがわかる</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>http://newtesthome.local/category/uncategorized/</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>カスタムリンクの設定</t>
+    <rPh sb="8" eb="10">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>外観➡メニュー</t>
+    <rPh sb="0" eb="2">
+      <t>ガイカン</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>ここに、http://newtesthome.local/category/uncategorized/を入力</t>
+    <rPh sb="53" eb="55">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>英語と複数形、単数形のラベルは、管理画面で表示名を入力します？</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>要するに、スラッグと、あとは</t>
+    <rPh sb="0" eb="1">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>複数形のラベル	　　　管理画面メニュー</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>単数形のラベル	　　「新規追加」ボタンなど</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>スラッグだけ慎重に決めれば、ラベルは後から変更しても問題ないです。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>このファイルに該当するPHPファイルは？</t>
+    <rPh sb="7" eb="9">
+      <t>ガイトウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>ページの種類</t>
+  </si>
+  <si>
+    <t>ファイル名</t>
+  </si>
+  <si>
+    <t>一覧ページ</t>
+  </si>
+  <si>
+    <t>archive-works.php</t>
+  </si>
+  <si>
+    <t>詳細ページ</t>
+  </si>
+  <si>
+    <t>single-works.php</t>
+  </si>
+  <si>
+    <t>スラッグが works の場合：</t>
+  </si>
+  <si>
+    <t>カスタムタクソノミいいー</t>
+    <phoneticPr fontId="9"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -568,8 +724,25 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,8 +780,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -636,11 +815,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -689,11 +884,17 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1220,7 +1421,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>73773</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>69851</xdr:rowOff>
+      <xdr:rowOff>60326</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1720,6 +1921,358 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78FF58EB-0783-68F7-CED2-1939F43BE092}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="514350"/>
+          <a:ext cx="5381625" cy="3552825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>51276</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAAE3C1F-B8CE-F010-94C8-E09E281A6511}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="6410325"/>
+          <a:ext cx="6115050" cy="5709126"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B10B49E3-839E-4668-BE32-93F081C4AD6E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5324475" y="7486650"/>
+          <a:ext cx="1343025" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>608838</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>18790</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA3E7650-44BB-683B-3A02-8DDC266C01FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="13096875"/>
+          <a:ext cx="6095238" cy="2076190"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3F92EDE-8722-4A6A-81B0-ADFC07E3E479}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="781050" y="13077825"/>
+          <a:ext cx="1619250" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6734C6FE-4032-1CD0-6318-BC31E8B39AC5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="171450"/>
+          <a:ext cx="6477000" cy="4152900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>485449</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>114136</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C747511-B24D-B710-4C37-CA5C7C498D0F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="8505825"/>
+          <a:ext cx="2609524" cy="1314286"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2009,14 +2562,14 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K6"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2030,8 +2583,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
@@ -2045,7 +2598,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2059,7 +2612,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2072,7 +2625,7 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:P61"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
@@ -2080,8 +2633,8 @@
     <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2095,8 +2648,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
@@ -2110,7 +2663,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
@@ -2124,19 +2677,19 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="7" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="8" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="10" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="24"/>
     </row>
-    <row r="12" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
@@ -2150,8 +2703,8 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B14" s="5" t="s">
         <v>7</v>
       </c>
@@ -2165,7 +2718,7 @@
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
@@ -2179,8 +2732,8 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="17" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
@@ -2194,8 +2747,8 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="2:11" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -2209,7 +2762,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
@@ -2223,7 +2776,7 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
         <v>12</v>
       </c>
@@ -2237,7 +2790,7 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B22" s="3" t="s">
         <v>13</v>
       </c>
@@ -2251,7 +2804,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -2263,7 +2816,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
         <v>14</v>
       </c>
@@ -2277,16 +2830,16 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>15</v>
       </c>
@@ -2300,8 +2853,8 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="7" t="s">
         <v>16</v>
       </c>
@@ -2315,8 +2868,8 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B34" s="3" t="s">
         <v>17</v>
       </c>
@@ -2330,7 +2883,7 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B35" s="3" t="s">
         <v>18</v>
       </c>
@@ -2344,7 +2897,7 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B36" s="3" t="s">
         <v>19</v>
       </c>
@@ -2358,22 +2911,22 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="38" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="2:16" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="9" t="s">
         <v>26</v>
       </c>
@@ -2392,7 +2945,7 @@
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
     </row>
-    <row r="61" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2406,15 +2959,15 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K83"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
     <col min="3" max="15" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>27</v>
       </c>
@@ -2428,8 +2981,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:11" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="2:11" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="10" t="s">
         <v>28</v>
       </c>
@@ -2443,7 +2996,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" s="5" t="s">
         <v>29</v>
       </c>
@@ -2457,7 +3010,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
@@ -2471,7 +3024,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
@@ -2485,7 +3038,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B8" s="11" t="s">
         <v>32</v>
       </c>
@@ -2499,7 +3052,7 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B9" s="11" t="s">
         <v>33</v>
       </c>
@@ -2513,7 +3066,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
@@ -2527,8 +3080,8 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="12" spans="2:11" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="13" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="7" t="s">
         <v>35</v>
       </c>
@@ -2542,17 +3095,17 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="19" spans="2:11" ht="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" ht="18.75" x14ac:dyDescent="0.2">
       <c r="B19" s="20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" ht="16.5" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B21" s="18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" ht="20" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="19.5" x14ac:dyDescent="0.15">
       <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
@@ -2566,7 +3119,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B24" s="5" t="s">
         <v>21</v>
       </c>
@@ -2580,7 +3133,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B25" s="3" t="s">
         <v>22</v>
       </c>
@@ -2594,9 +3147,9 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B26" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -2608,7 +3161,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B27" s="3" t="s">
         <v>23</v>
       </c>
@@ -2622,7 +3175,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B28" s="3" t="s">
         <v>19</v>
       </c>
@@ -2636,7 +3189,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
@@ -2650,7 +3203,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="32" spans="2:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" ht="16.5" x14ac:dyDescent="0.15">
       <c r="B32" s="7" t="s">
         <v>25</v>
       </c>
@@ -2664,44 +3217,44 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="36" spans="2:2" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B36" s="21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B38" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B39" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B40" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B41" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B42" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" ht="23.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="22" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B38" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B39" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B40" s="17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B41" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B42" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" ht="23.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="22" t="s">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B83" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B83" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2717,15 +3270,15 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K16"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="13" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>36</v>
       </c>
@@ -2739,8 +3292,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="12" t="s">
         <v>37</v>
       </c>
@@ -2752,7 +3305,7 @@
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
@@ -2766,7 +3319,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
         <v>39</v>
       </c>
@@ -2780,7 +3333,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -2792,7 +3345,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
@@ -2806,7 +3359,7 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B9" s="3" t="s">
         <v>41</v>
       </c>
@@ -2820,7 +3373,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -2832,7 +3385,7 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B11" s="3" t="s">
         <v>42</v>
       </c>
@@ -2846,8 +3399,8 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="13" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="14" t="s">
         <v>43</v>
       </c>
@@ -2859,7 +3412,7 @@
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B15" s="16" t="s">
         <v>44</v>
       </c>
@@ -2873,7 +3426,7 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2887,9 +3440,9 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B3:E38"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B3" s="17" t="s">
         <v>45</v>
       </c>
@@ -2897,17 +3450,17 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B38" t="s">
         <v>48</v>
       </c>
@@ -2922,46 +3475,211 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E4DE1B-CEE6-4D06-B682-4A9E3F05719A}">
   <dimension ref="B2:P147"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="16:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" spans="16:16" x14ac:dyDescent="0.15">
+      <c r="P38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="16:16" x14ac:dyDescent="0.15">
+      <c r="P39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B74" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B75" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B111" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="147" spans="16:16" x14ac:dyDescent="0.15">
+      <c r="P147" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A893AC6-FB79-450E-8D17-FE484C32412D}">
+  <dimension ref="B2:L75"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B27" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="16:16" x14ac:dyDescent="0.2">
-      <c r="P38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="16:16" x14ac:dyDescent="0.2">
-      <c r="P39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="B31" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="27"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B37" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="L44" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="L45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="L47" s="25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B74" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B75" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B111" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="147" spans="16:16" x14ac:dyDescent="0.2">
-      <c r="P147" t="s">
-        <v>55</v>
+        <v>79</v>
+      </c>
+      <c r="E74" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B75" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9"/>
+  <hyperlinks>
+    <hyperlink ref="L47" r:id="rId1" xr:uid="{4E01138E-D93F-4549-9360-3FE7DF17DB82}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F487261-4C57-4DE5-9D5F-EC7B6550A8CC}">
+  <dimension ref="B28:C47"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="12.375" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B29" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B30" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B32" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B37" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B40" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B42" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B44" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B47" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/各種資料/contact 7().xlsx
+++ b/各種資料/contact 7().xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\50_knowledge\各種資料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guest04\Desktop\高橋研三\03_knowledge\各種資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEEC766-9ED0-4962-8039-E9332F061FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBDD35B7-1DAF-409F-ACE9-F1BD8CED9396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17325" yWindow="840" windowWidth="20490" windowHeight="14505" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51735" yWindow="0" windowWidth="14610" windowHeight="16305" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="① インストール" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="135">
   <si>
     <t>① インストール</t>
   </si>
@@ -584,7 +584,377 @@
     <t>スラッグが works の場合：</t>
   </si>
   <si>
-    <t>カスタムタクソノミいいー</t>
+    <t>インストール</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>↓</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>CPTUIの、投稿タイプの追加</t>
+    <rPh sb="7" eb="9">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>（その際、アーカイブありに「true」を設定する）</t>
+    <rPh sb="3" eb="4">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>追加</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>サイドメニューに制作実績が追加される「これは、自分で設定したもの」</t>
+    <rPh sb="8" eb="10">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>制作実績を追加</t>
+    <rPh sb="0" eb="2">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>投稿タイプの追加時の「/works」→スラッグ、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>が新しく作成した投稿タイプの一覧ページのURLになります。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>「タクソノミー」とは分類のこと。</t>
+    <rPh sb="10" eb="12">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>カスタムタクソノミー</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>通常の投稿に最初からついている</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>「カテゴリー（category）」や「タグ（tag）」</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>もタクソノミーの一種です。</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>このようにメニューに追加される</t>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>※投稿タイプとおなじ。</t>
+    <rPh sb="1" eb="3">
+      <t>トウコウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>（だが、制作実績は全体メニュー）</t>
+    <rPh sb="4" eb="6">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゼンタイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>つまり制作実績は、は「CPTUIの、投稿タイプの追加」から追加する</t>
+    <rPh sb="3" eb="5">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>そのメインメニューが追加される。</t>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>タクソノミーの追加をすると</t>
+    <rPh sb="7" eb="9">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>メインメニューの下に項目が追加される</t>
+    <rPh sb="8" eb="9">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>（いくらでも追加できる）</t>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>★かならず、この設定をすること。</t>
+    <rPh sb="8" eb="10">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>さらにその「カテゴリ」メニューに対して、子要素にカテゴリに追加する</t>
+    <rPh sb="16" eb="17">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>コヨウソ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>そうするとカテゴリの中に「カテゴリ」が表示される</t>
+    <rPh sb="10" eb="11">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>↓（多分新規政策実績を追加）</t>
+    <rPh sb="2" eb="4">
+      <t>タブン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>投稿タイプの追加</t>
+    <rPh sb="0" eb="2">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>他の「問い合わせ contact form 7」等と、同様にメニューに追加する</t>
+    <rPh sb="0" eb="1">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ナド</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>★ようするに制作実績を不随するもののイメージ。</t>
+    <rPh sb="6" eb="10">
+      <t>セイサクジッセキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>フズイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>　　　　頻繁に投稿タイプで追加するもの</t>
+    <rPh sb="4" eb="6">
+      <t>ヒンパン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>ようするに</t>
+  </si>
+  <si>
+    <t>　↓</t>
+  </si>
+  <si>
+    <t>なければ   → archive.php を使う</t>
+  </si>
+  <si>
+    <t>今の状態</t>
+  </si>
+  <si>
+    <t>やること</t>
+  </si>
+  <si>
+    <t>WordPressは「どのPHPファイルを使うか」をファイル名で自動で決める。</t>
+  </si>
+  <si>
+    <t>archive-works.php がまだ存在しない。</t>
+  </si>
+  <si>
+    <t>だから /works を開いても archive.php（お知らせ用）が使われてしまう。</t>
+  </si>
+  <si>
+    <t>archive.php をコピーして</t>
+  </si>
+  <si>
+    <t>名前を archive-works.php に変えるだけ！</t>
+  </si>
+  <si>
+    <t>archive-works.php があれば → それを使う</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>/works を開く</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>現在の状態。今は、archive-works.phpがないので、archive.phpが使われる</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ツカ</t>
+    </rPh>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -592,7 +962,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -741,8 +1111,54 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -783,6 +1199,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -835,7 +1257,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -892,6 +1314,12 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -2186,57 +2614,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>120</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6734C6FE-4032-1CD0-6318-BC31E8B39AC5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="171450"/>
-          <a:ext cx="6477000" cy="4152900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>485449</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>114136</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2253,6 +2637,50 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="19973925"/>
+          <a:ext cx="3314700" cy="1247611"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>25401</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>161926</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A746C6B1-45FF-C063-6EE5-C07FFE731428}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
@@ -2260,8 +2688,420 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="8505825"/>
-          <a:ext cx="2609524" cy="1314286"/>
+          <a:off x="635001" y="9220200"/>
+          <a:ext cx="5127625" cy="4067175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>153019</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90E1460C-2ED5-FA27-8316-2191A1B97F9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="16897350"/>
+          <a:ext cx="3952875" cy="3877294"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF">
+            <a:shade val="85000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="88900" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="55000" dist="18000" dir="5400000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="40000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="twoPt" dir="t">
+            <a:rot lat="0" lon="0" rev="7200000"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT w="25400" h="19050"/>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>158</xdr:row>
+      <xdr:rowOff>86941</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>55909</xdr:colOff>
+      <xdr:row>187</xdr:row>
+      <xdr:rowOff>106638</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFE61026-934C-EBC3-5318-C47E0D4A2332}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="581025" y="26214016"/>
+          <a:ext cx="4465984" cy="4715522"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>374451</xdr:colOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>95076</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9568BE3-6F43-62A8-BF6C-D856EAC765E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5600700" y="21431250"/>
+          <a:ext cx="1590476" cy="1390476"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>45036</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>570449</xdr:colOff>
+      <xdr:row>217</xdr:row>
+      <xdr:rowOff>49769</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F21ED9B-899B-4B6F-6EAC-DF4F0FB731FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="654636" y="26650950"/>
+          <a:ext cx="4297313" cy="4218544"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>236</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>255</xdr:row>
+      <xdr:rowOff>20216</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0663876-B3A0-4E38-7AF3-C7D5D8F96F14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609601" y="33899475"/>
+          <a:ext cx="3962400" cy="3096791"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>22018</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>269479</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>79138</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC764CB3-61C1-2DE0-DFBC-F7B85686336B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7178675" y="345868"/>
+          <a:ext cx="1739504" cy="1028670"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>88899</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>105055</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>477199</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>2093</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7311FFDC-98B4-7B1F-4FD0-2ED91D3BB951}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="698499" y="4800880"/>
+          <a:ext cx="6598600" cy="2973613"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF">
+            <a:shade val="85000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="88900" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="55000" dist="18000" dir="5400000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="40000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="twoPt" dir="t">
+            <a:rot lat="0" lon="0" rev="7200000"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT w="25400" h="19050"/>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>428624</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{520656EB-EF15-4A1B-8A49-769F8DC36ACA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="571499" y="1158875"/>
+          <a:ext cx="6677025" cy="3413125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2562,14 +3402,14 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K6"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2583,8 +3423,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
@@ -2598,7 +3438,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2612,7 +3452,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="6" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2625,7 +3465,7 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:P61"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
@@ -2633,8 +3473,8 @@
     <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2648,8 +3488,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
@@ -2663,7 +3503,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
@@ -2677,19 +3517,19 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="8" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="24"/>
     </row>
-    <row r="12" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
@@ -2703,8 +3543,8 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>7</v>
       </c>
@@ -2718,7 +3558,7 @@
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
@@ -2732,8 +3572,8 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="17" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
@@ -2747,8 +3587,8 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="2:11" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:11" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -2762,7 +3602,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
@@ -2776,7 +3616,7 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>12</v>
       </c>
@@ -2790,7 +3630,7 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
         <v>13</v>
       </c>
@@ -2804,7 +3644,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -2816,7 +3656,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
         <v>14</v>
       </c>
@@ -2830,16 +3670,16 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="26" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="28" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>15</v>
       </c>
@@ -2853,8 +3693,8 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
         <v>16</v>
       </c>
@@ -2868,8 +3708,8 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B34" s="3" t="s">
         <v>17</v>
       </c>
@@ -2883,7 +3723,7 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B35" s="3" t="s">
         <v>18</v>
       </c>
@@ -2897,7 +3737,7 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B36" s="3" t="s">
         <v>19</v>
       </c>
@@ -2911,22 +3751,22 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="38" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="2:16" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="9" t="s">
         <v>26</v>
       </c>
@@ -2945,7 +3785,7 @@
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
     </row>
-    <row r="61" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2959,15 +3799,15 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K83"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
     <col min="3" max="15" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>27</v>
       </c>
@@ -2981,8 +3821,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="4" spans="2:11" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="2:11" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="10" t="s">
         <v>28</v>
       </c>
@@ -2996,7 +3836,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
         <v>29</v>
       </c>
@@ -3010,7 +3850,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
@@ -3024,7 +3864,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
@@ -3038,7 +3878,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="11" t="s">
         <v>32</v>
       </c>
@@ -3052,7 +3892,7 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="11" t="s">
         <v>33</v>
       </c>
@@ -3066,7 +3906,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
@@ -3080,8 +3920,8 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="12" spans="2:11" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="13" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:11" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="7" t="s">
         <v>35</v>
       </c>
@@ -3095,17 +3935,17 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="19" spans="2:11" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" ht="19" x14ac:dyDescent="0.3">
       <c r="B19" s="20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="19.5" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:11" ht="20" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
@@ -3119,7 +3959,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B24" s="5" t="s">
         <v>21</v>
       </c>
@@ -3133,7 +3973,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
         <v>22</v>
       </c>
@@ -3147,7 +3987,7 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B26" s="19" t="s">
         <v>58</v>
       </c>
@@ -3161,7 +4001,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B27" s="3" t="s">
         <v>23</v>
       </c>
@@ -3175,7 +4015,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B28" s="3" t="s">
         <v>19</v>
       </c>
@@ -3189,7 +4029,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
@@ -3203,7 +4043,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="32" spans="2:11" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
         <v>25</v>
       </c>
@@ -3217,42 +4057,42 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="36" spans="2:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" ht="25.5" x14ac:dyDescent="0.35">
       <c r="B36" s="21" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B38" s="17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B39" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B40" s="17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B41" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B42" s="17" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="2:2" ht="23.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:2" ht="23.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="22" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B83" t="s">
         <v>66</v>
       </c>
@@ -3270,15 +4110,15 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K16"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="13" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>36</v>
       </c>
@@ -3292,8 +4132,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="12" t="s">
         <v>37</v>
       </c>
@@ -3305,7 +4145,7 @@
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
@@ -3319,7 +4159,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>39</v>
       </c>
@@ -3333,7 +4173,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -3345,7 +4185,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
@@ -3359,7 +4199,7 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
         <v>41</v>
       </c>
@@ -3373,7 +4213,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -3385,7 +4225,7 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
         <v>42</v>
       </c>
@@ -3399,8 +4239,8 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="13" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="14" t="s">
         <v>43</v>
       </c>
@@ -3412,7 +4252,7 @@
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="16" t="s">
         <v>44</v>
       </c>
@@ -3426,7 +4266,7 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="16" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3440,9 +4280,9 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B3:E38"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B3" s="17" t="s">
         <v>45</v>
       </c>
@@ -3450,17 +4290,17 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>48</v>
       </c>
@@ -3475,45 +4315,45 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E4DE1B-CEE6-4D06-B682-4A9E3F05719A}">
   <dimension ref="B2:P147"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="16:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" spans="16:16" x14ac:dyDescent="0.15">
+    <row r="35" spans="16:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="16:16" x14ac:dyDescent="0.2">
       <c r="P38" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="16:16" x14ac:dyDescent="0.15">
+    <row r="39" spans="16:16" x14ac:dyDescent="0.2">
       <c r="P39" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="147" spans="16:16" x14ac:dyDescent="0.15">
+    <row r="147" spans="16:16" x14ac:dyDescent="0.2">
       <c r="P147" t="s">
         <v>54</v>
       </c>
@@ -3528,65 +4368,65 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A893AC6-FB79-450E-8D17-FE484C32412D}">
   <dimension ref="B2:L75"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:3" ht="19" x14ac:dyDescent="0.3">
       <c r="B31" s="26" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="27"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L44" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L45" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L47" s="25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
         <v>79</v>
       </c>
@@ -3594,7 +4434,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B75" s="17" t="s">
         <v>80</v>
       </c>
@@ -3611,75 +4451,355 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F487261-4C57-4DE5-9D5F-EC7B6550A8CC}">
-  <dimension ref="B28:C47"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="B1:L283"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.375" customWidth="1"/>
-    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B28" t="s">
+    <row r="1" spans="2:11" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="B1" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="K1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B4" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B50" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52" s="30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B89" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B29" s="17" t="s">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B90" s="17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B30" s="17" t="s">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B91" s="17" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B31" t="s">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B92" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B32" s="17" t="s">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B93" s="17" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="B37" s="18" t="s">
+    <row r="98" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B98" s="18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B40" s="17" t="s">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B101" s="17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="29" t="s">
+    <row r="103" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B103" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C103" s="29" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="28" t="s">
+    <row r="104" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B104" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="28" t="s">
+      <c r="C104" s="28" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B44" s="28" t="s">
+    <row r="105" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="C105" s="28" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B47" t="s">
-        <v>95</v>
+    <row r="114" spans="2:4" ht="19" x14ac:dyDescent="0.3">
+      <c r="B114" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C114" s="27"/>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B115" t="s">
+        <v>103</v>
+      </c>
+      <c r="D115" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B118" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B131" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="154" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="J154" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="155" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="J155" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="158" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I158" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="173" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I173" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="175" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I175" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="176" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I176" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="178" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I178" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="179" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I179" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="181" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I181" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="183" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I183" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="184" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I184" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="191" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B191" s="31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B221" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B223" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B224" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B226" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B227" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B229" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B231" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B232" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B233" s="31" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B234" s="32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B235" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B236" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="262" spans="2:12" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B262" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="C262" s="35"/>
+      <c r="D262" s="35"/>
+      <c r="E262" s="35"/>
+      <c r="F262" s="35"/>
+      <c r="G262" s="35"/>
+      <c r="H262" s="35"/>
+      <c r="I262" s="35"/>
+      <c r="J262" s="35"/>
+      <c r="K262" s="35"/>
+      <c r="L262" s="35"/>
+    </row>
+    <row r="264" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B264" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="265" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B265" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="268" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B268" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="269" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B269" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="270" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B270" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="271" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B271" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B275" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B276" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="278" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B278" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="280" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B280" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B281" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="283" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B283" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/各種資料/contact 7().xlsx
+++ b/各種資料/contact 7().xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guest04\Desktop\高橋研三\03_knowledge\各種資料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\50_knowledge\各種資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBDD35B7-1DAF-409F-ACE9-F1BD8CED9396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D287BA-513D-43CC-9C95-29493686ACAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51735" yWindow="0" windowWidth="14610" windowHeight="16305" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4785" yWindow="540" windowWidth="20490" windowHeight="14505" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="① インストール" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,12 @@
     <sheet name="自分が作成したファイルをメニューに表示したい時" sheetId="7" r:id="rId7"/>
     <sheet name="Custom Post Type UI（不明な場所だけ抜粋" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="169">
   <si>
     <t>① インストール</t>
   </si>
@@ -957,12 +957,339 @@
     </rPh>
     <phoneticPr fontId="9"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※「カテゴリー」は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>分類の仕組み（入れ物）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>、ターム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>その中に入る具体的な名前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>つまり第三階層になっている。</t>
+    <rPh sb="3" eb="5">
+      <t>ダイサン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイソウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t xml:space="preserve">　　　└ </t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>　</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>制作実績3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（投稿タイプの追加　CPTUI）</t>
+    </r>
+    <rPh sb="6" eb="8">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>カテゴリー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（タクソノミーの追加　CPTUI）</t>
+    </r>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>カテゴリのなかの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（ターム　制作実績３のメニュー）</t>
+    </r>
+    <rPh sb="13" eb="15">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッセキ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>メニューから追加可能</t>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t xml:space="preserve">newtesthome.local / works / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    ↑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">             投稿タイプのスラッグ（CPT UIで設定）</t>
+  </si>
+  <si>
+    <t>newtesthome.local / works-category / web-design /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    ↑                ↑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              タクソノミーのスラッグ   タームのスラッグ</t>
+  </si>
+  <si>
+    <t>アクセルURL</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t xml:space="preserve">              （CPT UIで設定）        （CPT UIで追加した、投稿タイプメニューのタクソノミーから追加）</t>
+    <rPh sb="41" eb="43">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>トウコウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>① 投稿タイプの一覧ページ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → 制作実績の記事が全部並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → テンプレート: archive-works.php</t>
+  </si>
+  <si>
+    <t>② タクソノミーのアーカイブページ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → 特定のタームで絞り込んだ記事が並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → テンプレート: taxonomy-works-category.php</t>
+  </si>
+  <si>
+    <t>表示したいページは２種類</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>スラッグが必要なのは、CPT UIで作成したもの。　</t>
+    <rPh sb="5" eb="7">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>作成するファイルは　カスタム投稿タイプが「制作実績」（スラッグ名・works3）ならば、アーカイブは archive-works3.php となる。</t>
+    <rPh sb="0" eb="2">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>➡</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>これはあとでもいい。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>大事</t>
+    <rPh sb="0" eb="2">
+      <t>ダイジ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>要約</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウヤク</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>カスタム投稿タイプとカスタム投稿タクソノミーがあります。</t>
+  </si>
+  <si>
+    <t>タクソノミーはカスタム投稿タイプの下に分類される、付属のタグのようなものです。それぞれを登録すると管理画面にメニューが表示されるので、そこからタクソノミーのさらに詳しい「ターム」を追加したり、投稿タイプから複数の記事を追加したりできます。</t>
+  </si>
+  <si>
+    <t>表示については、以下のいずれかを選択可能です：</t>
+  </si>
+  <si>
+    <t>1. 作成したカスタム投稿タイプの一覧</t>
+  </si>
+  <si>
+    <t>2. タクソノミーの各タームの一覧</t>
+    <phoneticPr fontId="9"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1157,8 +1484,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1208,8 +1567,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1252,12 +1617,92 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1314,12 +1759,32 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -2664,8 +3129,8 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>161926</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2871,7 +3336,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>570449</xdr:colOff>
       <xdr:row>217</xdr:row>
-      <xdr:rowOff>49769</xdr:rowOff>
+      <xdr:rowOff>40244</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2915,7 +3380,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>190501</xdr:colOff>
       <xdr:row>255</xdr:row>
-      <xdr:rowOff>20216</xdr:rowOff>
+      <xdr:rowOff>1166</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3102,6 +3567,200 @@
         <a:xfrm>
           <a:off x="571499" y="1158875"/>
           <a:ext cx="6677025" cy="3413125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>201</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線矢印コネクタ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33AF56D6-248D-50C9-ED48-77E5718C4BD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7219950" y="33585150"/>
+          <a:ext cx="9525" cy="1485900"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>193</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>200</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCD6B20F-606E-4333-9D74-4742ADBAB82C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7896225" y="33651825"/>
+          <a:ext cx="0" cy="1285875"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>220</xdr:row>
+      <xdr:rowOff>43455</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{960E5B78-0ED5-365A-5F9A-96C05F1CF9BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6238875" y="35509200"/>
+          <a:ext cx="4905375" cy="2786655"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>250</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>189619</xdr:colOff>
+      <xdr:row>274</xdr:row>
+      <xdr:rowOff>47086</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD27A687-0E3B-73FC-7D6C-19F42619128B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11039475" y="43462575"/>
+          <a:ext cx="7047619" cy="4314286"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3402,14 +4061,14 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K6"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3423,8 +4082,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
@@ -3438,7 +4097,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -3452,7 +4111,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3465,7 +4124,7 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:P61"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
@@ -3473,8 +4132,8 @@
     <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3488,8 +4147,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
@@ -3503,7 +4162,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
@@ -3517,19 +4176,19 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="7" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="8" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="10" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="24"/>
     </row>
-    <row r="12" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
@@ -3543,8 +4202,8 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B14" s="5" t="s">
         <v>7</v>
       </c>
@@ -3558,7 +4217,7 @@
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
@@ -3572,8 +4231,8 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="17" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
@@ -3587,8 +4246,8 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="2:11" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -3602,7 +4261,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
@@ -3616,7 +4275,7 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
         <v>12</v>
       </c>
@@ -3630,7 +4289,7 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B22" s="3" t="s">
         <v>13</v>
       </c>
@@ -3644,7 +4303,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -3656,7 +4315,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
         <v>14</v>
       </c>
@@ -3670,16 +4329,16 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>15</v>
       </c>
@@ -3693,8 +4352,8 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="7" t="s">
         <v>16</v>
       </c>
@@ -3708,8 +4367,8 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B34" s="3" t="s">
         <v>17</v>
       </c>
@@ -3723,7 +4382,7 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B35" s="3" t="s">
         <v>18</v>
       </c>
@@ -3737,7 +4396,7 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B36" s="3" t="s">
         <v>19</v>
       </c>
@@ -3751,22 +4410,22 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="38" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="2:16" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="9" t="s">
         <v>26</v>
       </c>
@@ -3785,7 +4444,7 @@
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
     </row>
-    <row r="61" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3799,15 +4458,15 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K83"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
     <col min="3" max="15" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>27</v>
       </c>
@@ -3821,8 +4480,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:11" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="2:11" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="10" t="s">
         <v>28</v>
       </c>
@@ -3836,7 +4495,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" s="5" t="s">
         <v>29</v>
       </c>
@@ -3850,7 +4509,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
@@ -3864,7 +4523,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
@@ -3878,7 +4537,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B8" s="11" t="s">
         <v>32</v>
       </c>
@@ -3892,7 +4551,7 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B9" s="11" t="s">
         <v>33</v>
       </c>
@@ -3906,7 +4565,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
@@ -3920,8 +4579,8 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="12" spans="2:11" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="13" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="7" t="s">
         <v>35</v>
       </c>
@@ -3935,17 +4594,17 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="19" spans="2:11" ht="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" ht="18.75" x14ac:dyDescent="0.2">
       <c r="B19" s="20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B21" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="20" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" ht="19.5" x14ac:dyDescent="0.15">
       <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
@@ -3959,7 +4618,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B24" s="5" t="s">
         <v>21</v>
       </c>
@@ -3973,7 +4632,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B25" s="3" t="s">
         <v>22</v>
       </c>
@@ -3987,7 +4646,7 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B26" s="19" t="s">
         <v>58</v>
       </c>
@@ -4001,7 +4660,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B27" s="3" t="s">
         <v>23</v>
       </c>
@@ -4015,7 +4674,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B28" s="3" t="s">
         <v>19</v>
       </c>
@@ -4029,7 +4688,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
@@ -4043,7 +4702,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="32" spans="2:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" ht="16.5" x14ac:dyDescent="0.15">
       <c r="B32" s="7" t="s">
         <v>25</v>
       </c>
@@ -4057,42 +4716,42 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="36" spans="2:2" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B36" s="21" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B38" s="17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B39" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B40" s="17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B41" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B42" s="17" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="2:2" ht="23.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" ht="23.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="22" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B83" t="s">
         <v>66</v>
       </c>
@@ -4110,15 +4769,15 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K16"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="13" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>36</v>
       </c>
@@ -4132,8 +4791,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="12" t="s">
         <v>37</v>
       </c>
@@ -4145,7 +4804,7 @@
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
         <v>38</v>
       </c>
@@ -4159,7 +4818,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
         <v>39</v>
       </c>
@@ -4173,7 +4832,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -4185,7 +4844,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
@@ -4199,7 +4858,7 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B9" s="3" t="s">
         <v>41</v>
       </c>
@@ -4213,7 +4872,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -4225,7 +4884,7 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B11" s="3" t="s">
         <v>42</v>
       </c>
@@ -4239,8 +4898,8 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="13" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="14" t="s">
         <v>43</v>
       </c>
@@ -4252,7 +4911,7 @@
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B15" s="16" t="s">
         <v>44</v>
       </c>
@@ -4266,7 +4925,7 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4280,9 +4939,9 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B3:E38"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B3" s="17" t="s">
         <v>45</v>
       </c>
@@ -4290,17 +4949,17 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B38" t="s">
         <v>48</v>
       </c>
@@ -4315,45 +4974,45 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E4DE1B-CEE6-4D06-B682-4A9E3F05719A}">
   <dimension ref="B2:P147"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="16:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="16:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="16:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P38" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="16:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P39" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B74" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B75" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B111" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="147" spans="16:16" x14ac:dyDescent="0.2">
+    <row r="147" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P147" t="s">
         <v>54</v>
       </c>
@@ -4368,65 +5027,65 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A893AC6-FB79-450E-8D17-FE484C32412D}">
   <dimension ref="B2:L75"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B26" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B27" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="19" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" ht="18.75" x14ac:dyDescent="0.2">
       <c r="B31" s="26" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="27"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B32" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B33" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B36" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.15">
       <c r="L44" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.15">
       <c r="L45" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.15">
       <c r="L47" s="25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B74" t="s">
         <v>79</v>
       </c>
@@ -4434,7 +5093,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B75" s="17" t="s">
         <v>80</v>
       </c>
@@ -4451,15 +5110,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F487261-4C57-4DE5-9D5F-EC7B6550A8CC}">
-  <dimension ref="B1:L283"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:AC283"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="12.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.375" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="B1" s="33" t="s">
+    <row r="1" spans="2:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B1" s="32" t="s">
         <v>118</v>
       </c>
       <c r="C1" s="27"/>
@@ -4468,98 +5127,609 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B4" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="31" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B50" s="17" t="s">
+    <row r="17" spans="13:13" x14ac:dyDescent="0.15">
+      <c r="M17" s="55" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="13:13" x14ac:dyDescent="0.15">
+      <c r="M18" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="13:13" x14ac:dyDescent="0.15">
+      <c r="M20" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="13:13" x14ac:dyDescent="0.15">
+      <c r="M22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="13:13" x14ac:dyDescent="0.15">
+      <c r="M23" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="13:13" x14ac:dyDescent="0.15">
+      <c r="M24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B50" s="48" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="37"/>
+      <c r="I50" s="37"/>
+      <c r="J50" s="37"/>
+      <c r="K50" s="37"/>
+      <c r="L50" s="37"/>
+      <c r="M50" s="38"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B51" s="39" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
+      <c r="C51" s="41"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="41"/>
+      <c r="J51" s="41"/>
+      <c r="K51" s="41"/>
+      <c r="L51" s="41"/>
+      <c r="M51" s="42"/>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B52" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="D52" s="30" t="s">
+      <c r="C52" s="41"/>
+      <c r="D52" s="40" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B53" t="s">
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="41"/>
+      <c r="J52" s="41"/>
+      <c r="K52" s="41"/>
+      <c r="L52" s="41"/>
+      <c r="M52" s="42"/>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B53" s="39" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
+      <c r="C53" s="41"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="41"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="41"/>
+      <c r="J53" s="41"/>
+      <c r="K53" s="41"/>
+      <c r="L53" s="41"/>
+      <c r="M53" s="42"/>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B54" s="39"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="41"/>
+      <c r="J54" s="41"/>
+      <c r="K54" s="41"/>
+      <c r="L54" s="41"/>
+      <c r="M54" s="42"/>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B55" s="39" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C55" s="41"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="41"/>
+      <c r="J55" s="41"/>
+      <c r="K55" s="41"/>
+      <c r="L55" s="41"/>
+      <c r="M55" s="42"/>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B56" s="39"/>
+      <c r="C56" s="41"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41"/>
+      <c r="G56" s="41"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="41"/>
+      <c r="J56" s="41"/>
+      <c r="K56" s="41"/>
+      <c r="L56" s="41"/>
+      <c r="M56" s="42"/>
+    </row>
+    <row r="57" spans="2:15" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="B57" s="39"/>
+      <c r="C57" s="41"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="41"/>
+      <c r="J57" s="41"/>
+      <c r="K57" s="41"/>
+      <c r="L57" s="41"/>
+      <c r="M57" s="42"/>
+      <c r="N57" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="O57" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B58" s="39"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="41"/>
+      <c r="G58" s="41"/>
+      <c r="H58" s="41"/>
+      <c r="I58" s="41"/>
+      <c r="J58" s="41"/>
+      <c r="K58" s="41"/>
+      <c r="L58" s="41"/>
+      <c r="M58" s="42"/>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B59" s="39"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="41"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="41"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="41"/>
+      <c r="J59" s="41"/>
+      <c r="K59" s="41"/>
+      <c r="L59" s="41"/>
+      <c r="M59" s="42"/>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B60" s="39"/>
+      <c r="C60" s="41"/>
+      <c r="D60" s="41"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="41"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="41"/>
+      <c r="I60" s="41"/>
+      <c r="J60" s="41"/>
+      <c r="K60" s="41"/>
+      <c r="L60" s="41"/>
+      <c r="M60" s="42"/>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B61" s="39"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="41"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="41"/>
+      <c r="I61" s="41"/>
+      <c r="J61" s="41"/>
+      <c r="K61" s="41"/>
+      <c r="L61" s="41"/>
+      <c r="M61" s="42"/>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B62" s="39"/>
+      <c r="C62" s="41"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="41"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="41"/>
+      <c r="I62" s="41"/>
+      <c r="J62" s="41"/>
+      <c r="K62" s="41"/>
+      <c r="L62" s="41"/>
+      <c r="M62" s="42"/>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B63" s="39"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="41"/>
+      <c r="G63" s="41"/>
+      <c r="H63" s="41"/>
+      <c r="I63" s="41"/>
+      <c r="J63" s="41"/>
+      <c r="K63" s="41"/>
+      <c r="L63" s="41"/>
+      <c r="M63" s="42"/>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.15">
+      <c r="B64" s="39"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="41"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="41"/>
+      <c r="I64" s="41"/>
+      <c r="J64" s="41"/>
+      <c r="K64" s="41"/>
+      <c r="L64" s="41"/>
+      <c r="M64" s="42"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B65" s="39"/>
+      <c r="C65" s="41"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="41"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="41"/>
+      <c r="J65" s="41"/>
+      <c r="K65" s="41"/>
+      <c r="L65" s="41"/>
+      <c r="M65" s="42"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B66" s="39"/>
+      <c r="C66" s="41"/>
+      <c r="D66" s="41"/>
+      <c r="E66" s="41"/>
+      <c r="F66" s="41"/>
+      <c r="G66" s="41"/>
+      <c r="H66" s="41"/>
+      <c r="I66" s="41"/>
+      <c r="J66" s="41"/>
+      <c r="K66" s="41"/>
+      <c r="L66" s="41"/>
+      <c r="M66" s="42"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B67" s="39"/>
+      <c r="C67" s="41"/>
+      <c r="D67" s="41"/>
+      <c r="E67" s="41"/>
+      <c r="F67" s="41"/>
+      <c r="G67" s="41"/>
+      <c r="H67" s="41"/>
+      <c r="I67" s="41"/>
+      <c r="J67" s="41"/>
+      <c r="K67" s="41"/>
+      <c r="L67" s="41"/>
+      <c r="M67" s="42"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B68" s="39"/>
+      <c r="C68" s="41"/>
+      <c r="D68" s="41"/>
+      <c r="E68" s="41"/>
+      <c r="F68" s="41"/>
+      <c r="G68" s="41"/>
+      <c r="H68" s="41"/>
+      <c r="I68" s="41"/>
+      <c r="J68" s="41"/>
+      <c r="K68" s="41"/>
+      <c r="L68" s="41"/>
+      <c r="M68" s="42"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B69" s="39"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="41"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="41"/>
+      <c r="I69" s="41"/>
+      <c r="J69" s="41"/>
+      <c r="K69" s="41"/>
+      <c r="L69" s="41"/>
+      <c r="M69" s="42"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B70" s="39"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="41"/>
+      <c r="E70" s="41"/>
+      <c r="F70" s="41"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="41"/>
+      <c r="I70" s="41"/>
+      <c r="J70" s="41"/>
+      <c r="K70" s="41"/>
+      <c r="L70" s="41"/>
+      <c r="M70" s="42"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B71" s="39"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="41"/>
+      <c r="F71" s="41"/>
+      <c r="G71" s="41"/>
+      <c r="H71" s="41"/>
+      <c r="I71" s="41"/>
+      <c r="J71" s="41"/>
+      <c r="K71" s="41"/>
+      <c r="L71" s="41"/>
+      <c r="M71" s="42"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B72" s="39"/>
+      <c r="C72" s="41"/>
+      <c r="D72" s="41"/>
+      <c r="E72" s="41"/>
+      <c r="F72" s="41"/>
+      <c r="G72" s="41"/>
+      <c r="H72" s="41"/>
+      <c r="I72" s="41"/>
+      <c r="J72" s="41"/>
+      <c r="K72" s="41"/>
+      <c r="L72" s="41"/>
+      <c r="M72" s="42"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B73" s="39"/>
+      <c r="C73" s="41"/>
+      <c r="D73" s="41"/>
+      <c r="E73" s="41"/>
+      <c r="F73" s="41"/>
+      <c r="G73" s="41"/>
+      <c r="H73" s="41"/>
+      <c r="I73" s="41"/>
+      <c r="J73" s="41"/>
+      <c r="K73" s="41"/>
+      <c r="L73" s="41"/>
+      <c r="M73" s="42"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B74" s="39"/>
+      <c r="C74" s="41"/>
+      <c r="D74" s="41"/>
+      <c r="E74" s="41"/>
+      <c r="F74" s="41"/>
+      <c r="G74" s="41"/>
+      <c r="H74" s="41"/>
+      <c r="I74" s="41"/>
+      <c r="J74" s="41"/>
+      <c r="K74" s="41"/>
+      <c r="L74" s="41"/>
+      <c r="M74" s="42"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B75" s="39"/>
+      <c r="C75" s="41"/>
+      <c r="D75" s="41"/>
+      <c r="E75" s="41"/>
+      <c r="F75" s="41"/>
+      <c r="G75" s="41"/>
+      <c r="H75" s="41"/>
+      <c r="I75" s="41"/>
+      <c r="J75" s="41"/>
+      <c r="K75" s="41"/>
+      <c r="L75" s="41"/>
+      <c r="M75" s="42"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B76" s="39"/>
+      <c r="C76" s="41"/>
+      <c r="D76" s="41"/>
+      <c r="E76" s="41"/>
+      <c r="F76" s="41"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="41"/>
+      <c r="I76" s="41"/>
+      <c r="J76" s="41"/>
+      <c r="K76" s="41"/>
+      <c r="L76" s="41"/>
+      <c r="M76" s="42"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B77" s="39"/>
+      <c r="C77" s="41"/>
+      <c r="D77" s="41"/>
+      <c r="E77" s="41"/>
+      <c r="F77" s="41"/>
+      <c r="G77" s="41"/>
+      <c r="H77" s="41"/>
+      <c r="I77" s="41"/>
+      <c r="J77" s="41"/>
+      <c r="K77" s="41"/>
+      <c r="L77" s="41"/>
+      <c r="M77" s="42"/>
+    </row>
+    <row r="78" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B78" s="39"/>
+      <c r="C78" s="41"/>
+      <c r="D78" s="41"/>
+      <c r="E78" s="41"/>
+      <c r="F78" s="41"/>
+      <c r="G78" s="41"/>
+      <c r="H78" s="41"/>
+      <c r="I78" s="41"/>
+      <c r="J78" s="41"/>
+      <c r="K78" s="41"/>
+      <c r="L78" s="41"/>
+      <c r="M78" s="42"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B79" s="39"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="41"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="41"/>
+      <c r="I79" s="41"/>
+      <c r="J79" s="41"/>
+      <c r="K79" s="41"/>
+      <c r="L79" s="41"/>
+      <c r="M79" s="42"/>
+    </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B80" s="39"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="41"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="41"/>
+      <c r="J80" s="41"/>
+      <c r="K80" s="41"/>
+      <c r="L80" s="41"/>
+      <c r="M80" s="42"/>
+    </row>
+    <row r="81" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B81" s="39"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="41"/>
+      <c r="F81" s="41"/>
+      <c r="G81" s="41"/>
+      <c r="H81" s="41"/>
+      <c r="I81" s="41"/>
+      <c r="J81" s="41"/>
+      <c r="K81" s="41"/>
+      <c r="L81" s="41"/>
+      <c r="M81" s="42"/>
+    </row>
+    <row r="82" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B82" s="39"/>
+      <c r="C82" s="41"/>
+      <c r="D82" s="41"/>
+      <c r="E82" s="41"/>
+      <c r="F82" s="41"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="41"/>
+      <c r="I82" s="41"/>
+      <c r="J82" s="41"/>
+      <c r="K82" s="41"/>
+      <c r="L82" s="41"/>
+      <c r="M82" s="42"/>
+    </row>
+    <row r="83" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B83" s="39"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="41"/>
+      <c r="F83" s="41"/>
+      <c r="G83" s="41"/>
+      <c r="H83" s="41"/>
+      <c r="I83" s="41"/>
+      <c r="J83" s="41"/>
+      <c r="K83" s="41"/>
+      <c r="L83" s="41"/>
+      <c r="M83" s="42"/>
+    </row>
+    <row r="84" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="43"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="44"/>
+      <c r="F84" s="44"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="44"/>
+      <c r="I84" s="44"/>
+      <c r="J84" s="44"/>
+      <c r="K84" s="44"/>
+      <c r="L84" s="44"/>
+      <c r="M84" s="45"/>
+    </row>
+    <row r="89" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B89" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B90" s="17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B91" s="17" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B92" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B93" s="17" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="98" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:3" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B98" s="18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B101" s="17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="103" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B103" s="29" t="s">
         <v>88</v>
       </c>
@@ -4567,7 +5737,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="104" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B104" s="28" t="s">
         <v>90</v>
       </c>
@@ -4575,7 +5745,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="105" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B105" s="28" t="s">
         <v>92</v>
       </c>
@@ -4583,13 +5753,13 @@
         <v>93</v>
       </c>
     </row>
-    <row r="114" spans="2:4" ht="19" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:4" ht="18.75" x14ac:dyDescent="0.2">
       <c r="B114" s="26" t="s">
         <v>104</v>
       </c>
       <c r="C114" s="27"/>
     </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B115" t="s">
         <v>103</v>
       </c>
@@ -4597,207 +5767,1412 @@
         <v>120</v>
       </c>
     </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B118" s="17" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B131" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="154" spans="9:10" x14ac:dyDescent="0.2">
+    <row r="154" spans="9:10" x14ac:dyDescent="0.15">
       <c r="J154" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="155" spans="9:10" x14ac:dyDescent="0.2">
+    <row r="155" spans="9:10" x14ac:dyDescent="0.15">
       <c r="J155" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="158" spans="9:10" x14ac:dyDescent="0.2">
+    <row r="158" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I158" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="173" spans="9:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="9:9" x14ac:dyDescent="0.15">
       <c r="I173" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="175" spans="9:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="9:9" x14ac:dyDescent="0.15">
       <c r="I175" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="176" spans="9:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="9:9" x14ac:dyDescent="0.15">
       <c r="I176" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:17" x14ac:dyDescent="0.15">
       <c r="I178" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="179" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:17" x14ac:dyDescent="0.15">
       <c r="I179" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="181" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:17" x14ac:dyDescent="0.15">
       <c r="I181" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="183" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:17" x14ac:dyDescent="0.15">
       <c r="I183" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="184" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:17" x14ac:dyDescent="0.15">
       <c r="I184" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="191" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B191" s="31" t="s">
+    <row r="188" spans="2:17" ht="15" x14ac:dyDescent="0.25">
+      <c r="I188" s="35" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="189" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="I189" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="190" spans="2:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="191" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="B191" s="30" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="I191" s="36"/>
+      <c r="J191" s="37"/>
+      <c r="K191" s="37"/>
+      <c r="L191" s="37"/>
+      <c r="M191" s="37"/>
+      <c r="N191" s="37"/>
+      <c r="O191" s="37"/>
+      <c r="P191" s="37"/>
+      <c r="Q191" s="38"/>
+    </row>
+    <row r="192" spans="2:17" x14ac:dyDescent="0.15">
+      <c r="I192" s="39"/>
+      <c r="J192" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="K192" s="41"/>
+      <c r="L192" s="41"/>
+      <c r="M192" s="41"/>
+      <c r="N192" s="41"/>
+      <c r="O192" s="41"/>
+      <c r="P192" s="41"/>
+      <c r="Q192" s="42"/>
+    </row>
+    <row r="193" spans="9:17" x14ac:dyDescent="0.15">
+      <c r="I193" s="39"/>
+      <c r="J193" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="K193" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="L193" s="41"/>
+      <c r="M193" s="41"/>
+      <c r="N193" s="41"/>
+      <c r="O193" s="41"/>
+      <c r="P193" s="41"/>
+      <c r="Q193" s="42"/>
+    </row>
+    <row r="194" spans="9:17" x14ac:dyDescent="0.15">
+      <c r="I194" s="39"/>
+      <c r="J194" s="41"/>
+      <c r="K194" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="L194" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="M194" s="41"/>
+      <c r="N194" s="41"/>
+      <c r="O194" s="41"/>
+      <c r="P194" s="41"/>
+      <c r="Q194" s="42"/>
+    </row>
+    <row r="195" spans="9:17" x14ac:dyDescent="0.15">
+      <c r="I195" s="39"/>
+      <c r="J195" s="41"/>
+      <c r="K195" s="41"/>
+      <c r="L195" s="41"/>
+      <c r="M195" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="N195" s="41"/>
+      <c r="O195" s="41"/>
+      <c r="P195" s="41"/>
+      <c r="Q195" s="42"/>
+    </row>
+    <row r="196" spans="9:17" x14ac:dyDescent="0.15">
+      <c r="I196" s="39"/>
+      <c r="J196" s="41"/>
+      <c r="K196" s="41"/>
+      <c r="L196" s="41"/>
+      <c r="M196" s="41"/>
+      <c r="N196" s="41"/>
+      <c r="O196" s="41"/>
+      <c r="P196" s="41"/>
+      <c r="Q196" s="42"/>
+    </row>
+    <row r="197" spans="9:17" x14ac:dyDescent="0.15">
+      <c r="I197" s="39"/>
+      <c r="J197" s="41"/>
+      <c r="K197" s="41"/>
+      <c r="L197" s="41"/>
+      <c r="M197" s="41"/>
+      <c r="N197" s="41"/>
+      <c r="O197" s="41"/>
+      <c r="P197" s="41"/>
+      <c r="Q197" s="42"/>
+    </row>
+    <row r="198" spans="9:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="I198" s="43"/>
+      <c r="J198" s="44"/>
+      <c r="K198" s="44"/>
+      <c r="L198" s="44"/>
+      <c r="M198" s="44"/>
+      <c r="N198" s="44"/>
+      <c r="O198" s="44"/>
+      <c r="P198" s="44"/>
+      <c r="Q198" s="45"/>
+    </row>
+    <row r="202" spans="9:17" x14ac:dyDescent="0.15">
+      <c r="K202" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="203" spans="9:17" x14ac:dyDescent="0.15">
+      <c r="J203" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B221" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B223" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B224" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B226" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B227" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B229" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H230" s="17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="231" spans="2:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B231" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B232" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B233" s="31" t="s">
+      <c r="H232" s="36"/>
+      <c r="I232" s="37"/>
+      <c r="J232" s="37"/>
+      <c r="K232" s="37"/>
+      <c r="L232" s="37"/>
+      <c r="M232" s="37"/>
+      <c r="N232" s="37"/>
+      <c r="O232" s="37"/>
+      <c r="P232" s="37"/>
+      <c r="Q232" s="37"/>
+      <c r="R232" s="37"/>
+      <c r="S232" s="37"/>
+      <c r="T232" s="37"/>
+      <c r="U232" s="37"/>
+      <c r="V232" s="37"/>
+      <c r="W232" s="37"/>
+      <c r="X232" s="37"/>
+      <c r="Y232" s="37"/>
+      <c r="Z232" s="37"/>
+      <c r="AA232" s="37"/>
+      <c r="AB232" s="37"/>
+      <c r="AC232" s="38"/>
+    </row>
+    <row r="233" spans="2:29" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B233" s="30" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B234" s="32" t="s">
+      <c r="H233" s="39"/>
+      <c r="I233" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="J233" s="52"/>
+      <c r="K233" s="41"/>
+      <c r="L233" s="41"/>
+      <c r="M233" s="41"/>
+      <c r="N233" s="41"/>
+      <c r="O233" s="41"/>
+      <c r="P233" s="41"/>
+      <c r="Q233" s="41"/>
+      <c r="R233" s="41"/>
+      <c r="S233" s="41"/>
+      <c r="T233" s="41"/>
+      <c r="U233" s="41"/>
+      <c r="V233" s="41"/>
+      <c r="W233" s="41"/>
+      <c r="X233" s="41"/>
+      <c r="Y233" s="41"/>
+      <c r="Z233" s="41"/>
+      <c r="AA233" s="41"/>
+      <c r="AB233" s="41"/>
+      <c r="AC233" s="42"/>
+    </row>
+    <row r="234" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="B234" s="31" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="H234" s="39"/>
+      <c r="I234" s="41"/>
+      <c r="J234" s="41"/>
+      <c r="K234" s="41"/>
+      <c r="L234" s="41"/>
+      <c r="M234" s="41"/>
+      <c r="N234" s="41"/>
+      <c r="O234" s="41"/>
+      <c r="P234" s="41"/>
+      <c r="Q234" s="41"/>
+      <c r="R234" s="41"/>
+      <c r="S234" s="41"/>
+      <c r="T234" s="41"/>
+      <c r="U234" s="41"/>
+      <c r="V234" s="41"/>
+      <c r="W234" s="41"/>
+      <c r="X234" s="41"/>
+      <c r="Y234" s="41"/>
+      <c r="Z234" s="41"/>
+      <c r="AA234" s="41"/>
+      <c r="AB234" s="41"/>
+      <c r="AC234" s="42"/>
+    </row>
+    <row r="235" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B235" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="H235" s="39"/>
+      <c r="I235" s="41"/>
+      <c r="J235" s="41"/>
+      <c r="K235" s="41"/>
+      <c r="L235" s="41"/>
+      <c r="M235" s="41"/>
+      <c r="N235" s="41"/>
+      <c r="O235" s="41"/>
+      <c r="P235" s="41"/>
+      <c r="Q235" s="41"/>
+      <c r="R235" s="41"/>
+      <c r="S235" s="41"/>
+      <c r="T235" s="41"/>
+      <c r="U235" s="41"/>
+      <c r="V235" s="41"/>
+      <c r="W235" s="41"/>
+      <c r="X235" s="41"/>
+      <c r="Y235" s="41"/>
+      <c r="Z235" s="41"/>
+      <c r="AA235" s="41"/>
+      <c r="AB235" s="41"/>
+      <c r="AC235" s="42"/>
+    </row>
+    <row r="236" spans="2:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B236" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="262" spans="2:12" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="B262" s="34" t="s">
+      <c r="H236" s="39"/>
+      <c r="I236" s="41"/>
+      <c r="J236" s="41"/>
+      <c r="K236" s="41"/>
+      <c r="L236" s="41"/>
+      <c r="M236" s="41"/>
+      <c r="N236" s="41"/>
+      <c r="O236" s="41"/>
+      <c r="P236" s="41"/>
+      <c r="Q236" s="41"/>
+      <c r="R236" s="41"/>
+      <c r="S236" s="41"/>
+      <c r="T236" s="41"/>
+      <c r="U236" s="41"/>
+      <c r="V236" s="41"/>
+      <c r="W236" s="41"/>
+      <c r="X236" s="41"/>
+      <c r="Y236" s="41"/>
+      <c r="Z236" s="41"/>
+      <c r="AA236" s="41"/>
+      <c r="AB236" s="41"/>
+      <c r="AC236" s="42"/>
+    </row>
+    <row r="237" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H237" s="39"/>
+      <c r="I237" s="36"/>
+      <c r="J237" s="37"/>
+      <c r="K237" s="37"/>
+      <c r="L237" s="37"/>
+      <c r="M237" s="37"/>
+      <c r="N237" s="38"/>
+      <c r="O237" s="41"/>
+      <c r="P237" s="41"/>
+      <c r="Q237" s="41"/>
+      <c r="R237" s="41"/>
+      <c r="S237" s="41"/>
+      <c r="T237" s="41"/>
+      <c r="U237" s="41"/>
+      <c r="V237" s="41"/>
+      <c r="W237" s="41"/>
+      <c r="X237" s="41"/>
+      <c r="Y237" s="41"/>
+      <c r="Z237" s="41"/>
+      <c r="AA237" s="41"/>
+      <c r="AB237" s="41"/>
+      <c r="AC237" s="42"/>
+    </row>
+    <row r="238" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H238" s="39"/>
+      <c r="I238" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="J238" s="47"/>
+      <c r="K238" s="47"/>
+      <c r="L238" s="41"/>
+      <c r="M238" s="41"/>
+      <c r="N238" s="42"/>
+      <c r="O238" s="41"/>
+      <c r="P238" s="41"/>
+      <c r="Q238" s="41"/>
+      <c r="R238" s="41"/>
+      <c r="S238" s="41"/>
+      <c r="T238" s="41"/>
+      <c r="U238" s="41"/>
+      <c r="V238" s="41"/>
+      <c r="W238" s="41"/>
+      <c r="X238" s="41"/>
+      <c r="Y238" s="41"/>
+      <c r="Z238" s="41"/>
+      <c r="AA238" s="41"/>
+      <c r="AB238" s="41"/>
+      <c r="AC238" s="42"/>
+    </row>
+    <row r="239" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H239" s="39"/>
+      <c r="I239" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="J239" s="41"/>
+      <c r="K239" s="41"/>
+      <c r="L239" s="41"/>
+      <c r="M239" s="41"/>
+      <c r="N239" s="42"/>
+      <c r="O239" s="41"/>
+      <c r="P239" s="41"/>
+      <c r="Q239" s="41"/>
+      <c r="R239" s="41"/>
+      <c r="S239" s="41"/>
+      <c r="T239" s="41"/>
+      <c r="U239" s="41"/>
+      <c r="V239" s="41"/>
+      <c r="W239" s="41"/>
+      <c r="X239" s="41"/>
+      <c r="Y239" s="41"/>
+      <c r="Z239" s="41"/>
+      <c r="AA239" s="41"/>
+      <c r="AB239" s="41"/>
+      <c r="AC239" s="42"/>
+    </row>
+    <row r="240" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H240" s="39"/>
+      <c r="I240" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="J240" s="41"/>
+      <c r="K240" s="41"/>
+      <c r="L240" s="41"/>
+      <c r="M240" s="41"/>
+      <c r="N240" s="42"/>
+      <c r="O240" s="41"/>
+      <c r="P240" s="41"/>
+      <c r="Q240" s="41"/>
+      <c r="R240" s="41"/>
+      <c r="S240" s="41"/>
+      <c r="T240" s="41"/>
+      <c r="U240" s="41"/>
+      <c r="V240" s="41"/>
+      <c r="W240" s="41"/>
+      <c r="X240" s="41"/>
+      <c r="Y240" s="41"/>
+      <c r="Z240" s="41"/>
+      <c r="AA240" s="41"/>
+      <c r="AB240" s="41"/>
+      <c r="AC240" s="42"/>
+    </row>
+    <row r="241" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H241" s="39"/>
+      <c r="I241" s="39"/>
+      <c r="J241" s="41"/>
+      <c r="K241" s="41"/>
+      <c r="L241" s="41"/>
+      <c r="M241" s="41"/>
+      <c r="N241" s="42"/>
+      <c r="O241" s="41"/>
+      <c r="P241" s="41"/>
+      <c r="Q241" s="41"/>
+      <c r="R241" s="41"/>
+      <c r="S241" s="41"/>
+      <c r="T241" s="41"/>
+      <c r="U241" s="41"/>
+      <c r="V241" s="41"/>
+      <c r="W241" s="41"/>
+      <c r="X241" s="41"/>
+      <c r="Y241" s="41"/>
+      <c r="Z241" s="41"/>
+      <c r="AA241" s="41"/>
+      <c r="AB241" s="41"/>
+      <c r="AC241" s="42"/>
+    </row>
+    <row r="242" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H242" s="39"/>
+      <c r="I242" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="J242" s="47"/>
+      <c r="K242" s="47"/>
+      <c r="L242" s="47"/>
+      <c r="M242" s="47"/>
+      <c r="N242" s="42"/>
+      <c r="O242" s="41"/>
+      <c r="P242" s="41"/>
+      <c r="Q242" s="41"/>
+      <c r="R242" s="41"/>
+      <c r="S242" s="41"/>
+      <c r="T242" s="41"/>
+      <c r="U242" s="41"/>
+      <c r="V242" s="41"/>
+      <c r="W242" s="41"/>
+      <c r="X242" s="41"/>
+      <c r="Y242" s="41"/>
+      <c r="Z242" s="41"/>
+      <c r="AA242" s="41"/>
+      <c r="AB242" s="41"/>
+      <c r="AC242" s="42"/>
+    </row>
+    <row r="243" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H243" s="39"/>
+      <c r="I243" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="J243" s="41"/>
+      <c r="K243" s="41"/>
+      <c r="L243" s="41"/>
+      <c r="M243" s="41"/>
+      <c r="N243" s="42"/>
+      <c r="O243" s="41"/>
+      <c r="P243" s="41"/>
+      <c r="Q243" s="41"/>
+      <c r="R243" s="41"/>
+      <c r="S243" s="41"/>
+      <c r="T243" s="41"/>
+      <c r="U243" s="41"/>
+      <c r="V243" s="41"/>
+      <c r="W243" s="41"/>
+      <c r="X243" s="41"/>
+      <c r="Y243" s="41"/>
+      <c r="Z243" s="41"/>
+      <c r="AA243" s="41"/>
+      <c r="AB243" s="41"/>
+      <c r="AC243" s="42"/>
+    </row>
+    <row r="244" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H244" s="39"/>
+      <c r="I244" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="J244" s="41"/>
+      <c r="K244" s="41"/>
+      <c r="L244" s="41"/>
+      <c r="M244" s="41"/>
+      <c r="N244" s="42"/>
+      <c r="O244" s="41"/>
+      <c r="P244" s="41"/>
+      <c r="Q244" s="41"/>
+      <c r="R244" s="41"/>
+      <c r="S244" s="41"/>
+      <c r="T244" s="41"/>
+      <c r="U244" s="41"/>
+      <c r="V244" s="41"/>
+      <c r="W244" s="41"/>
+      <c r="X244" s="41"/>
+      <c r="Y244" s="41"/>
+      <c r="Z244" s="41"/>
+      <c r="AA244" s="41"/>
+      <c r="AB244" s="41"/>
+      <c r="AC244" s="42"/>
+    </row>
+    <row r="245" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H245" s="39"/>
+      <c r="I245" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="J245" s="41"/>
+      <c r="K245" s="41"/>
+      <c r="L245" s="41"/>
+      <c r="M245" s="41"/>
+      <c r="N245" s="42"/>
+      <c r="O245" s="41"/>
+      <c r="P245" s="41"/>
+      <c r="Q245" s="41"/>
+      <c r="R245" s="41"/>
+      <c r="S245" s="41"/>
+      <c r="T245" s="41"/>
+      <c r="U245" s="41"/>
+      <c r="V245" s="41"/>
+      <c r="W245" s="41"/>
+      <c r="X245" s="41"/>
+      <c r="Y245" s="41"/>
+      <c r="Z245" s="41"/>
+      <c r="AA245" s="41"/>
+      <c r="AB245" s="41"/>
+      <c r="AC245" s="42"/>
+    </row>
+    <row r="246" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H246" s="39"/>
+      <c r="I246" s="39"/>
+      <c r="J246" s="41"/>
+      <c r="K246" s="41"/>
+      <c r="L246" s="41"/>
+      <c r="M246" s="41"/>
+      <c r="N246" s="42"/>
+      <c r="O246" s="41"/>
+      <c r="P246" s="41"/>
+      <c r="Q246" s="41"/>
+      <c r="R246" s="41"/>
+      <c r="S246" s="41"/>
+      <c r="T246" s="41"/>
+      <c r="U246" s="41"/>
+      <c r="V246" s="41"/>
+      <c r="W246" s="41"/>
+      <c r="X246" s="41"/>
+      <c r="Y246" s="41"/>
+      <c r="Z246" s="41"/>
+      <c r="AA246" s="41"/>
+      <c r="AB246" s="41"/>
+      <c r="AC246" s="42"/>
+    </row>
+    <row r="247" spans="8:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H247" s="39"/>
+      <c r="I247" s="43"/>
+      <c r="J247" s="44"/>
+      <c r="K247" s="44"/>
+      <c r="L247" s="44"/>
+      <c r="M247" s="44"/>
+      <c r="N247" s="45"/>
+      <c r="O247" s="41"/>
+      <c r="P247" s="41"/>
+      <c r="Q247" s="41"/>
+      <c r="R247" s="41"/>
+      <c r="S247" s="41"/>
+      <c r="T247" s="41"/>
+      <c r="U247" s="41"/>
+      <c r="V247" s="41"/>
+      <c r="W247" s="41"/>
+      <c r="X247" s="41"/>
+      <c r="Y247" s="41"/>
+      <c r="Z247" s="41"/>
+      <c r="AA247" s="41"/>
+      <c r="AB247" s="41"/>
+      <c r="AC247" s="42"/>
+    </row>
+    <row r="248" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H248" s="39"/>
+      <c r="I248" s="41"/>
+      <c r="J248" s="41"/>
+      <c r="K248" s="41"/>
+      <c r="L248" s="41"/>
+      <c r="M248" s="41"/>
+      <c r="N248" s="41"/>
+      <c r="O248" s="41"/>
+      <c r="P248" s="41"/>
+      <c r="Q248" s="41"/>
+      <c r="R248" s="41"/>
+      <c r="S248" s="41"/>
+      <c r="T248" s="41"/>
+      <c r="U248" s="41"/>
+      <c r="V248" s="41"/>
+      <c r="W248" s="41"/>
+      <c r="X248" s="41"/>
+      <c r="Y248" s="41"/>
+      <c r="Z248" s="41"/>
+      <c r="AA248" s="41"/>
+      <c r="AB248" s="41"/>
+      <c r="AC248" s="42"/>
+    </row>
+    <row r="249" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H249" s="39"/>
+      <c r="I249" s="41"/>
+      <c r="J249" s="41"/>
+      <c r="K249" s="41"/>
+      <c r="L249" s="41"/>
+      <c r="M249" s="41"/>
+      <c r="N249" s="41"/>
+      <c r="O249" s="41"/>
+      <c r="P249" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q249" s="47"/>
+      <c r="R249" s="47"/>
+      <c r="S249" s="47"/>
+      <c r="T249" s="47"/>
+      <c r="U249" s="47"/>
+      <c r="V249" s="47"/>
+      <c r="W249" s="47"/>
+      <c r="X249" s="41"/>
+      <c r="Y249" s="41"/>
+      <c r="Z249" s="41"/>
+      <c r="AA249" s="41"/>
+      <c r="AB249" s="41"/>
+      <c r="AC249" s="42"/>
+    </row>
+    <row r="250" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H250" s="39"/>
+      <c r="I250" s="41"/>
+      <c r="J250" s="41"/>
+      <c r="K250" s="41"/>
+      <c r="L250" s="41"/>
+      <c r="M250" s="41"/>
+      <c r="N250" s="41"/>
+      <c r="O250" s="41"/>
+      <c r="P250" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q250" s="47"/>
+      <c r="R250" s="47"/>
+      <c r="S250" s="47"/>
+      <c r="T250" s="47"/>
+      <c r="U250" s="47"/>
+      <c r="V250" s="47"/>
+      <c r="W250" s="47"/>
+      <c r="X250" s="41"/>
+      <c r="Y250" s="41"/>
+      <c r="Z250" s="41"/>
+      <c r="AA250" s="41"/>
+      <c r="AB250" s="41"/>
+      <c r="AC250" s="42"/>
+    </row>
+    <row r="251" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H251" s="39"/>
+      <c r="I251" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="J251" s="52"/>
+      <c r="K251" s="52"/>
+      <c r="L251" s="41"/>
+      <c r="M251" s="41"/>
+      <c r="N251" s="41"/>
+      <c r="O251" s="41"/>
+      <c r="P251" s="41"/>
+      <c r="Q251" s="41"/>
+      <c r="R251" s="41"/>
+      <c r="S251" s="41"/>
+      <c r="T251" s="41"/>
+      <c r="U251" s="41"/>
+      <c r="V251" s="41"/>
+      <c r="W251" s="41"/>
+      <c r="X251" s="41"/>
+      <c r="Y251" s="41"/>
+      <c r="Z251" s="41"/>
+      <c r="AA251" s="41"/>
+      <c r="AB251" s="41"/>
+      <c r="AC251" s="42"/>
+    </row>
+    <row r="252" spans="8:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H252" s="39"/>
+      <c r="I252" s="41"/>
+      <c r="J252" s="41"/>
+      <c r="K252" s="41"/>
+      <c r="L252" s="41"/>
+      <c r="M252" s="41"/>
+      <c r="N252" s="41"/>
+      <c r="O252" s="41"/>
+      <c r="P252" s="41"/>
+      <c r="Q252" s="41"/>
+      <c r="R252" s="41"/>
+      <c r="S252" s="41"/>
+      <c r="T252" s="41"/>
+      <c r="U252" s="41"/>
+      <c r="V252" s="41"/>
+      <c r="W252" s="41"/>
+      <c r="X252" s="41"/>
+      <c r="Y252" s="41"/>
+      <c r="Z252" s="41"/>
+      <c r="AA252" s="41"/>
+      <c r="AB252" s="41"/>
+      <c r="AC252" s="42"/>
+    </row>
+    <row r="253" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H253" s="39"/>
+      <c r="I253" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="J253" s="49"/>
+      <c r="K253" s="49"/>
+      <c r="L253" s="37"/>
+      <c r="M253" s="37"/>
+      <c r="N253" s="38"/>
+      <c r="O253" s="41"/>
+      <c r="P253" s="41"/>
+      <c r="Q253" s="41"/>
+      <c r="R253" s="41"/>
+      <c r="S253" s="41"/>
+      <c r="T253" s="41"/>
+      <c r="U253" s="41"/>
+      <c r="V253" s="41"/>
+      <c r="W253" s="41"/>
+      <c r="X253" s="41"/>
+      <c r="Y253" s="41"/>
+      <c r="Z253" s="41"/>
+      <c r="AA253" s="41"/>
+      <c r="AB253" s="41"/>
+      <c r="AC253" s="42"/>
+    </row>
+    <row r="254" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H254" s="39"/>
+      <c r="I254" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="J254" s="41"/>
+      <c r="K254" s="41"/>
+      <c r="L254" s="41"/>
+      <c r="M254" s="41"/>
+      <c r="N254" s="42"/>
+      <c r="O254" s="41"/>
+      <c r="P254" s="41"/>
+      <c r="Q254" s="41"/>
+      <c r="R254" s="41"/>
+      <c r="S254" s="41"/>
+      <c r="T254" s="41"/>
+      <c r="U254" s="41"/>
+      <c r="V254" s="41"/>
+      <c r="W254" s="41"/>
+      <c r="X254" s="41"/>
+      <c r="Y254" s="41"/>
+      <c r="Z254" s="41"/>
+      <c r="AA254" s="41"/>
+      <c r="AB254" s="41"/>
+      <c r="AC254" s="42"/>
+    </row>
+    <row r="255" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H255" s="39"/>
+      <c r="I255" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="J255" s="41"/>
+      <c r="K255" s="41"/>
+      <c r="L255" s="41"/>
+      <c r="M255" s="41"/>
+      <c r="N255" s="42"/>
+      <c r="O255" s="41"/>
+      <c r="P255" s="41"/>
+      <c r="Q255" s="41"/>
+      <c r="R255" s="41"/>
+      <c r="S255" s="41"/>
+      <c r="T255" s="41"/>
+      <c r="U255" s="41"/>
+      <c r="V255" s="41"/>
+      <c r="W255" s="41"/>
+      <c r="X255" s="41"/>
+      <c r="Y255" s="41"/>
+      <c r="Z255" s="41"/>
+      <c r="AA255" s="41"/>
+      <c r="AB255" s="41"/>
+      <c r="AC255" s="42"/>
+    </row>
+    <row r="256" spans="8:29" x14ac:dyDescent="0.15">
+      <c r="H256" s="39"/>
+      <c r="I256" s="39"/>
+      <c r="J256" s="41"/>
+      <c r="K256" s="41"/>
+      <c r="L256" s="41"/>
+      <c r="M256" s="41"/>
+      <c r="N256" s="42"/>
+      <c r="O256" s="41"/>
+      <c r="P256" s="41"/>
+      <c r="Q256" s="41"/>
+      <c r="R256" s="41"/>
+      <c r="S256" s="41"/>
+      <c r="T256" s="41"/>
+      <c r="U256" s="41"/>
+      <c r="V256" s="41"/>
+      <c r="W256" s="41"/>
+      <c r="X256" s="41"/>
+      <c r="Y256" s="41"/>
+      <c r="Z256" s="41"/>
+      <c r="AA256" s="41"/>
+      <c r="AB256" s="41"/>
+      <c r="AC256" s="42"/>
+    </row>
+    <row r="257" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H257" s="39"/>
+      <c r="I257" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="J257" s="47"/>
+      <c r="K257" s="47"/>
+      <c r="L257" s="41"/>
+      <c r="M257" s="41"/>
+      <c r="N257" s="42"/>
+      <c r="O257" s="41"/>
+      <c r="P257" s="41"/>
+      <c r="Q257" s="41"/>
+      <c r="R257" s="41"/>
+      <c r="S257" s="41"/>
+      <c r="T257" s="41"/>
+      <c r="U257" s="41"/>
+      <c r="V257" s="41"/>
+      <c r="W257" s="41"/>
+      <c r="X257" s="41"/>
+      <c r="Y257" s="41"/>
+      <c r="Z257" s="41"/>
+      <c r="AA257" s="41"/>
+      <c r="AB257" s="41"/>
+      <c r="AC257" s="42"/>
+    </row>
+    <row r="258" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H258" s="39"/>
+      <c r="I258" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="J258" s="41"/>
+      <c r="K258" s="41"/>
+      <c r="L258" s="41"/>
+      <c r="M258" s="41"/>
+      <c r="N258" s="42"/>
+      <c r="O258" s="41"/>
+      <c r="P258" s="41"/>
+      <c r="Q258" s="41"/>
+      <c r="R258" s="41"/>
+      <c r="S258" s="41"/>
+      <c r="T258" s="41"/>
+      <c r="U258" s="41"/>
+      <c r="V258" s="41"/>
+      <c r="W258" s="41"/>
+      <c r="X258" s="41"/>
+      <c r="Y258" s="41"/>
+      <c r="Z258" s="41"/>
+      <c r="AA258" s="41"/>
+      <c r="AB258" s="41"/>
+      <c r="AC258" s="42"/>
+    </row>
+    <row r="259" spans="2:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="H259" s="39"/>
+      <c r="I259" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J259" s="44"/>
+      <c r="K259" s="44"/>
+      <c r="L259" s="44"/>
+      <c r="M259" s="44"/>
+      <c r="N259" s="45"/>
+      <c r="O259" s="41"/>
+      <c r="P259" s="41"/>
+      <c r="Q259" s="41"/>
+      <c r="R259" s="41"/>
+      <c r="S259" s="41"/>
+      <c r="T259" s="41"/>
+      <c r="U259" s="41"/>
+      <c r="V259" s="41"/>
+      <c r="W259" s="41"/>
+      <c r="X259" s="41"/>
+      <c r="Y259" s="41"/>
+      <c r="Z259" s="41"/>
+      <c r="AA259" s="41"/>
+      <c r="AB259" s="41"/>
+      <c r="AC259" s="42"/>
+    </row>
+    <row r="260" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H260" s="39"/>
+      <c r="I260" s="41"/>
+      <c r="J260" s="41"/>
+      <c r="K260" s="41"/>
+      <c r="L260" s="41"/>
+      <c r="M260" s="41"/>
+      <c r="N260" s="41"/>
+      <c r="O260" s="41"/>
+      <c r="P260" s="41"/>
+      <c r="Q260" s="41"/>
+      <c r="R260" s="41"/>
+      <c r="S260" s="41"/>
+      <c r="T260" s="41"/>
+      <c r="U260" s="41"/>
+      <c r="V260" s="41"/>
+      <c r="W260" s="41"/>
+      <c r="X260" s="41"/>
+      <c r="Y260" s="41"/>
+      <c r="Z260" s="41"/>
+      <c r="AA260" s="41"/>
+      <c r="AB260" s="41"/>
+      <c r="AC260" s="42"/>
+    </row>
+    <row r="261" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H261" s="39"/>
+      <c r="I261" s="41"/>
+      <c r="J261" s="41"/>
+      <c r="K261" s="41"/>
+      <c r="L261" s="41"/>
+      <c r="M261" s="41"/>
+      <c r="N261" s="41"/>
+      <c r="O261" s="41"/>
+      <c r="P261" s="41"/>
+      <c r="Q261" s="41"/>
+      <c r="R261" s="41"/>
+      <c r="S261" s="41"/>
+      <c r="T261" s="41"/>
+      <c r="U261" s="41"/>
+      <c r="V261" s="41"/>
+      <c r="W261" s="41"/>
+      <c r="X261" s="41"/>
+      <c r="Y261" s="41"/>
+      <c r="Z261" s="41"/>
+      <c r="AA261" s="41"/>
+      <c r="AB261" s="41"/>
+      <c r="AC261" s="42"/>
+    </row>
+    <row r="262" spans="2:29" ht="24" x14ac:dyDescent="0.25">
+      <c r="B262" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="C262" s="35"/>
-      <c r="D262" s="35"/>
-      <c r="E262" s="35"/>
-      <c r="F262" s="35"/>
-      <c r="G262" s="35"/>
-      <c r="H262" s="35"/>
-      <c r="I262" s="35"/>
-      <c r="J262" s="35"/>
-      <c r="K262" s="35"/>
-      <c r="L262" s="35"/>
-    </row>
-    <row r="264" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C262" s="34"/>
+      <c r="D262" s="34"/>
+      <c r="E262" s="34"/>
+      <c r="F262" s="34"/>
+      <c r="G262" s="34"/>
+      <c r="H262" s="53"/>
+      <c r="I262" s="54"/>
+      <c r="J262" s="54"/>
+      <c r="K262" s="54"/>
+      <c r="L262" s="54"/>
+      <c r="M262" s="41"/>
+      <c r="N262" s="41"/>
+      <c r="O262" s="41"/>
+      <c r="P262" s="41"/>
+      <c r="Q262" s="41"/>
+      <c r="R262" s="41"/>
+      <c r="S262" s="41"/>
+      <c r="T262" s="41"/>
+      <c r="U262" s="41"/>
+      <c r="V262" s="41"/>
+      <c r="W262" s="41"/>
+      <c r="X262" s="41"/>
+      <c r="Y262" s="41"/>
+      <c r="Z262" s="41"/>
+      <c r="AA262" s="41"/>
+      <c r="AB262" s="41"/>
+      <c r="AC262" s="42"/>
+    </row>
+    <row r="263" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H263" s="39"/>
+      <c r="I263" s="41"/>
+      <c r="J263" s="41"/>
+      <c r="K263" s="41"/>
+      <c r="L263" s="41"/>
+      <c r="M263" s="41"/>
+      <c r="N263" s="41"/>
+      <c r="O263" s="41"/>
+      <c r="P263" s="41"/>
+      <c r="Q263" s="41"/>
+      <c r="R263" s="41"/>
+      <c r="S263" s="41"/>
+      <c r="T263" s="41"/>
+      <c r="U263" s="41"/>
+      <c r="V263" s="41"/>
+      <c r="W263" s="41"/>
+      <c r="X263" s="41"/>
+      <c r="Y263" s="41"/>
+      <c r="Z263" s="41"/>
+      <c r="AA263" s="41"/>
+      <c r="AB263" s="41"/>
+      <c r="AC263" s="42"/>
+    </row>
+    <row r="264" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B264" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="265" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H264" s="39"/>
+      <c r="I264" s="41"/>
+      <c r="J264" s="41"/>
+      <c r="K264" s="41"/>
+      <c r="L264" s="41"/>
+      <c r="M264" s="41"/>
+      <c r="N264" s="41"/>
+      <c r="O264" s="41"/>
+      <c r="P264" s="41"/>
+      <c r="Q264" s="41"/>
+      <c r="R264" s="41"/>
+      <c r="S264" s="41"/>
+      <c r="T264" s="41"/>
+      <c r="U264" s="41"/>
+      <c r="V264" s="41"/>
+      <c r="W264" s="41"/>
+      <c r="X264" s="41"/>
+      <c r="Y264" s="41"/>
+      <c r="Z264" s="41"/>
+      <c r="AA264" s="41"/>
+      <c r="AB264" s="41"/>
+      <c r="AC264" s="42"/>
+    </row>
+    <row r="265" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B265" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="268" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H265" s="39"/>
+      <c r="I265" s="41"/>
+      <c r="J265" s="41"/>
+      <c r="K265" s="41"/>
+      <c r="L265" s="41"/>
+      <c r="M265" s="41"/>
+      <c r="N265" s="41"/>
+      <c r="O265" s="41"/>
+      <c r="P265" s="41"/>
+      <c r="Q265" s="41"/>
+      <c r="R265" s="41"/>
+      <c r="S265" s="41"/>
+      <c r="T265" s="41"/>
+      <c r="U265" s="41"/>
+      <c r="V265" s="41"/>
+      <c r="W265" s="41"/>
+      <c r="X265" s="41"/>
+      <c r="Y265" s="41"/>
+      <c r="Z265" s="41"/>
+      <c r="AA265" s="41"/>
+      <c r="AB265" s="41"/>
+      <c r="AC265" s="42"/>
+    </row>
+    <row r="266" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H266" s="39"/>
+      <c r="I266" s="41"/>
+      <c r="J266" s="41"/>
+      <c r="K266" s="41"/>
+      <c r="L266" s="41"/>
+      <c r="M266" s="41"/>
+      <c r="N266" s="41"/>
+      <c r="O266" s="41"/>
+      <c r="P266" s="41"/>
+      <c r="Q266" s="41"/>
+      <c r="R266" s="41"/>
+      <c r="S266" s="41"/>
+      <c r="T266" s="41"/>
+      <c r="U266" s="41"/>
+      <c r="V266" s="41"/>
+      <c r="W266" s="41"/>
+      <c r="X266" s="41"/>
+      <c r="Y266" s="41"/>
+      <c r="Z266" s="41"/>
+      <c r="AA266" s="41"/>
+      <c r="AB266" s="41"/>
+      <c r="AC266" s="42"/>
+    </row>
+    <row r="267" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H267" s="39"/>
+      <c r="I267" s="41"/>
+      <c r="J267" s="41"/>
+      <c r="K267" s="41"/>
+      <c r="L267" s="41"/>
+      <c r="M267" s="41"/>
+      <c r="N267" s="41"/>
+      <c r="O267" s="41"/>
+      <c r="P267" s="41"/>
+      <c r="Q267" s="41"/>
+      <c r="R267" s="41"/>
+      <c r="S267" s="41"/>
+      <c r="T267" s="41"/>
+      <c r="U267" s="41"/>
+      <c r="V267" s="41"/>
+      <c r="W267" s="41"/>
+      <c r="X267" s="41"/>
+      <c r="Y267" s="41"/>
+      <c r="Z267" s="41"/>
+      <c r="AA267" s="41"/>
+      <c r="AB267" s="41"/>
+      <c r="AC267" s="42"/>
+    </row>
+    <row r="268" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B268" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="269" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H268" s="39"/>
+      <c r="I268" s="41"/>
+      <c r="J268" s="41"/>
+      <c r="K268" s="41"/>
+      <c r="L268" s="41"/>
+      <c r="M268" s="41"/>
+      <c r="N268" s="41"/>
+      <c r="O268" s="41"/>
+      <c r="P268" s="41"/>
+      <c r="Q268" s="41"/>
+      <c r="R268" s="41"/>
+      <c r="S268" s="41"/>
+      <c r="T268" s="41"/>
+      <c r="U268" s="41"/>
+      <c r="V268" s="41"/>
+      <c r="W268" s="41"/>
+      <c r="X268" s="41"/>
+      <c r="Y268" s="41"/>
+      <c r="Z268" s="41"/>
+      <c r="AA268" s="41"/>
+      <c r="AB268" s="41"/>
+      <c r="AC268" s="42"/>
+    </row>
+    <row r="269" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B269" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="270" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H269" s="39"/>
+      <c r="I269" s="41"/>
+      <c r="J269" s="41"/>
+      <c r="K269" s="41"/>
+      <c r="L269" s="41"/>
+      <c r="M269" s="41"/>
+      <c r="N269" s="41"/>
+      <c r="O269" s="41"/>
+      <c r="P269" s="41"/>
+      <c r="Q269" s="41"/>
+      <c r="R269" s="41"/>
+      <c r="S269" s="41"/>
+      <c r="T269" s="41"/>
+      <c r="U269" s="41"/>
+      <c r="V269" s="41"/>
+      <c r="W269" s="41"/>
+      <c r="X269" s="41"/>
+      <c r="Y269" s="41"/>
+      <c r="Z269" s="41"/>
+      <c r="AA269" s="41"/>
+      <c r="AB269" s="41"/>
+      <c r="AC269" s="42"/>
+    </row>
+    <row r="270" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B270" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="271" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H270" s="39"/>
+      <c r="I270" s="41"/>
+      <c r="J270" s="41"/>
+      <c r="K270" s="41"/>
+      <c r="L270" s="41"/>
+      <c r="M270" s="41"/>
+      <c r="N270" s="41"/>
+      <c r="O270" s="41"/>
+      <c r="P270" s="41"/>
+      <c r="Q270" s="41"/>
+      <c r="R270" s="41"/>
+      <c r="S270" s="41"/>
+      <c r="T270" s="41"/>
+      <c r="U270" s="41"/>
+      <c r="V270" s="41"/>
+      <c r="W270" s="41"/>
+      <c r="X270" s="41"/>
+      <c r="Y270" s="41"/>
+      <c r="Z270" s="41"/>
+      <c r="AA270" s="41"/>
+      <c r="AB270" s="41"/>
+      <c r="AC270" s="42"/>
+    </row>
+    <row r="271" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B271" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="275" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="H271" s="39"/>
+      <c r="I271" s="41"/>
+      <c r="J271" s="41"/>
+      <c r="K271" s="41"/>
+      <c r="L271" s="41"/>
+      <c r="M271" s="41"/>
+      <c r="N271" s="41"/>
+      <c r="O271" s="41"/>
+      <c r="P271" s="41"/>
+      <c r="Q271" s="41"/>
+      <c r="R271" s="41"/>
+      <c r="S271" s="41"/>
+      <c r="T271" s="41"/>
+      <c r="U271" s="41"/>
+      <c r="V271" s="41"/>
+      <c r="W271" s="41"/>
+      <c r="X271" s="41"/>
+      <c r="Y271" s="41"/>
+      <c r="Z271" s="41"/>
+      <c r="AA271" s="41"/>
+      <c r="AB271" s="41"/>
+      <c r="AC271" s="42"/>
+    </row>
+    <row r="272" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H272" s="39"/>
+      <c r="I272" s="41"/>
+      <c r="J272" s="41"/>
+      <c r="K272" s="41"/>
+      <c r="L272" s="41"/>
+      <c r="M272" s="41"/>
+      <c r="N272" s="41"/>
+      <c r="O272" s="41"/>
+      <c r="P272" s="41"/>
+      <c r="Q272" s="41"/>
+      <c r="R272" s="41"/>
+      <c r="S272" s="41"/>
+      <c r="T272" s="41"/>
+      <c r="U272" s="41"/>
+      <c r="V272" s="41"/>
+      <c r="W272" s="41"/>
+      <c r="X272" s="41"/>
+      <c r="Y272" s="41"/>
+      <c r="Z272" s="41"/>
+      <c r="AA272" s="41"/>
+      <c r="AB272" s="41"/>
+      <c r="AC272" s="42"/>
+    </row>
+    <row r="273" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H273" s="39"/>
+      <c r="I273" s="41"/>
+      <c r="J273" s="41"/>
+      <c r="K273" s="41"/>
+      <c r="L273" s="41"/>
+      <c r="M273" s="41"/>
+      <c r="N273" s="41"/>
+      <c r="O273" s="41"/>
+      <c r="P273" s="41"/>
+      <c r="Q273" s="41"/>
+      <c r="R273" s="41"/>
+      <c r="S273" s="41"/>
+      <c r="T273" s="41"/>
+      <c r="U273" s="41"/>
+      <c r="V273" s="41"/>
+      <c r="W273" s="41"/>
+      <c r="X273" s="41"/>
+      <c r="Y273" s="41"/>
+      <c r="Z273" s="41"/>
+      <c r="AA273" s="41"/>
+      <c r="AB273" s="41"/>
+      <c r="AC273" s="42"/>
+    </row>
+    <row r="274" spans="2:29" x14ac:dyDescent="0.15">
+      <c r="H274" s="39"/>
+      <c r="I274" s="41"/>
+      <c r="J274" s="41"/>
+      <c r="K274" s="41"/>
+      <c r="L274" s="41"/>
+      <c r="M274" s="41"/>
+      <c r="N274" s="41"/>
+      <c r="O274" s="41"/>
+      <c r="P274" s="41"/>
+      <c r="Q274" s="41"/>
+      <c r="R274" s="41"/>
+      <c r="S274" s="41"/>
+      <c r="T274" s="41"/>
+      <c r="U274" s="41"/>
+      <c r="V274" s="41"/>
+      <c r="W274" s="41"/>
+      <c r="X274" s="41"/>
+      <c r="Y274" s="41"/>
+      <c r="Z274" s="41"/>
+      <c r="AA274" s="41"/>
+      <c r="AB274" s="41"/>
+      <c r="AC274" s="42"/>
+    </row>
+    <row r="275" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B275" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="276" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="H275" s="39"/>
+      <c r="I275" s="41"/>
+      <c r="J275" s="41"/>
+      <c r="K275" s="41"/>
+      <c r="L275" s="41"/>
+      <c r="M275" s="41"/>
+      <c r="N275" s="41"/>
+      <c r="O275" s="41"/>
+      <c r="P275" s="41"/>
+      <c r="Q275" s="41"/>
+      <c r="R275" s="41"/>
+      <c r="S275" s="41"/>
+      <c r="T275" s="41"/>
+      <c r="U275" s="41"/>
+      <c r="V275" s="41"/>
+      <c r="W275" s="41"/>
+      <c r="X275" s="41"/>
+      <c r="Y275" s="41"/>
+      <c r="Z275" s="41"/>
+      <c r="AA275" s="41"/>
+      <c r="AB275" s="41"/>
+      <c r="AC275" s="42"/>
+    </row>
+    <row r="276" spans="2:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B276" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="278" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="H276" s="43"/>
+      <c r="I276" s="44"/>
+      <c r="J276" s="44"/>
+      <c r="K276" s="44"/>
+      <c r="L276" s="44"/>
+      <c r="M276" s="44"/>
+      <c r="N276" s="44"/>
+      <c r="O276" s="44"/>
+      <c r="P276" s="44"/>
+      <c r="Q276" s="44"/>
+      <c r="R276" s="44"/>
+      <c r="S276" s="44"/>
+      <c r="T276" s="44"/>
+      <c r="U276" s="44"/>
+      <c r="V276" s="44"/>
+      <c r="W276" s="44"/>
+      <c r="X276" s="44"/>
+      <c r="Y276" s="44"/>
+      <c r="Z276" s="44"/>
+      <c r="AA276" s="44"/>
+      <c r="AB276" s="44"/>
+      <c r="AC276" s="45"/>
+    </row>
+    <row r="278" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B278" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="280" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="280" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B280" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="281" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="281" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B281" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="283" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="283" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B283" t="s">
         <v>131</v>
       </c>
@@ -4805,6 +7180,7 @@
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/各種資料/contact 7().xlsx
+++ b/各種資料/contact 7().xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\50_knowledge\各種資料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guest04\Desktop\高橋研三\03_knowledge\各種資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D287BA-513D-43CC-9C95-29493686ACAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2CC9A7-CA51-469E-8D60-7A8E136B6F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4785" yWindow="540" windowWidth="20490" windowHeight="14505" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47610" yWindow="0" windowWidth="18030" windowHeight="16305" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="① インストール" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="178">
   <si>
     <t>① インストール</t>
   </si>
@@ -68,9 +68,6 @@
     <t xml:space="preserve">        &lt;!-- &lt;form action=""&gt; --&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">        &lt;?php echo do_shortcode('[contact-form-7 id="XXX"]') ?&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">      &lt;/div&gt;</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
   </si>
   <si>
     <t>if (is_page('contact')) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    wp_enqueue_style('contact7', get_template_directory_uri() . '/css/contact7.css');</t>
   </si>
   <si>
     <t>}</t>
@@ -121,16 +115,7 @@
     <t>// functions.php</t>
   </si>
   <si>
-    <t>function my_theme_setup()</t>
-  </si>
-  <si>
     <t>{</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  add_theme_support('post-thumbnails'); // アイキャッチ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  add_theme_support('menus');          // メニュー機能を有効化</t>
   </si>
   <si>
     <t>]</t>
@@ -1126,6 +1111,206 @@
     <phoneticPr fontId="9"/>
   </si>
   <si>
+    <t>メニューから追加可能</t>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t xml:space="preserve">newtesthome.local / works / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    ↑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">             投稿タイプのスラッグ（CPT UIで設定）</t>
+  </si>
+  <si>
+    <t>newtesthome.local / works-category / web-design /</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    ↑                ↑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              タクソノミーのスラッグ   タームのスラッグ</t>
+  </si>
+  <si>
+    <t>アクセルURL</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t xml:space="preserve">              （CPT UIで設定）        （CPT UIで追加した、投稿タイプメニューのタクソノミーから追加）</t>
+    <rPh sb="41" eb="43">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>トウコウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>① 投稿タイプの一覧ページ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → 制作実績の記事が全部並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → テンプレート: archive-works.php</t>
+  </si>
+  <si>
+    <t>② タクソノミーのアーカイブページ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → 特定のタームで絞り込んだ記事が並ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → テンプレート: taxonomy-works-category.php</t>
+  </si>
+  <si>
+    <t>表示したいページは２種類</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>スラッグが必要なのは、CPT UIで作成したもの。　</t>
+    <rPh sb="5" eb="7">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>作成するファイルは　カスタム投稿タイプが「制作実績」（スラッグ名・works3）ならば、アーカイブは archive-works3.php となる。</t>
+    <rPh sb="0" eb="2">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>➡</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>これはあとでもいい。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>大事</t>
+    <rPh sb="0" eb="2">
+      <t>ダイジ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>要約</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウヤク</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>カスタム投稿タイプとカスタム投稿タクソノミーがあります。</t>
+  </si>
+  <si>
+    <t>タクソノミーはカスタム投稿タイプの下に分類される、付属のタグのようなものです。それぞれを登録すると管理画面にメニューが表示されるので、そこからタクソノミーのさらに詳しい「ターム」を追加したり、投稿タイプから複数の記事を追加したりできます。</t>
+  </si>
+  <si>
+    <t>表示については、以下のいずれかを選択可能です：</t>
+  </si>
+  <si>
+    <t>1. 作成したカスタム投稿タイプの一覧</t>
+  </si>
+  <si>
+    <t>2. タクソノミーの各タームの一覧</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        &lt;?php echo do_shortcode('[contact-form-7 id="XXX"]') ?&gt;</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>// page-contact.php</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>・CSSを充てるために、function.phpに設定する</t>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>【要するに】</t>
+    <rPh sb="1" eb="2">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>・作成するファイル（page-contact.php）に&lt;?php echo do_shortcode('[contact-form-7 id="XXX"]') ?&gt;をセット</t>
+    <rPh sb="1" eb="3">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    wp_enqueue_style('contact7', get_template_directory_uri() . '/css/contact7.css');</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>function my_theme_setup()</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  add_theme_support('menus');          // </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6A9955"/>
+        <rFont val="ＭＳ 明朝"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>メニュー機能を有効化</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  add_theme_support('post-thumbnails'); // </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF6A9955"/>
+        <rFont val="ＭＳ 明朝"/>
+        <family val="1"/>
+        <charset val="128"/>
+      </rPr>
+      <t>アイキャッチ</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1146,7 +1331,28 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>（ターム　制作実績３のメニュー）</t>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ターム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>　制作実績３のメニュー）</t>
     </r>
     <rPh sb="13" eb="15">
       <t>セイサク</t>
@@ -1157,131 +1363,80 @@
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>メニューから追加可能</t>
+    <t>★スラッグをつくるもの</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>・投稿タイプ（制作実績などのメニュー）　その↓につく制作実績じょ一覧はスラッグはない</t>
+    <rPh sb="1" eb="3">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>・タクソノミーのスラッグ（例えばタグとか）</t>
+    <rPh sb="13" eb="14">
+      <t>タト</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>※共通事項。どちらもCPTのメニューで作成するもの</t>
+    <rPh sb="1" eb="3">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジコウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>★ファイルを作成する際の、カスタム投稿タイプ作成時のスラッグ名。例）archive-work.php(なお気を付けるのはコンタクトページはpage-contact.ph)</t>
     <rPh sb="6" eb="8">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カノウ</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t xml:space="preserve">newtesthome.local / works / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                    ↑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">             投稿タイプのスラッグ（CPT UIで設定）</t>
-  </si>
-  <si>
-    <t>newtesthome.local / works-category / web-design /</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                    ↑                ↑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">              タクソノミーのスラッグ   タームのスラッグ</t>
-  </si>
-  <si>
-    <t>アクセルURL</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t xml:space="preserve">              （CPT UIで設定）        （CPT UIで追加した、投稿タイプメニューのタクソノミーから追加）</t>
-    <rPh sb="41" eb="43">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
       <t>トウコウ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>① 投稿タイプの一覧ページ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   → 制作実績の記事が全部並ぶ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   → テンプレート: archive-works.php</t>
-  </si>
-  <si>
-    <t>② タクソノミーのアーカイブページ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   → 特定のタームで絞り込んだ記事が並ぶ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   → テンプレート: taxonomy-works-category.php</t>
-  </si>
-  <si>
-    <t>表示したいページは２種類</t>
-    <rPh sb="0" eb="2">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シュルイ</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>スラッグが必要なのは、CPT UIで作成したもの。　</t>
-    <rPh sb="5" eb="7">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
+    <rPh sb="22" eb="24">
       <t>サクセイ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>作成するファイルは　カスタム投稿タイプが「制作実績」（スラッグ名・works3）ならば、アーカイブは archive-works3.php となる。</t>
-    <rPh sb="0" eb="2">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
+    <rPh sb="24" eb="25">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>➡</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>これはあとでもいい。</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>大事</t>
-    <rPh sb="0" eb="2">
-      <t>ダイジ</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>要約</t>
-    <rPh sb="0" eb="2">
-      <t>ヨウヤク</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>カスタム投稿タイプとカスタム投稿タクソノミーがあります。</t>
-  </si>
-  <si>
-    <t>タクソノミーはカスタム投稿タイプの下に分類される、付属のタグのようなものです。それぞれを登録すると管理画面にメニューが表示されるので、そこからタクソノミーのさらに詳しい「ターム」を追加したり、投稿タイプから複数の記事を追加したりできます。</t>
-  </si>
-  <si>
-    <t>表示については、以下のいずれかを選択可能です：</t>
-  </si>
-  <si>
-    <t>1. 作成したカスタム投稿タイプの一覧</t>
-  </si>
-  <si>
-    <t>2. タクソノミーの各タームの一覧</t>
+    <rPh sb="32" eb="33">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ツ</t>
+    </rPh>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -1289,7 +1444,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1516,6 +1671,19 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6A9955"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6A9955"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -1702,7 +1870,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1725,9 +1893,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
@@ -1769,22 +1934,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1804,6 +1968,202 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB8AA22B-0846-DFA2-C18C-A3DE7C85F948}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6391275" y="1600200"/>
+          <a:ext cx="5638800" cy="4343400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>要するに</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・作成するファイル（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>page-contact.php</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>）に</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>　　　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>&lt;?php echo do_shortcode('[contact-form-7 id="XXX"]') ?&gt;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>をセット</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>CSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>とひもづけるために、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>function.php</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>に</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>wp_enqueue_style('contact7', get_template_directory_uri() . '/css/contact7.css');</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>を追加</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -2070,10 +2430,828 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EF465A5-E552-466D-81D4-9E1D0A818CFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4857750" y="3016250"/>
+          <a:ext cx="5638800" cy="4756150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>要するに</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>】</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>➀作成するファイル（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>page-contact.php</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>）に</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>　　　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>&lt;?php echo do_shortcode('[contact-form-7 id="XXX"]') ?&gt;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>をセット</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>contact</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+            <a:t> form 7</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>を有効化する（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+            <a:t>function</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>。</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+            <a:t>PHP</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>）→</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>　　　　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>function my_theme_setup()</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>メソッドを追加→設定後管理画面を読み込む</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>　　　　→外観メニューに表示</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>→嘘！！</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>これは調べたところ関係ない</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>WordPress</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>に向かって**「このテーマはこれを使いますよ」と宣言している**だけです。これがないと</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>post-thumbnails</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>とか全体に表示されない</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> add_theme_support('menus');          </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>➡　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>/</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>「メニュー機能を有効化なのでこれは必要（ただし、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>contact form7</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>にかぎらず全体的に必要</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>）</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>➁管理画面にメニューを追加する（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+            <a:t>function.php</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>）</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+            <a:t>            </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>  register_nav_menus(array(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    'header-menu' =&gt; '</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ヘッダーメニュー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1',</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>));</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> を追加</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:effectLst/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>　　　　　→ここでメニューに追加される。</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:effectLst/>
+            </a:rPr>
+          </a:br>
+          <a:br>
+            <a:rPr lang="en-US" altLang="ja-JP">
+              <a:effectLst/>
+            </a:rPr>
+          </a:br>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>外観メニュー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>】</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:effectLst/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>メニュー項目を追加していく。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>・お問い合わせの・コンタクトフォームなどから、外観をセットできる</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>CSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>とひもづけるために、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>function.php</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>に</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>wp_enqueue_style('contact7', get_template_directory_uri() . '/css/contact7.css');</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>を追加</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+            <a:t>            </a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>　　　　　　　</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" baseline="0"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" baseline="0"/>
+            <a:t>　　　　</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>CSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>とひもづけるために、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>function.php</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>に</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>wp_enqueue_style('contact7', get_template_directory_uri() . '/css/contact7.css');</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>を追加</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -2115,7 +3293,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2252,7 +3430,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2814,7 +3992,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3073,7 +4251,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3683,16 +4861,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>204</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>203</xdr:row>
+      <xdr:rowOff>161924</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>220</xdr:row>
-      <xdr:rowOff>43455</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>345648</xdr:colOff>
+      <xdr:row>223</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3715,8 +4893,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6238875" y="35509200"/>
-          <a:ext cx="4905375" cy="2786655"/>
+          <a:off x="5600699" y="33870899"/>
+          <a:ext cx="5222449" cy="3152775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3728,15 +4906,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>250</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>104776</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>189619</xdr:colOff>
-      <xdr:row>274</xdr:row>
-      <xdr:rowOff>47086</xdr:rowOff>
+      <xdr:colOff>246769</xdr:colOff>
+      <xdr:row>269</xdr:row>
+      <xdr:rowOff>111126</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3759,14 +4937,577 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11039475" y="43462575"/>
-          <a:ext cx="7047619" cy="4314286"/>
+          <a:off x="9925050" y="41500426"/>
+          <a:ext cx="6285619" cy="3235325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF">
+            <a:shade val="85000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="88900" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="55000" dist="18000" dir="5400000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="40000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:scene3d>
+          <a:camera prst="orthographicFront"/>
+          <a:lightRig rig="twoPt" dir="t">
+            <a:rot lat="0" lon="0" rev="7200000"/>
+          </a:lightRig>
+        </a:scene3d>
+        <a:sp3d>
+          <a:bevelT w="25400" h="19050"/>
+          <a:contourClr>
+            <a:srgbClr val="FFFFFF"/>
+          </a:contourClr>
+        </a:sp3d>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>238</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>251</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="直線矢印コネクタ 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7B21F8A-C2BB-A874-E5C5-32FF0A4F0DD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="11420475" y="39490650"/>
+          <a:ext cx="1571625" cy="2209800"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>237</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>245</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FF18910-74AC-5B76-40A3-6D580CA0CF4E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12211050" y="39300150"/>
+          <a:ext cx="1638300" cy="1314450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>いわゆる、投稿タイプの一覧が入る「箱」みたいなもの　</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・それで記事</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>A</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>とか記事</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>B</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>とか記事</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>C</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>とかセットされる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>237</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>123824</xdr:colOff>
+      <xdr:row>245</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="正方形/長方形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E28C310-7650-4F48-97F7-6EB9E055DB87}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14744699" y="39281100"/>
+          <a:ext cx="1952625" cy="1314450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>つまりその記事一覧がタームを結びつけることによってどんな投稿タイプがわかるってことね。　</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・名前（個別の記事）だけでも予想できるけどタームがあることで、さらに予想がつく</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>267</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>275</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="正方形/長方形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55D04643-3AF7-4D28-B22D-F8D839A0305C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6534150" y="44338875"/>
+          <a:ext cx="2825750" cy="1314450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>それぞれの、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>個別記事を</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>を取得するのは「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>get_the_ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>」を</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>（なおループでするのが前提）</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>**</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>【</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>コード例</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>】**</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100" b="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>```php</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>while ( have_posts() ) : the_post();</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    // get_the_ID() </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>は自動でその記事の</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ID</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>になる</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>$terms = get_the_terms( get_the_ID(), 'works-category' );</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>endwhile;</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>```</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4061,14 +5802,14 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K6"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4082,8 +5823,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
@@ -4097,7 +5838,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -4111,7 +5852,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="6" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4123,8 +5864,8 @@
   <sheetPr>
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
-  <dimension ref="B1:P61"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="B1:T61"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
@@ -4132,8 +5873,8 @@
     <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:20" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -4147,8 +5888,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
@@ -4161,8 +5902,11 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="O4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
@@ -4175,20 +5919,28 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="8" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="24"/>
-    </row>
-    <row r="12" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O5" t="s">
+        <v>167</v>
+      </c>
+      <c r="T5" s="39"/>
+    </row>
+    <row r="6" spans="2:20" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="2:20" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="2:20" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="2:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="23"/>
+    </row>
+    <row r="12" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
@@ -4202,8 +5954,8 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>7</v>
       </c>
@@ -4217,7 +5969,7 @@
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
@@ -4231,8 +5983,8 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="17" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
@@ -4246,8 +5998,8 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="2:11" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:11" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -4261,7 +6013,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
@@ -4275,7 +6027,7 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>12</v>
       </c>
@@ -4289,9 +6041,9 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B22" s="3" t="s">
-        <v>13</v>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B22" s="18" t="s">
+        <v>163</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -4303,7 +6055,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -4315,9 +6067,9 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -4329,18 +6081,18 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="26" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="28" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -4352,10 +6104,10 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4367,10 +6119,10 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B34" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -4382,9 +6134,9 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B35" s="3" t="s">
-        <v>18</v>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B35" s="18" t="s">
+        <v>168</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -4396,9 +6148,9 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B36" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -4410,24 +6162,24 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="38" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="2:16" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -4444,11 +6196,12 @@
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
     </row>
-    <row r="61" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4458,17 +6211,17 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K83"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
     <col min="3" max="15" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4480,10 +6233,10 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="4" spans="2:11" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="2:11" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
@@ -4495,9 +6248,9 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -4509,9 +6262,9 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B6" s="3" t="s">
-        <v>30</v>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B6" s="18" t="s">
+        <v>169</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -4523,9 +6276,9 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -4537,9 +6290,9 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B8" s="11" t="s">
-        <v>32</v>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B8" s="51" t="s">
+        <v>171</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -4551,9 +6304,9 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B9" s="11" t="s">
-        <v>33</v>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B9" s="51" t="s">
+        <v>170</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -4565,9 +6318,9 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -4579,10 +6332,10 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="12" spans="2:11" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="13" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:11" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -4594,19 +6347,19 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="19" spans="2:11" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="B19" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="B21" s="18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" ht="19.5" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:11" ht="19" x14ac:dyDescent="0.3">
+      <c r="B19" s="19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="20" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -4618,9 +6371,9 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B24" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -4632,9 +6385,9 @@
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -4646,9 +6399,9 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B26" s="19" t="s">
-        <v>58</v>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B26" s="18" t="s">
+        <v>53</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -4660,9 +6413,9 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B27" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -4674,9 +6427,9 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B28" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -4688,9 +6441,9 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -4702,9 +6455,9 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="32" spans="2:11" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4716,44 +6469,44 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="36" spans="2:2" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B36" s="21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B38" s="17" t="s">
+    <row r="36" spans="2:2" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="B36" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B38" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B39" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B40" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B41" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B42" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" ht="23.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="21" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B39" s="17" t="s">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B83" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B40" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B41" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B42" s="17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" ht="23.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B83" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4769,17 +6522,17 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K16"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="13" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4791,22 +6544,22 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -4818,9 +6571,9 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -4832,7 +6585,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -4844,9 +6597,9 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -4858,9 +6611,9 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -4872,7 +6625,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -4884,9 +6637,9 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -4898,22 +6651,22 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="13" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B15" s="16" t="s">
-        <v>44</v>
+    <row r="13" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B15" s="15" t="s">
+        <v>39</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -4925,7 +6678,7 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="16" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4939,29 +6692,29 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B3:E38"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B3" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B3" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.15">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -4974,47 +6727,47 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E4DE1B-CEE6-4D06-B682-4A9E3F05719A}">
   <dimension ref="B2:P147"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.15">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="16:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="16:16" x14ac:dyDescent="0.2">
+      <c r="P38" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="16:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" spans="16:16" x14ac:dyDescent="0.15">
-      <c r="P38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="16:16" x14ac:dyDescent="0.15">
+    <row r="39" spans="16:16" x14ac:dyDescent="0.2">
       <c r="P39" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.15">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="147" spans="16:16" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="147" spans="16:16" x14ac:dyDescent="0.2">
       <c r="P147" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -5027,75 +6780,75 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A893AC6-FB79-450E-8D17-FE484C32412D}">
   <dimension ref="B2:L75"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" ht="19" x14ac:dyDescent="0.3">
+      <c r="B31" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="26"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B26" t="s">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B27" t="s">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="B31" s="26" t="s">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="27"/>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B32" t="s">
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B33" t="s">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="24" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B36" t="s">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B37" t="s">
+      <c r="E74" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B75" s="16" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="L44" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="L45" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="L47" s="25" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B74" t="s">
-        <v>79</v>
-      </c>
-      <c r="E74" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B75" s="17" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -5111,2070 +6864,955 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F487261-4C57-4DE5-9D5F-EC7B6550A8CC}">
   <dimension ref="B1:AC283"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.375" customWidth="1"/>
-    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B1" s="32" t="s">
+    <row r="1" spans="2:11" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="B1" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="K1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B4" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M17" s="50" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M22" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="23" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="N29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="N30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="N32" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="13:13" x14ac:dyDescent="0.2">
+      <c r="M34" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B50" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="36"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="36"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="36"/>
+      <c r="K50" s="36"/>
+      <c r="L50" s="36"/>
+      <c r="M50" s="37"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B51" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="M51" s="40"/>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B52" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="M52" s="40"/>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B53" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="M53" s="40"/>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B54" s="38"/>
+      <c r="M54" s="40"/>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B55" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="M55" s="40"/>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B56" s="38"/>
+      <c r="M56" s="40"/>
+    </row>
+    <row r="57" spans="2:15" ht="30" x14ac:dyDescent="0.4">
+      <c r="B57" s="38"/>
+      <c r="M57" s="40"/>
+      <c r="N57" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="O57" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B58" s="38"/>
+      <c r="M58" s="40"/>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B59" s="38"/>
+      <c r="M59" s="40"/>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B60" s="38"/>
+      <c r="M60" s="40"/>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B61" s="38"/>
+      <c r="M61" s="40"/>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B62" s="38"/>
+      <c r="M62" s="40"/>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B63" s="38"/>
+      <c r="M63" s="40"/>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B64" s="38"/>
+      <c r="M64" s="40"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B65" s="38"/>
+      <c r="M65" s="40"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B66" s="38"/>
+      <c r="M66" s="40"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B67" s="38"/>
+      <c r="M67" s="40"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B68" s="38"/>
+      <c r="M68" s="40"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B69" s="38"/>
+      <c r="M69" s="40"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B70" s="38"/>
+      <c r="M70" s="40"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B71" s="38"/>
+      <c r="M71" s="40"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B72" s="38"/>
+      <c r="M72" s="40"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B73" s="38"/>
+      <c r="M73" s="40"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B74" s="38"/>
+      <c r="M74" s="40"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B75" s="38"/>
+      <c r="M75" s="40"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B76" s="38"/>
+      <c r="M76" s="40"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B77" s="38"/>
+      <c r="M77" s="40"/>
+    </row>
+    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B78" s="38"/>
+      <c r="M78" s="40"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B79" s="38"/>
+      <c r="M79" s="40"/>
+    </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B80" s="38"/>
+      <c r="M80" s="40"/>
+    </row>
+    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B81" s="38"/>
+      <c r="M81" s="40"/>
+    </row>
+    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B82" s="38"/>
+      <c r="M82" s="40"/>
+    </row>
+    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B83" s="38"/>
+      <c r="M83" s="40"/>
+    </row>
+    <row r="84" spans="2:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="41"/>
+      <c r="C84" s="42"/>
+      <c r="D84" s="42"/>
+      <c r="E84" s="42"/>
+      <c r="F84" s="42"/>
+      <c r="G84" s="42"/>
+      <c r="H84" s="42"/>
+      <c r="I84" s="42"/>
+      <c r="J84" s="42"/>
+      <c r="K84" s="42"/>
+      <c r="L84" s="42"/>
+      <c r="M84" s="43"/>
+    </row>
+    <row r="89" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B89" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B90" s="16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="91" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B91" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="92" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B92" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B93" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B98" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B101" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B103" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C103" s="28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B104" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C104" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C105" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" ht="19" x14ac:dyDescent="0.3">
+      <c r="B114" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C114" s="26"/>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B115" t="s">
+        <v>98</v>
+      </c>
+      <c r="D115" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B118" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B131" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="154" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="J154" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="155" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="J155" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="158" spans="9:10" x14ac:dyDescent="0.2">
+      <c r="I158" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="173" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I173" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="175" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I175" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="176" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I176" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="178" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="I178" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="179" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="I179" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="181" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="I181" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="183" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="I183" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="184" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="I184" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="188" spans="2:17" ht="16" x14ac:dyDescent="0.45">
+      <c r="I188" s="34" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="189" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="I189" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="190" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B191" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="I191" s="35"/>
+      <c r="J191" s="36"/>
+      <c r="K191" s="36"/>
+      <c r="L191" s="36"/>
+      <c r="M191" s="36"/>
+      <c r="N191" s="36"/>
+      <c r="O191" s="36"/>
+      <c r="P191" s="36"/>
+      <c r="Q191" s="37"/>
+    </row>
+    <row r="192" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="I192" s="38"/>
+      <c r="J192" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q192" s="40"/>
+    </row>
+    <row r="193" spans="9:17" x14ac:dyDescent="0.2">
+      <c r="I193" s="38"/>
+      <c r="J193" t="s">
+        <v>132</v>
+      </c>
+      <c r="K193" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q193" s="40"/>
+    </row>
+    <row r="194" spans="9:17" x14ac:dyDescent="0.2">
+      <c r="I194" s="38"/>
+      <c r="K194" t="s">
+        <v>133</v>
+      </c>
+      <c r="L194" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q194" s="40"/>
+    </row>
+    <row r="195" spans="9:17" x14ac:dyDescent="0.2">
+      <c r="I195" s="38"/>
+      <c r="M195" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q195" s="40"/>
+    </row>
+    <row r="196" spans="9:17" x14ac:dyDescent="0.2">
+      <c r="I196" s="38"/>
+      <c r="Q196" s="40"/>
+    </row>
+    <row r="197" spans="9:17" x14ac:dyDescent="0.2">
+      <c r="I197" s="38"/>
+      <c r="Q197" s="40"/>
+    </row>
+    <row r="198" spans="9:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I198" s="41"/>
+      <c r="J198" s="42"/>
+      <c r="K198" s="42"/>
+      <c r="L198" s="42"/>
+      <c r="M198" s="42"/>
+      <c r="N198" s="42"/>
+      <c r="O198" s="42"/>
+      <c r="P198" s="42"/>
+      <c r="Q198" s="43"/>
+    </row>
+    <row r="202" spans="9:17" x14ac:dyDescent="0.2">
+      <c r="K202" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="203" spans="9:17" x14ac:dyDescent="0.2">
+      <c r="J203" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B221" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B223" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B224" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="226" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B226" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="227" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B227" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="229" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B229" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="230" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H230" s="16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="231" spans="2:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B231" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="232" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B232" t="s">
+        <v>108</v>
+      </c>
+      <c r="H232" s="35"/>
+      <c r="I232" s="36"/>
+      <c r="J232" s="36"/>
+      <c r="K232" s="36"/>
+      <c r="L232" s="36"/>
+      <c r="M232" s="36"/>
+      <c r="N232" s="36"/>
+      <c r="O232" s="36"/>
+      <c r="P232" s="36"/>
+      <c r="Q232" s="36"/>
+      <c r="R232" s="36"/>
+      <c r="S232" s="36"/>
+      <c r="T232" s="36"/>
+      <c r="U232" s="36"/>
+      <c r="V232" s="36"/>
+      <c r="W232" s="36"/>
+      <c r="X232" s="36"/>
+      <c r="Y232" s="36"/>
+      <c r="Z232" s="36"/>
+      <c r="AA232" s="36"/>
+      <c r="AB232" s="36"/>
+      <c r="AC232" s="37"/>
+    </row>
+    <row r="233" spans="2:29" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B233" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H233" s="38"/>
+      <c r="I233" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="J233" s="26"/>
+      <c r="AC233" s="40"/>
+    </row>
+    <row r="234" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B234" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="H234" s="38"/>
+      <c r="AC234" s="40"/>
+    </row>
+    <row r="235" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B235" t="s">
+        <v>91</v>
+      </c>
+      <c r="H235" s="38"/>
+      <c r="AC235" s="40"/>
+    </row>
+    <row r="236" spans="2:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B236" t="s">
+        <v>111</v>
+      </c>
+      <c r="H236" s="38"/>
+      <c r="AC236" s="40"/>
+    </row>
+    <row r="237" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H237" s="38"/>
+      <c r="I237" s="35"/>
+      <c r="J237" s="36"/>
+      <c r="K237" s="36"/>
+      <c r="L237" s="36"/>
+      <c r="M237" s="36"/>
+      <c r="N237" s="37"/>
+      <c r="AC237" s="40"/>
+    </row>
+    <row r="238" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H238" s="38"/>
+      <c r="I238" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="J238" s="16"/>
+      <c r="K238" s="16"/>
+      <c r="N238" s="40"/>
+      <c r="AC238" s="40"/>
+    </row>
+    <row r="239" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H239" s="38"/>
+      <c r="I239" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="N239" s="40"/>
+      <c r="AC239" s="40"/>
+    </row>
+    <row r="240" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H240" s="38"/>
+      <c r="I240" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="N240" s="40"/>
+      <c r="AC240" s="40"/>
+    </row>
+    <row r="241" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H241" s="38"/>
+      <c r="I241" s="38"/>
+      <c r="N241" s="40"/>
+      <c r="AC241" s="40"/>
+    </row>
+    <row r="242" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H242" s="38"/>
+      <c r="I242" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="J242" s="16"/>
+      <c r="K242" s="16"/>
+      <c r="L242" s="16"/>
+      <c r="M242" s="16"/>
+      <c r="N242" s="40"/>
+      <c r="AC242" s="40"/>
+    </row>
+    <row r="243" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H243" s="38"/>
+      <c r="I243" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="N243" s="40"/>
+      <c r="AC243" s="40"/>
+    </row>
+    <row r="244" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H244" s="38"/>
+      <c r="I244" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="N244" s="40"/>
+      <c r="AC244" s="40"/>
+    </row>
+    <row r="245" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H245" s="38"/>
+      <c r="I245" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="N245" s="40"/>
+      <c r="AC245" s="40"/>
+    </row>
+    <row r="246" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H246" s="38"/>
+      <c r="I246" s="38"/>
+      <c r="N246" s="40"/>
+      <c r="AC246" s="40"/>
+    </row>
+    <row r="247" spans="8:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H247" s="38"/>
+      <c r="I247" s="41"/>
+      <c r="J247" s="42"/>
+      <c r="K247" s="42"/>
+      <c r="L247" s="42"/>
+      <c r="M247" s="42"/>
+      <c r="N247" s="43"/>
+      <c r="AC247" s="40"/>
+    </row>
+    <row r="248" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H248" s="38"/>
+      <c r="AC248" s="40"/>
+    </row>
+    <row r="249" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H249" s="38"/>
+      <c r="P249" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q249" s="16"/>
+      <c r="R249" s="16"/>
+      <c r="S249" s="16"/>
+      <c r="T249" s="16"/>
+      <c r="U249" s="16"/>
+      <c r="V249" s="16"/>
+      <c r="W249" s="16"/>
+      <c r="AC249" s="40"/>
+    </row>
+    <row r="250" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H250" s="38"/>
+      <c r="P250" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q250" s="16"/>
+      <c r="R250" s="16"/>
+      <c r="S250" s="16"/>
+      <c r="T250" s="16"/>
+      <c r="U250" s="16"/>
+      <c r="V250" s="16"/>
+      <c r="W250" s="16"/>
+      <c r="AC250" s="40"/>
+    </row>
+    <row r="251" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H251" s="38"/>
+      <c r="I251" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="J251" s="26"/>
+      <c r="K251" s="26"/>
+      <c r="AC251" s="40"/>
+    </row>
+    <row r="252" spans="8:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H252" s="38"/>
+      <c r="AC252" s="40"/>
+    </row>
+    <row r="253" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H253" s="38"/>
+      <c r="I253" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="J253" s="46"/>
+      <c r="K253" s="46"/>
+      <c r="L253" s="36"/>
+      <c r="M253" s="36"/>
+      <c r="N253" s="37"/>
+      <c r="AC253" s="40"/>
+    </row>
+    <row r="254" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H254" s="38"/>
+      <c r="I254" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="N254" s="40"/>
+      <c r="AC254" s="40"/>
+    </row>
+    <row r="255" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H255" s="38"/>
+      <c r="I255" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="N255" s="40"/>
+      <c r="AC255" s="40"/>
+    </row>
+    <row r="256" spans="8:29" x14ac:dyDescent="0.2">
+      <c r="H256" s="38"/>
+      <c r="I256" s="38"/>
+      <c r="N256" s="40"/>
+      <c r="AC256" s="40"/>
+    </row>
+    <row r="257" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H257" s="38"/>
+      <c r="I257" s="44" t="s">
+        <v>148</v>
+      </c>
+      <c r="J257" s="16"/>
+      <c r="K257" s="16"/>
+      <c r="N257" s="40"/>
+      <c r="AC257" s="40"/>
+    </row>
+    <row r="258" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H258" s="38"/>
+      <c r="I258" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="N258" s="40"/>
+      <c r="AC258" s="40"/>
+    </row>
+    <row r="259" spans="2:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H259" s="38"/>
+      <c r="I259" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="J259" s="42"/>
+      <c r="K259" s="42"/>
+      <c r="L259" s="42"/>
+      <c r="M259" s="42"/>
+      <c r="N259" s="43"/>
+      <c r="AC259" s="40"/>
+    </row>
+    <row r="260" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H260" s="38"/>
+      <c r="AC260" s="40"/>
+    </row>
+    <row r="261" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H261" s="38"/>
+      <c r="AC261" s="40"/>
+    </row>
+    <row r="262" spans="2:29" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B262" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="C262" s="33"/>
+      <c r="D262" s="33"/>
+      <c r="E262" s="33"/>
+      <c r="F262" s="33"/>
+      <c r="G262" s="33"/>
+      <c r="H262" s="49"/>
+      <c r="I262" s="33"/>
+      <c r="J262" s="33"/>
+      <c r="K262" s="33"/>
+      <c r="L262" s="33"/>
+      <c r="AC262" s="40"/>
+    </row>
+    <row r="263" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H263" s="38"/>
+      <c r="AC263" s="40"/>
+    </row>
+    <row r="264" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B264" t="s">
+        <v>117</v>
+      </c>
+      <c r="H264" s="38"/>
+      <c r="AC264" s="40"/>
+    </row>
+    <row r="265" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B265" t="s">
+        <v>122</v>
+      </c>
+      <c r="H265" s="38"/>
+      <c r="AC265" s="40"/>
+    </row>
+    <row r="266" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H266" s="38"/>
+      <c r="AC266" s="40"/>
+    </row>
+    <row r="267" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H267" s="38"/>
+      <c r="AC267" s="40"/>
+    </row>
+    <row r="268" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B268" t="s">
+        <v>128</v>
+      </c>
+      <c r="H268" s="38"/>
+      <c r="AC268" s="40"/>
+    </row>
+    <row r="269" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B269" t="s">
         <v>118</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="K1" t="s">
+      <c r="H269" s="38"/>
+      <c r="AC269" s="40"/>
+    </row>
+    <row r="270" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B270" t="s">
+        <v>127</v>
+      </c>
+      <c r="H270" s="38"/>
+      <c r="AC270" s="40"/>
+    </row>
+    <row r="271" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B271" t="s">
+        <v>119</v>
+      </c>
+      <c r="H271" s="38"/>
+      <c r="AC271" s="40"/>
+    </row>
+    <row r="272" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H272" s="38"/>
+      <c r="AC272" s="40"/>
+    </row>
+    <row r="273" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H273" s="38"/>
+      <c r="AC273" s="40"/>
+    </row>
+    <row r="274" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="H274" s="38"/>
+      <c r="AC274" s="40"/>
+    </row>
+    <row r="275" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B275" t="s">
+        <v>120</v>
+      </c>
+      <c r="H275" s="38"/>
+      <c r="AC275" s="40"/>
+    </row>
+    <row r="276" spans="2:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B276" t="s">
+        <v>123</v>
+      </c>
+      <c r="H276" s="41"/>
+      <c r="I276" s="42"/>
+      <c r="J276" s="42"/>
+      <c r="K276" s="42"/>
+      <c r="L276" s="42"/>
+      <c r="M276" s="42"/>
+      <c r="N276" s="42"/>
+      <c r="O276" s="42"/>
+      <c r="P276" s="42"/>
+      <c r="Q276" s="42"/>
+      <c r="R276" s="42"/>
+      <c r="S276" s="42"/>
+      <c r="T276" s="42"/>
+      <c r="U276" s="42"/>
+      <c r="V276" s="42"/>
+      <c r="W276" s="42"/>
+      <c r="X276" s="42"/>
+      <c r="Y276" s="42"/>
+      <c r="Z276" s="42"/>
+      <c r="AA276" s="42"/>
+      <c r="AB276" s="42"/>
+      <c r="AC276" s="43"/>
+    </row>
+    <row r="278" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B278" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="280" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B280" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B4" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="13:13" x14ac:dyDescent="0.15">
-      <c r="M17" s="55" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="18" spans="13:13" x14ac:dyDescent="0.15">
-      <c r="M18" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" spans="13:13" x14ac:dyDescent="0.15">
-      <c r="M20" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="13:13" x14ac:dyDescent="0.15">
-      <c r="M22" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="23" spans="13:13" x14ac:dyDescent="0.15">
-      <c r="M23" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="24" spans="13:13" x14ac:dyDescent="0.15">
-      <c r="M24" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B50" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="37"/>
-      <c r="I50" s="37"/>
-      <c r="J50" s="37"/>
-      <c r="K50" s="37"/>
-      <c r="L50" s="37"/>
-      <c r="M50" s="38"/>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B51" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="C51" s="41"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="41"/>
-      <c r="I51" s="41"/>
-      <c r="J51" s="41"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="41"/>
-      <c r="M51" s="42"/>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B52" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="C52" s="41"/>
-      <c r="D52" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="41"/>
-      <c r="J52" s="41"/>
-      <c r="K52" s="41"/>
-      <c r="L52" s="41"/>
-      <c r="M52" s="42"/>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B53" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="41"/>
-      <c r="J53" s="41"/>
-      <c r="K53" s="41"/>
-      <c r="L53" s="41"/>
-      <c r="M53" s="42"/>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B54" s="39"/>
-      <c r="C54" s="41"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="41"/>
-      <c r="M54" s="42"/>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B55" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="C55" s="41"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="41"/>
-      <c r="J55" s="41"/>
-      <c r="K55" s="41"/>
-      <c r="L55" s="41"/>
-      <c r="M55" s="42"/>
-    </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B56" s="39"/>
-      <c r="C56" s="41"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="41"/>
-      <c r="I56" s="41"/>
-      <c r="J56" s="41"/>
-      <c r="K56" s="41"/>
-      <c r="L56" s="41"/>
-      <c r="M56" s="42"/>
-    </row>
-    <row r="57" spans="2:15" ht="30.75" x14ac:dyDescent="0.3">
-      <c r="B57" s="39"/>
-      <c r="C57" s="41"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="41"/>
-      <c r="J57" s="41"/>
-      <c r="K57" s="41"/>
-      <c r="L57" s="41"/>
-      <c r="M57" s="42"/>
-      <c r="N57" s="50" t="s">
-        <v>160</v>
-      </c>
-      <c r="O57" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B58" s="39"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
-      <c r="H58" s="41"/>
-      <c r="I58" s="41"/>
-      <c r="J58" s="41"/>
-      <c r="K58" s="41"/>
-      <c r="L58" s="41"/>
-      <c r="M58" s="42"/>
-    </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B59" s="39"/>
-      <c r="C59" s="41"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="41"/>
-      <c r="H59" s="41"/>
-      <c r="I59" s="41"/>
-      <c r="J59" s="41"/>
-      <c r="K59" s="41"/>
-      <c r="L59" s="41"/>
-      <c r="M59" s="42"/>
-    </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B60" s="39"/>
-      <c r="C60" s="41"/>
-      <c r="D60" s="41"/>
-      <c r="E60" s="41"/>
-      <c r="F60" s="41"/>
-      <c r="G60" s="41"/>
-      <c r="H60" s="41"/>
-      <c r="I60" s="41"/>
-      <c r="J60" s="41"/>
-      <c r="K60" s="41"/>
-      <c r="L60" s="41"/>
-      <c r="M60" s="42"/>
-    </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B61" s="39"/>
-      <c r="C61" s="41"/>
-      <c r="D61" s="41"/>
-      <c r="E61" s="41"/>
-      <c r="F61" s="41"/>
-      <c r="G61" s="41"/>
-      <c r="H61" s="41"/>
-      <c r="I61" s="41"/>
-      <c r="J61" s="41"/>
-      <c r="K61" s="41"/>
-      <c r="L61" s="41"/>
-      <c r="M61" s="42"/>
-    </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B62" s="39"/>
-      <c r="C62" s="41"/>
-      <c r="D62" s="41"/>
-      <c r="E62" s="41"/>
-      <c r="F62" s="41"/>
-      <c r="G62" s="41"/>
-      <c r="H62" s="41"/>
-      <c r="I62" s="41"/>
-      <c r="J62" s="41"/>
-      <c r="K62" s="41"/>
-      <c r="L62" s="41"/>
-      <c r="M62" s="42"/>
-    </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B63" s="39"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="41"/>
-      <c r="H63" s="41"/>
-      <c r="I63" s="41"/>
-      <c r="J63" s="41"/>
-      <c r="K63" s="41"/>
-      <c r="L63" s="41"/>
-      <c r="M63" s="42"/>
-    </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.15">
-      <c r="B64" s="39"/>
-      <c r="C64" s="41"/>
-      <c r="D64" s="41"/>
-      <c r="E64" s="41"/>
-      <c r="F64" s="41"/>
-      <c r="G64" s="41"/>
-      <c r="H64" s="41"/>
-      <c r="I64" s="41"/>
-      <c r="J64" s="41"/>
-      <c r="K64" s="41"/>
-      <c r="L64" s="41"/>
-      <c r="M64" s="42"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B65" s="39"/>
-      <c r="C65" s="41"/>
-      <c r="D65" s="41"/>
-      <c r="E65" s="41"/>
-      <c r="F65" s="41"/>
-      <c r="G65" s="41"/>
-      <c r="H65" s="41"/>
-      <c r="I65" s="41"/>
-      <c r="J65" s="41"/>
-      <c r="K65" s="41"/>
-      <c r="L65" s="41"/>
-      <c r="M65" s="42"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B66" s="39"/>
-      <c r="C66" s="41"/>
-      <c r="D66" s="41"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="41"/>
-      <c r="H66" s="41"/>
-      <c r="I66" s="41"/>
-      <c r="J66" s="41"/>
-      <c r="K66" s="41"/>
-      <c r="L66" s="41"/>
-      <c r="M66" s="42"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B67" s="39"/>
-      <c r="C67" s="41"/>
-      <c r="D67" s="41"/>
-      <c r="E67" s="41"/>
-      <c r="F67" s="41"/>
-      <c r="G67" s="41"/>
-      <c r="H67" s="41"/>
-      <c r="I67" s="41"/>
-      <c r="J67" s="41"/>
-      <c r="K67" s="41"/>
-      <c r="L67" s="41"/>
-      <c r="M67" s="42"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B68" s="39"/>
-      <c r="C68" s="41"/>
-      <c r="D68" s="41"/>
-      <c r="E68" s="41"/>
-      <c r="F68" s="41"/>
-      <c r="G68" s="41"/>
-      <c r="H68" s="41"/>
-      <c r="I68" s="41"/>
-      <c r="J68" s="41"/>
-      <c r="K68" s="41"/>
-      <c r="L68" s="41"/>
-      <c r="M68" s="42"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B69" s="39"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="41"/>
-      <c r="H69" s="41"/>
-      <c r="I69" s="41"/>
-      <c r="J69" s="41"/>
-      <c r="K69" s="41"/>
-      <c r="L69" s="41"/>
-      <c r="M69" s="42"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B70" s="39"/>
-      <c r="C70" s="41"/>
-      <c r="D70" s="41"/>
-      <c r="E70" s="41"/>
-      <c r="F70" s="41"/>
-      <c r="G70" s="41"/>
-      <c r="H70" s="41"/>
-      <c r="I70" s="41"/>
-      <c r="J70" s="41"/>
-      <c r="K70" s="41"/>
-      <c r="L70" s="41"/>
-      <c r="M70" s="42"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B71" s="39"/>
-      <c r="C71" s="41"/>
-      <c r="D71" s="41"/>
-      <c r="E71" s="41"/>
-      <c r="F71" s="41"/>
-      <c r="G71" s="41"/>
-      <c r="H71" s="41"/>
-      <c r="I71" s="41"/>
-      <c r="J71" s="41"/>
-      <c r="K71" s="41"/>
-      <c r="L71" s="41"/>
-      <c r="M71" s="42"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B72" s="39"/>
-      <c r="C72" s="41"/>
-      <c r="D72" s="41"/>
-      <c r="E72" s="41"/>
-      <c r="F72" s="41"/>
-      <c r="G72" s="41"/>
-      <c r="H72" s="41"/>
-      <c r="I72" s="41"/>
-      <c r="J72" s="41"/>
-      <c r="K72" s="41"/>
-      <c r="L72" s="41"/>
-      <c r="M72" s="42"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B73" s="39"/>
-      <c r="C73" s="41"/>
-      <c r="D73" s="41"/>
-      <c r="E73" s="41"/>
-      <c r="F73" s="41"/>
-      <c r="G73" s="41"/>
-      <c r="H73" s="41"/>
-      <c r="I73" s="41"/>
-      <c r="J73" s="41"/>
-      <c r="K73" s="41"/>
-      <c r="L73" s="41"/>
-      <c r="M73" s="42"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B74" s="39"/>
-      <c r="C74" s="41"/>
-      <c r="D74" s="41"/>
-      <c r="E74" s="41"/>
-      <c r="F74" s="41"/>
-      <c r="G74" s="41"/>
-      <c r="H74" s="41"/>
-      <c r="I74" s="41"/>
-      <c r="J74" s="41"/>
-      <c r="K74" s="41"/>
-      <c r="L74" s="41"/>
-      <c r="M74" s="42"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B75" s="39"/>
-      <c r="C75" s="41"/>
-      <c r="D75" s="41"/>
-      <c r="E75" s="41"/>
-      <c r="F75" s="41"/>
-      <c r="G75" s="41"/>
-      <c r="H75" s="41"/>
-      <c r="I75" s="41"/>
-      <c r="J75" s="41"/>
-      <c r="K75" s="41"/>
-      <c r="L75" s="41"/>
-      <c r="M75" s="42"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B76" s="39"/>
-      <c r="C76" s="41"/>
-      <c r="D76" s="41"/>
-      <c r="E76" s="41"/>
-      <c r="F76" s="41"/>
-      <c r="G76" s="41"/>
-      <c r="H76" s="41"/>
-      <c r="I76" s="41"/>
-      <c r="J76" s="41"/>
-      <c r="K76" s="41"/>
-      <c r="L76" s="41"/>
-      <c r="M76" s="42"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B77" s="39"/>
-      <c r="C77" s="41"/>
-      <c r="D77" s="41"/>
-      <c r="E77" s="41"/>
-      <c r="F77" s="41"/>
-      <c r="G77" s="41"/>
-      <c r="H77" s="41"/>
-      <c r="I77" s="41"/>
-      <c r="J77" s="41"/>
-      <c r="K77" s="41"/>
-      <c r="L77" s="41"/>
-      <c r="M77" s="42"/>
-    </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B78" s="39"/>
-      <c r="C78" s="41"/>
-      <c r="D78" s="41"/>
-      <c r="E78" s="41"/>
-      <c r="F78" s="41"/>
-      <c r="G78" s="41"/>
-      <c r="H78" s="41"/>
-      <c r="I78" s="41"/>
-      <c r="J78" s="41"/>
-      <c r="K78" s="41"/>
-      <c r="L78" s="41"/>
-      <c r="M78" s="42"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B79" s="39"/>
-      <c r="C79" s="41"/>
-      <c r="D79" s="41"/>
-      <c r="E79" s="41"/>
-      <c r="F79" s="41"/>
-      <c r="G79" s="41"/>
-      <c r="H79" s="41"/>
-      <c r="I79" s="41"/>
-      <c r="J79" s="41"/>
-      <c r="K79" s="41"/>
-      <c r="L79" s="41"/>
-      <c r="M79" s="42"/>
-    </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B80" s="39"/>
-      <c r="C80" s="41"/>
-      <c r="D80" s="41"/>
-      <c r="E80" s="41"/>
-      <c r="F80" s="41"/>
-      <c r="G80" s="41"/>
-      <c r="H80" s="41"/>
-      <c r="I80" s="41"/>
-      <c r="J80" s="41"/>
-      <c r="K80" s="41"/>
-      <c r="L80" s="41"/>
-      <c r="M80" s="42"/>
-    </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B81" s="39"/>
-      <c r="C81" s="41"/>
-      <c r="D81" s="41"/>
-      <c r="E81" s="41"/>
-      <c r="F81" s="41"/>
-      <c r="G81" s="41"/>
-      <c r="H81" s="41"/>
-      <c r="I81" s="41"/>
-      <c r="J81" s="41"/>
-      <c r="K81" s="41"/>
-      <c r="L81" s="41"/>
-      <c r="M81" s="42"/>
-    </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B82" s="39"/>
-      <c r="C82" s="41"/>
-      <c r="D82" s="41"/>
-      <c r="E82" s="41"/>
-      <c r="F82" s="41"/>
-      <c r="G82" s="41"/>
-      <c r="H82" s="41"/>
-      <c r="I82" s="41"/>
-      <c r="J82" s="41"/>
-      <c r="K82" s="41"/>
-      <c r="L82" s="41"/>
-      <c r="M82" s="42"/>
-    </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B83" s="39"/>
-      <c r="C83" s="41"/>
-      <c r="D83" s="41"/>
-      <c r="E83" s="41"/>
-      <c r="F83" s="41"/>
-      <c r="G83" s="41"/>
-      <c r="H83" s="41"/>
-      <c r="I83" s="41"/>
-      <c r="J83" s="41"/>
-      <c r="K83" s="41"/>
-      <c r="L83" s="41"/>
-      <c r="M83" s="42"/>
-    </row>
-    <row r="84" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="43"/>
-      <c r="C84" s="44"/>
-      <c r="D84" s="44"/>
-      <c r="E84" s="44"/>
-      <c r="F84" s="44"/>
-      <c r="G84" s="44"/>
-      <c r="H84" s="44"/>
-      <c r="I84" s="44"/>
-      <c r="J84" s="44"/>
-      <c r="K84" s="44"/>
-      <c r="L84" s="44"/>
-      <c r="M84" s="45"/>
-    </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B89" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B90" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B91" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="92" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B92" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B93" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="98" spans="2:3" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="B98" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B101" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="103" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B103" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C103" s="29" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="104" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B104" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C104" s="28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="105" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B105" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C105" s="28" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="B114" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="C114" s="27"/>
-    </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B115" t="s">
-        <v>103</v>
-      </c>
-      <c r="D115" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B118" s="17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B131" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="154" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="J154" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="155" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="J155" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="158" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I158" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="173" spans="9:9" x14ac:dyDescent="0.15">
-      <c r="I173" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="175" spans="9:9" x14ac:dyDescent="0.15">
-      <c r="I175" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="176" spans="9:9" x14ac:dyDescent="0.15">
-      <c r="I176" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="178" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="I178" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="179" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="I179" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="181" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="I181" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="183" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="I183" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="184" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="I184" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="188" spans="2:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="I188" s="35" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="189" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="I189" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="190" spans="2:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="191" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="B191" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="I191" s="36"/>
-      <c r="J191" s="37"/>
-      <c r="K191" s="37"/>
-      <c r="L191" s="37"/>
-      <c r="M191" s="37"/>
-      <c r="N191" s="37"/>
-      <c r="O191" s="37"/>
-      <c r="P191" s="37"/>
-      <c r="Q191" s="38"/>
-    </row>
-    <row r="192" spans="2:17" x14ac:dyDescent="0.15">
-      <c r="I192" s="39"/>
-      <c r="J192" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="K192" s="41"/>
-      <c r="L192" s="41"/>
-      <c r="M192" s="41"/>
-      <c r="N192" s="41"/>
-      <c r="O192" s="41"/>
-      <c r="P192" s="41"/>
-      <c r="Q192" s="42"/>
-    </row>
-    <row r="193" spans="9:17" x14ac:dyDescent="0.15">
-      <c r="I193" s="39"/>
-      <c r="J193" s="41" t="s">
-        <v>137</v>
-      </c>
-      <c r="K193" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="L193" s="41"/>
-      <c r="M193" s="41"/>
-      <c r="N193" s="41"/>
-      <c r="O193" s="41"/>
-      <c r="P193" s="41"/>
-      <c r="Q193" s="42"/>
-    </row>
-    <row r="194" spans="9:17" x14ac:dyDescent="0.15">
-      <c r="I194" s="39"/>
-      <c r="J194" s="41"/>
-      <c r="K194" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="L194" s="41" t="s">
-        <v>137</v>
-      </c>
-      <c r="M194" s="41"/>
-      <c r="N194" s="41"/>
-      <c r="O194" s="41"/>
-      <c r="P194" s="41"/>
-      <c r="Q194" s="42"/>
-    </row>
-    <row r="195" spans="9:17" x14ac:dyDescent="0.15">
-      <c r="I195" s="39"/>
-      <c r="J195" s="41"/>
-      <c r="K195" s="41"/>
-      <c r="L195" s="41"/>
-      <c r="M195" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="N195" s="41"/>
-      <c r="O195" s="41"/>
-      <c r="P195" s="41"/>
-      <c r="Q195" s="42"/>
-    </row>
-    <row r="196" spans="9:17" x14ac:dyDescent="0.15">
-      <c r="I196" s="39"/>
-      <c r="J196" s="41"/>
-      <c r="K196" s="41"/>
-      <c r="L196" s="41"/>
-      <c r="M196" s="41"/>
-      <c r="N196" s="41"/>
-      <c r="O196" s="41"/>
-      <c r="P196" s="41"/>
-      <c r="Q196" s="42"/>
-    </row>
-    <row r="197" spans="9:17" x14ac:dyDescent="0.15">
-      <c r="I197" s="39"/>
-      <c r="J197" s="41"/>
-      <c r="K197" s="41"/>
-      <c r="L197" s="41"/>
-      <c r="M197" s="41"/>
-      <c r="N197" s="41"/>
-      <c r="O197" s="41"/>
-      <c r="P197" s="41"/>
-      <c r="Q197" s="42"/>
-    </row>
-    <row r="198" spans="9:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="I198" s="43"/>
-      <c r="J198" s="44"/>
-      <c r="K198" s="44"/>
-      <c r="L198" s="44"/>
-      <c r="M198" s="44"/>
-      <c r="N198" s="44"/>
-      <c r="O198" s="44"/>
-      <c r="P198" s="44"/>
-      <c r="Q198" s="45"/>
-    </row>
-    <row r="202" spans="9:17" x14ac:dyDescent="0.15">
-      <c r="K202" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="203" spans="9:17" x14ac:dyDescent="0.15">
-      <c r="J203" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B221" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B223" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B224" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="226" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B226" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="227" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B227" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="229" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B229" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="230" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H230" s="17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="231" spans="2:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B231" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="232" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B232" t="s">
-        <v>113</v>
-      </c>
-      <c r="H232" s="36"/>
-      <c r="I232" s="37"/>
-      <c r="J232" s="37"/>
-      <c r="K232" s="37"/>
-      <c r="L232" s="37"/>
-      <c r="M232" s="37"/>
-      <c r="N232" s="37"/>
-      <c r="O232" s="37"/>
-      <c r="P232" s="37"/>
-      <c r="Q232" s="37"/>
-      <c r="R232" s="37"/>
-      <c r="S232" s="37"/>
-      <c r="T232" s="37"/>
-      <c r="U232" s="37"/>
-      <c r="V232" s="37"/>
-      <c r="W232" s="37"/>
-      <c r="X232" s="37"/>
-      <c r="Y232" s="37"/>
-      <c r="Z232" s="37"/>
-      <c r="AA232" s="37"/>
-      <c r="AB232" s="37"/>
-      <c r="AC232" s="38"/>
-    </row>
-    <row r="233" spans="2:29" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="B233" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="H233" s="39"/>
-      <c r="I233" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="J233" s="52"/>
-      <c r="K233" s="41"/>
-      <c r="L233" s="41"/>
-      <c r="M233" s="41"/>
-      <c r="N233" s="41"/>
-      <c r="O233" s="41"/>
-      <c r="P233" s="41"/>
-      <c r="Q233" s="41"/>
-      <c r="R233" s="41"/>
-      <c r="S233" s="41"/>
-      <c r="T233" s="41"/>
-      <c r="U233" s="41"/>
-      <c r="V233" s="41"/>
-      <c r="W233" s="41"/>
-      <c r="X233" s="41"/>
-      <c r="Y233" s="41"/>
-      <c r="Z233" s="41"/>
-      <c r="AA233" s="41"/>
-      <c r="AB233" s="41"/>
-      <c r="AC233" s="42"/>
-    </row>
-    <row r="234" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B234" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="H234" s="39"/>
-      <c r="I234" s="41"/>
-      <c r="J234" s="41"/>
-      <c r="K234" s="41"/>
-      <c r="L234" s="41"/>
-      <c r="M234" s="41"/>
-      <c r="N234" s="41"/>
-      <c r="O234" s="41"/>
-      <c r="P234" s="41"/>
-      <c r="Q234" s="41"/>
-      <c r="R234" s="41"/>
-      <c r="S234" s="41"/>
-      <c r="T234" s="41"/>
-      <c r="U234" s="41"/>
-      <c r="V234" s="41"/>
-      <c r="W234" s="41"/>
-      <c r="X234" s="41"/>
-      <c r="Y234" s="41"/>
-      <c r="Z234" s="41"/>
-      <c r="AA234" s="41"/>
-      <c r="AB234" s="41"/>
-      <c r="AC234" s="42"/>
-    </row>
-    <row r="235" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B235" t="s">
-        <v>96</v>
-      </c>
-      <c r="H235" s="39"/>
-      <c r="I235" s="41"/>
-      <c r="J235" s="41"/>
-      <c r="K235" s="41"/>
-      <c r="L235" s="41"/>
-      <c r="M235" s="41"/>
-      <c r="N235" s="41"/>
-      <c r="O235" s="41"/>
-      <c r="P235" s="41"/>
-      <c r="Q235" s="41"/>
-      <c r="R235" s="41"/>
-      <c r="S235" s="41"/>
-      <c r="T235" s="41"/>
-      <c r="U235" s="41"/>
-      <c r="V235" s="41"/>
-      <c r="W235" s="41"/>
-      <c r="X235" s="41"/>
-      <c r="Y235" s="41"/>
-      <c r="Z235" s="41"/>
-      <c r="AA235" s="41"/>
-      <c r="AB235" s="41"/>
-      <c r="AC235" s="42"/>
-    </row>
-    <row r="236" spans="2:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B236" t="s">
-        <v>116</v>
-      </c>
-      <c r="H236" s="39"/>
-      <c r="I236" s="41"/>
-      <c r="J236" s="41"/>
-      <c r="K236" s="41"/>
-      <c r="L236" s="41"/>
-      <c r="M236" s="41"/>
-      <c r="N236" s="41"/>
-      <c r="O236" s="41"/>
-      <c r="P236" s="41"/>
-      <c r="Q236" s="41"/>
-      <c r="R236" s="41"/>
-      <c r="S236" s="41"/>
-      <c r="T236" s="41"/>
-      <c r="U236" s="41"/>
-      <c r="V236" s="41"/>
-      <c r="W236" s="41"/>
-      <c r="X236" s="41"/>
-      <c r="Y236" s="41"/>
-      <c r="Z236" s="41"/>
-      <c r="AA236" s="41"/>
-      <c r="AB236" s="41"/>
-      <c r="AC236" s="42"/>
-    </row>
-    <row r="237" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H237" s="39"/>
-      <c r="I237" s="36"/>
-      <c r="J237" s="37"/>
-      <c r="K237" s="37"/>
-      <c r="L237" s="37"/>
-      <c r="M237" s="37"/>
-      <c r="N237" s="38"/>
-      <c r="O237" s="41"/>
-      <c r="P237" s="41"/>
-      <c r="Q237" s="41"/>
-      <c r="R237" s="41"/>
-      <c r="S237" s="41"/>
-      <c r="T237" s="41"/>
-      <c r="U237" s="41"/>
-      <c r="V237" s="41"/>
-      <c r="W237" s="41"/>
-      <c r="X237" s="41"/>
-      <c r="Y237" s="41"/>
-      <c r="Z237" s="41"/>
-      <c r="AA237" s="41"/>
-      <c r="AB237" s="41"/>
-      <c r="AC237" s="42"/>
-    </row>
-    <row r="238" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H238" s="39"/>
-      <c r="I238" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="J238" s="47"/>
-      <c r="K238" s="47"/>
-      <c r="L238" s="41"/>
-      <c r="M238" s="41"/>
-      <c r="N238" s="42"/>
-      <c r="O238" s="41"/>
-      <c r="P238" s="41"/>
-      <c r="Q238" s="41"/>
-      <c r="R238" s="41"/>
-      <c r="S238" s="41"/>
-      <c r="T238" s="41"/>
-      <c r="U238" s="41"/>
-      <c r="V238" s="41"/>
-      <c r="W238" s="41"/>
-      <c r="X238" s="41"/>
-      <c r="Y238" s="41"/>
-      <c r="Z238" s="41"/>
-      <c r="AA238" s="41"/>
-      <c r="AB238" s="41"/>
-      <c r="AC238" s="42"/>
-    </row>
-    <row r="239" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H239" s="39"/>
-      <c r="I239" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="J239" s="41"/>
-      <c r="K239" s="41"/>
-      <c r="L239" s="41"/>
-      <c r="M239" s="41"/>
-      <c r="N239" s="42"/>
-      <c r="O239" s="41"/>
-      <c r="P239" s="41"/>
-      <c r="Q239" s="41"/>
-      <c r="R239" s="41"/>
-      <c r="S239" s="41"/>
-      <c r="T239" s="41"/>
-      <c r="U239" s="41"/>
-      <c r="V239" s="41"/>
-      <c r="W239" s="41"/>
-      <c r="X239" s="41"/>
-      <c r="Y239" s="41"/>
-      <c r="Z239" s="41"/>
-      <c r="AA239" s="41"/>
-      <c r="AB239" s="41"/>
-      <c r="AC239" s="42"/>
-    </row>
-    <row r="240" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H240" s="39"/>
-      <c r="I240" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="J240" s="41"/>
-      <c r="K240" s="41"/>
-      <c r="L240" s="41"/>
-      <c r="M240" s="41"/>
-      <c r="N240" s="42"/>
-      <c r="O240" s="41"/>
-      <c r="P240" s="41"/>
-      <c r="Q240" s="41"/>
-      <c r="R240" s="41"/>
-      <c r="S240" s="41"/>
-      <c r="T240" s="41"/>
-      <c r="U240" s="41"/>
-      <c r="V240" s="41"/>
-      <c r="W240" s="41"/>
-      <c r="X240" s="41"/>
-      <c r="Y240" s="41"/>
-      <c r="Z240" s="41"/>
-      <c r="AA240" s="41"/>
-      <c r="AB240" s="41"/>
-      <c r="AC240" s="42"/>
-    </row>
-    <row r="241" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H241" s="39"/>
-      <c r="I241" s="39"/>
-      <c r="J241" s="41"/>
-      <c r="K241" s="41"/>
-      <c r="L241" s="41"/>
-      <c r="M241" s="41"/>
-      <c r="N241" s="42"/>
-      <c r="O241" s="41"/>
-      <c r="P241" s="41"/>
-      <c r="Q241" s="41"/>
-      <c r="R241" s="41"/>
-      <c r="S241" s="41"/>
-      <c r="T241" s="41"/>
-      <c r="U241" s="41"/>
-      <c r="V241" s="41"/>
-      <c r="W241" s="41"/>
-      <c r="X241" s="41"/>
-      <c r="Y241" s="41"/>
-      <c r="Z241" s="41"/>
-      <c r="AA241" s="41"/>
-      <c r="AB241" s="41"/>
-      <c r="AC241" s="42"/>
-    </row>
-    <row r="242" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H242" s="39"/>
-      <c r="I242" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="J242" s="47"/>
-      <c r="K242" s="47"/>
-      <c r="L242" s="47"/>
-      <c r="M242" s="47"/>
-      <c r="N242" s="42"/>
-      <c r="O242" s="41"/>
-      <c r="P242" s="41"/>
-      <c r="Q242" s="41"/>
-      <c r="R242" s="41"/>
-      <c r="S242" s="41"/>
-      <c r="T242" s="41"/>
-      <c r="U242" s="41"/>
-      <c r="V242" s="41"/>
-      <c r="W242" s="41"/>
-      <c r="X242" s="41"/>
-      <c r="Y242" s="41"/>
-      <c r="Z242" s="41"/>
-      <c r="AA242" s="41"/>
-      <c r="AB242" s="41"/>
-      <c r="AC242" s="42"/>
-    </row>
-    <row r="243" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H243" s="39"/>
-      <c r="I243" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="J243" s="41"/>
-      <c r="K243" s="41"/>
-      <c r="L243" s="41"/>
-      <c r="M243" s="41"/>
-      <c r="N243" s="42"/>
-      <c r="O243" s="41"/>
-      <c r="P243" s="41"/>
-      <c r="Q243" s="41"/>
-      <c r="R243" s="41"/>
-      <c r="S243" s="41"/>
-      <c r="T243" s="41"/>
-      <c r="U243" s="41"/>
-      <c r="V243" s="41"/>
-      <c r="W243" s="41"/>
-      <c r="X243" s="41"/>
-      <c r="Y243" s="41"/>
-      <c r="Z243" s="41"/>
-      <c r="AA243" s="41"/>
-      <c r="AB243" s="41"/>
-      <c r="AC243" s="42"/>
-    </row>
-    <row r="244" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H244" s="39"/>
-      <c r="I244" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="J244" s="41"/>
-      <c r="K244" s="41"/>
-      <c r="L244" s="41"/>
-      <c r="M244" s="41"/>
-      <c r="N244" s="42"/>
-      <c r="O244" s="41"/>
-      <c r="P244" s="41"/>
-      <c r="Q244" s="41"/>
-      <c r="R244" s="41"/>
-      <c r="S244" s="41"/>
-      <c r="T244" s="41"/>
-      <c r="U244" s="41"/>
-      <c r="V244" s="41"/>
-      <c r="W244" s="41"/>
-      <c r="X244" s="41"/>
-      <c r="Y244" s="41"/>
-      <c r="Z244" s="41"/>
-      <c r="AA244" s="41"/>
-      <c r="AB244" s="41"/>
-      <c r="AC244" s="42"/>
-    </row>
-    <row r="245" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H245" s="39"/>
-      <c r="I245" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="J245" s="41"/>
-      <c r="K245" s="41"/>
-      <c r="L245" s="41"/>
-      <c r="M245" s="41"/>
-      <c r="N245" s="42"/>
-      <c r="O245" s="41"/>
-      <c r="P245" s="41"/>
-      <c r="Q245" s="41"/>
-      <c r="R245" s="41"/>
-      <c r="S245" s="41"/>
-      <c r="T245" s="41"/>
-      <c r="U245" s="41"/>
-      <c r="V245" s="41"/>
-      <c r="W245" s="41"/>
-      <c r="X245" s="41"/>
-      <c r="Y245" s="41"/>
-      <c r="Z245" s="41"/>
-      <c r="AA245" s="41"/>
-      <c r="AB245" s="41"/>
-      <c r="AC245" s="42"/>
-    </row>
-    <row r="246" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H246" s="39"/>
-      <c r="I246" s="39"/>
-      <c r="J246" s="41"/>
-      <c r="K246" s="41"/>
-      <c r="L246" s="41"/>
-      <c r="M246" s="41"/>
-      <c r="N246" s="42"/>
-      <c r="O246" s="41"/>
-      <c r="P246" s="41"/>
-      <c r="Q246" s="41"/>
-      <c r="R246" s="41"/>
-      <c r="S246" s="41"/>
-      <c r="T246" s="41"/>
-      <c r="U246" s="41"/>
-      <c r="V246" s="41"/>
-      <c r="W246" s="41"/>
-      <c r="X246" s="41"/>
-      <c r="Y246" s="41"/>
-      <c r="Z246" s="41"/>
-      <c r="AA246" s="41"/>
-      <c r="AB246" s="41"/>
-      <c r="AC246" s="42"/>
-    </row>
-    <row r="247" spans="8:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="H247" s="39"/>
-      <c r="I247" s="43"/>
-      <c r="J247" s="44"/>
-      <c r="K247" s="44"/>
-      <c r="L247" s="44"/>
-      <c r="M247" s="44"/>
-      <c r="N247" s="45"/>
-      <c r="O247" s="41"/>
-      <c r="P247" s="41"/>
-      <c r="Q247" s="41"/>
-      <c r="R247" s="41"/>
-      <c r="S247" s="41"/>
-      <c r="T247" s="41"/>
-      <c r="U247" s="41"/>
-      <c r="V247" s="41"/>
-      <c r="W247" s="41"/>
-      <c r="X247" s="41"/>
-      <c r="Y247" s="41"/>
-      <c r="Z247" s="41"/>
-      <c r="AA247" s="41"/>
-      <c r="AB247" s="41"/>
-      <c r="AC247" s="42"/>
-    </row>
-    <row r="248" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H248" s="39"/>
-      <c r="I248" s="41"/>
-      <c r="J248" s="41"/>
-      <c r="K248" s="41"/>
-      <c r="L248" s="41"/>
-      <c r="M248" s="41"/>
-      <c r="N248" s="41"/>
-      <c r="O248" s="41"/>
-      <c r="P248" s="41"/>
-      <c r="Q248" s="41"/>
-      <c r="R248" s="41"/>
-      <c r="S248" s="41"/>
-      <c r="T248" s="41"/>
-      <c r="U248" s="41"/>
-      <c r="V248" s="41"/>
-      <c r="W248" s="41"/>
-      <c r="X248" s="41"/>
-      <c r="Y248" s="41"/>
-      <c r="Z248" s="41"/>
-      <c r="AA248" s="41"/>
-      <c r="AB248" s="41"/>
-      <c r="AC248" s="42"/>
-    </row>
-    <row r="249" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H249" s="39"/>
-      <c r="I249" s="41"/>
-      <c r="J249" s="41"/>
-      <c r="K249" s="41"/>
-      <c r="L249" s="41"/>
-      <c r="M249" s="41"/>
-      <c r="N249" s="41"/>
-      <c r="O249" s="41"/>
-      <c r="P249" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q249" s="47"/>
-      <c r="R249" s="47"/>
-      <c r="S249" s="47"/>
-      <c r="T249" s="47"/>
-      <c r="U249" s="47"/>
-      <c r="V249" s="47"/>
-      <c r="W249" s="47"/>
-      <c r="X249" s="41"/>
-      <c r="Y249" s="41"/>
-      <c r="Z249" s="41"/>
-      <c r="AA249" s="41"/>
-      <c r="AB249" s="41"/>
-      <c r="AC249" s="42"/>
-    </row>
-    <row r="250" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H250" s="39"/>
-      <c r="I250" s="41"/>
-      <c r="J250" s="41"/>
-      <c r="K250" s="41"/>
-      <c r="L250" s="41"/>
-      <c r="M250" s="41"/>
-      <c r="N250" s="41"/>
-      <c r="O250" s="41"/>
-      <c r="P250" s="47" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q250" s="47"/>
-      <c r="R250" s="47"/>
-      <c r="S250" s="47"/>
-      <c r="T250" s="47"/>
-      <c r="U250" s="47"/>
-      <c r="V250" s="47"/>
-      <c r="W250" s="47"/>
-      <c r="X250" s="41"/>
-      <c r="Y250" s="41"/>
-      <c r="Z250" s="41"/>
-      <c r="AA250" s="41"/>
-      <c r="AB250" s="41"/>
-      <c r="AC250" s="42"/>
-    </row>
-    <row r="251" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H251" s="39"/>
-      <c r="I251" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="J251" s="52"/>
-      <c r="K251" s="52"/>
-      <c r="L251" s="41"/>
-      <c r="M251" s="41"/>
-      <c r="N251" s="41"/>
-      <c r="O251" s="41"/>
-      <c r="P251" s="41"/>
-      <c r="Q251" s="41"/>
-      <c r="R251" s="41"/>
-      <c r="S251" s="41"/>
-      <c r="T251" s="41"/>
-      <c r="U251" s="41"/>
-      <c r="V251" s="41"/>
-      <c r="W251" s="41"/>
-      <c r="X251" s="41"/>
-      <c r="Y251" s="41"/>
-      <c r="Z251" s="41"/>
-      <c r="AA251" s="41"/>
-      <c r="AB251" s="41"/>
-      <c r="AC251" s="42"/>
-    </row>
-    <row r="252" spans="8:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="H252" s="39"/>
-      <c r="I252" s="41"/>
-      <c r="J252" s="41"/>
-      <c r="K252" s="41"/>
-      <c r="L252" s="41"/>
-      <c r="M252" s="41"/>
-      <c r="N252" s="41"/>
-      <c r="O252" s="41"/>
-      <c r="P252" s="41"/>
-      <c r="Q252" s="41"/>
-      <c r="R252" s="41"/>
-      <c r="S252" s="41"/>
-      <c r="T252" s="41"/>
-      <c r="U252" s="41"/>
-      <c r="V252" s="41"/>
-      <c r="W252" s="41"/>
-      <c r="X252" s="41"/>
-      <c r="Y252" s="41"/>
-      <c r="Z252" s="41"/>
-      <c r="AA252" s="41"/>
-      <c r="AB252" s="41"/>
-      <c r="AC252" s="42"/>
-    </row>
-    <row r="253" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H253" s="39"/>
-      <c r="I253" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="J253" s="49"/>
-      <c r="K253" s="49"/>
-      <c r="L253" s="37"/>
-      <c r="M253" s="37"/>
-      <c r="N253" s="38"/>
-      <c r="O253" s="41"/>
-      <c r="P253" s="41"/>
-      <c r="Q253" s="41"/>
-      <c r="R253" s="41"/>
-      <c r="S253" s="41"/>
-      <c r="T253" s="41"/>
-      <c r="U253" s="41"/>
-      <c r="V253" s="41"/>
-      <c r="W253" s="41"/>
-      <c r="X253" s="41"/>
-      <c r="Y253" s="41"/>
-      <c r="Z253" s="41"/>
-      <c r="AA253" s="41"/>
-      <c r="AB253" s="41"/>
-      <c r="AC253" s="42"/>
-    </row>
-    <row r="254" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H254" s="39"/>
-      <c r="I254" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="J254" s="41"/>
-      <c r="K254" s="41"/>
-      <c r="L254" s="41"/>
-      <c r="M254" s="41"/>
-      <c r="N254" s="42"/>
-      <c r="O254" s="41"/>
-      <c r="P254" s="41"/>
-      <c r="Q254" s="41"/>
-      <c r="R254" s="41"/>
-      <c r="S254" s="41"/>
-      <c r="T254" s="41"/>
-      <c r="U254" s="41"/>
-      <c r="V254" s="41"/>
-      <c r="W254" s="41"/>
-      <c r="X254" s="41"/>
-      <c r="Y254" s="41"/>
-      <c r="Z254" s="41"/>
-      <c r="AA254" s="41"/>
-      <c r="AB254" s="41"/>
-      <c r="AC254" s="42"/>
-    </row>
-    <row r="255" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H255" s="39"/>
-      <c r="I255" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="J255" s="41"/>
-      <c r="K255" s="41"/>
-      <c r="L255" s="41"/>
-      <c r="M255" s="41"/>
-      <c r="N255" s="42"/>
-      <c r="O255" s="41"/>
-      <c r="P255" s="41"/>
-      <c r="Q255" s="41"/>
-      <c r="R255" s="41"/>
-      <c r="S255" s="41"/>
-      <c r="T255" s="41"/>
-      <c r="U255" s="41"/>
-      <c r="V255" s="41"/>
-      <c r="W255" s="41"/>
-      <c r="X255" s="41"/>
-      <c r="Y255" s="41"/>
-      <c r="Z255" s="41"/>
-      <c r="AA255" s="41"/>
-      <c r="AB255" s="41"/>
-      <c r="AC255" s="42"/>
-    </row>
-    <row r="256" spans="8:29" x14ac:dyDescent="0.15">
-      <c r="H256" s="39"/>
-      <c r="I256" s="39"/>
-      <c r="J256" s="41"/>
-      <c r="K256" s="41"/>
-      <c r="L256" s="41"/>
-      <c r="M256" s="41"/>
-      <c r="N256" s="42"/>
-      <c r="O256" s="41"/>
-      <c r="P256" s="41"/>
-      <c r="Q256" s="41"/>
-      <c r="R256" s="41"/>
-      <c r="S256" s="41"/>
-      <c r="T256" s="41"/>
-      <c r="U256" s="41"/>
-      <c r="V256" s="41"/>
-      <c r="W256" s="41"/>
-      <c r="X256" s="41"/>
-      <c r="Y256" s="41"/>
-      <c r="Z256" s="41"/>
-      <c r="AA256" s="41"/>
-      <c r="AB256" s="41"/>
-      <c r="AC256" s="42"/>
-    </row>
-    <row r="257" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H257" s="39"/>
-      <c r="I257" s="46" t="s">
-        <v>154</v>
-      </c>
-      <c r="J257" s="47"/>
-      <c r="K257" s="47"/>
-      <c r="L257" s="41"/>
-      <c r="M257" s="41"/>
-      <c r="N257" s="42"/>
-      <c r="O257" s="41"/>
-      <c r="P257" s="41"/>
-      <c r="Q257" s="41"/>
-      <c r="R257" s="41"/>
-      <c r="S257" s="41"/>
-      <c r="T257" s="41"/>
-      <c r="U257" s="41"/>
-      <c r="V257" s="41"/>
-      <c r="W257" s="41"/>
-      <c r="X257" s="41"/>
-      <c r="Y257" s="41"/>
-      <c r="Z257" s="41"/>
-      <c r="AA257" s="41"/>
-      <c r="AB257" s="41"/>
-      <c r="AC257" s="42"/>
-    </row>
-    <row r="258" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H258" s="39"/>
-      <c r="I258" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="J258" s="41"/>
-      <c r="K258" s="41"/>
-      <c r="L258" s="41"/>
-      <c r="M258" s="41"/>
-      <c r="N258" s="42"/>
-      <c r="O258" s="41"/>
-      <c r="P258" s="41"/>
-      <c r="Q258" s="41"/>
-      <c r="R258" s="41"/>
-      <c r="S258" s="41"/>
-      <c r="T258" s="41"/>
-      <c r="U258" s="41"/>
-      <c r="V258" s="41"/>
-      <c r="W258" s="41"/>
-      <c r="X258" s="41"/>
-      <c r="Y258" s="41"/>
-      <c r="Z258" s="41"/>
-      <c r="AA258" s="41"/>
-      <c r="AB258" s="41"/>
-      <c r="AC258" s="42"/>
-    </row>
-    <row r="259" spans="2:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="H259" s="39"/>
-      <c r="I259" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="J259" s="44"/>
-      <c r="K259" s="44"/>
-      <c r="L259" s="44"/>
-      <c r="M259" s="44"/>
-      <c r="N259" s="45"/>
-      <c r="O259" s="41"/>
-      <c r="P259" s="41"/>
-      <c r="Q259" s="41"/>
-      <c r="R259" s="41"/>
-      <c r="S259" s="41"/>
-      <c r="T259" s="41"/>
-      <c r="U259" s="41"/>
-      <c r="V259" s="41"/>
-      <c r="W259" s="41"/>
-      <c r="X259" s="41"/>
-      <c r="Y259" s="41"/>
-      <c r="Z259" s="41"/>
-      <c r="AA259" s="41"/>
-      <c r="AB259" s="41"/>
-      <c r="AC259" s="42"/>
-    </row>
-    <row r="260" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H260" s="39"/>
-      <c r="I260" s="41"/>
-      <c r="J260" s="41"/>
-      <c r="K260" s="41"/>
-      <c r="L260" s="41"/>
-      <c r="M260" s="41"/>
-      <c r="N260" s="41"/>
-      <c r="O260" s="41"/>
-      <c r="P260" s="41"/>
-      <c r="Q260" s="41"/>
-      <c r="R260" s="41"/>
-      <c r="S260" s="41"/>
-      <c r="T260" s="41"/>
-      <c r="U260" s="41"/>
-      <c r="V260" s="41"/>
-      <c r="W260" s="41"/>
-      <c r="X260" s="41"/>
-      <c r="Y260" s="41"/>
-      <c r="Z260" s="41"/>
-      <c r="AA260" s="41"/>
-      <c r="AB260" s="41"/>
-      <c r="AC260" s="42"/>
-    </row>
-    <row r="261" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H261" s="39"/>
-      <c r="I261" s="41"/>
-      <c r="J261" s="41"/>
-      <c r="K261" s="41"/>
-      <c r="L261" s="41"/>
-      <c r="M261" s="41"/>
-      <c r="N261" s="41"/>
-      <c r="O261" s="41"/>
-      <c r="P261" s="41"/>
-      <c r="Q261" s="41"/>
-      <c r="R261" s="41"/>
-      <c r="S261" s="41"/>
-      <c r="T261" s="41"/>
-      <c r="U261" s="41"/>
-      <c r="V261" s="41"/>
-      <c r="W261" s="41"/>
-      <c r="X261" s="41"/>
-      <c r="Y261" s="41"/>
-      <c r="Z261" s="41"/>
-      <c r="AA261" s="41"/>
-      <c r="AB261" s="41"/>
-      <c r="AC261" s="42"/>
-    </row>
-    <row r="262" spans="2:29" ht="24" x14ac:dyDescent="0.25">
-      <c r="B262" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="C262" s="34"/>
-      <c r="D262" s="34"/>
-      <c r="E262" s="34"/>
-      <c r="F262" s="34"/>
-      <c r="G262" s="34"/>
-      <c r="H262" s="53"/>
-      <c r="I262" s="54"/>
-      <c r="J262" s="54"/>
-      <c r="K262" s="54"/>
-      <c r="L262" s="54"/>
-      <c r="M262" s="41"/>
-      <c r="N262" s="41"/>
-      <c r="O262" s="41"/>
-      <c r="P262" s="41"/>
-      <c r="Q262" s="41"/>
-      <c r="R262" s="41"/>
-      <c r="S262" s="41"/>
-      <c r="T262" s="41"/>
-      <c r="U262" s="41"/>
-      <c r="V262" s="41"/>
-      <c r="W262" s="41"/>
-      <c r="X262" s="41"/>
-      <c r="Y262" s="41"/>
-      <c r="Z262" s="41"/>
-      <c r="AA262" s="41"/>
-      <c r="AB262" s="41"/>
-      <c r="AC262" s="42"/>
-    </row>
-    <row r="263" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H263" s="39"/>
-      <c r="I263" s="41"/>
-      <c r="J263" s="41"/>
-      <c r="K263" s="41"/>
-      <c r="L263" s="41"/>
-      <c r="M263" s="41"/>
-      <c r="N263" s="41"/>
-      <c r="O263" s="41"/>
-      <c r="P263" s="41"/>
-      <c r="Q263" s="41"/>
-      <c r="R263" s="41"/>
-      <c r="S263" s="41"/>
-      <c r="T263" s="41"/>
-      <c r="U263" s="41"/>
-      <c r="V263" s="41"/>
-      <c r="W263" s="41"/>
-      <c r="X263" s="41"/>
-      <c r="Y263" s="41"/>
-      <c r="Z263" s="41"/>
-      <c r="AA263" s="41"/>
-      <c r="AB263" s="41"/>
-      <c r="AC263" s="42"/>
-    </row>
-    <row r="264" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B264" t="s">
-        <v>122</v>
-      </c>
-      <c r="H264" s="39"/>
-      <c r="I264" s="41"/>
-      <c r="J264" s="41"/>
-      <c r="K264" s="41"/>
-      <c r="L264" s="41"/>
-      <c r="M264" s="41"/>
-      <c r="N264" s="41"/>
-      <c r="O264" s="41"/>
-      <c r="P264" s="41"/>
-      <c r="Q264" s="41"/>
-      <c r="R264" s="41"/>
-      <c r="S264" s="41"/>
-      <c r="T264" s="41"/>
-      <c r="U264" s="41"/>
-      <c r="V264" s="41"/>
-      <c r="W264" s="41"/>
-      <c r="X264" s="41"/>
-      <c r="Y264" s="41"/>
-      <c r="Z264" s="41"/>
-      <c r="AA264" s="41"/>
-      <c r="AB264" s="41"/>
-      <c r="AC264" s="42"/>
-    </row>
-    <row r="265" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B265" t="s">
-        <v>127</v>
-      </c>
-      <c r="H265" s="39"/>
-      <c r="I265" s="41"/>
-      <c r="J265" s="41"/>
-      <c r="K265" s="41"/>
-      <c r="L265" s="41"/>
-      <c r="M265" s="41"/>
-      <c r="N265" s="41"/>
-      <c r="O265" s="41"/>
-      <c r="P265" s="41"/>
-      <c r="Q265" s="41"/>
-      <c r="R265" s="41"/>
-      <c r="S265" s="41"/>
-      <c r="T265" s="41"/>
-      <c r="U265" s="41"/>
-      <c r="V265" s="41"/>
-      <c r="W265" s="41"/>
-      <c r="X265" s="41"/>
-      <c r="Y265" s="41"/>
-      <c r="Z265" s="41"/>
-      <c r="AA265" s="41"/>
-      <c r="AB265" s="41"/>
-      <c r="AC265" s="42"/>
-    </row>
-    <row r="266" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H266" s="39"/>
-      <c r="I266" s="41"/>
-      <c r="J266" s="41"/>
-      <c r="K266" s="41"/>
-      <c r="L266" s="41"/>
-      <c r="M266" s="41"/>
-      <c r="N266" s="41"/>
-      <c r="O266" s="41"/>
-      <c r="P266" s="41"/>
-      <c r="Q266" s="41"/>
-      <c r="R266" s="41"/>
-      <c r="S266" s="41"/>
-      <c r="T266" s="41"/>
-      <c r="U266" s="41"/>
-      <c r="V266" s="41"/>
-      <c r="W266" s="41"/>
-      <c r="X266" s="41"/>
-      <c r="Y266" s="41"/>
-      <c r="Z266" s="41"/>
-      <c r="AA266" s="41"/>
-      <c r="AB266" s="41"/>
-      <c r="AC266" s="42"/>
-    </row>
-    <row r="267" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H267" s="39"/>
-      <c r="I267" s="41"/>
-      <c r="J267" s="41"/>
-      <c r="K267" s="41"/>
-      <c r="L267" s="41"/>
-      <c r="M267" s="41"/>
-      <c r="N267" s="41"/>
-      <c r="O267" s="41"/>
-      <c r="P267" s="41"/>
-      <c r="Q267" s="41"/>
-      <c r="R267" s="41"/>
-      <c r="S267" s="41"/>
-      <c r="T267" s="41"/>
-      <c r="U267" s="41"/>
-      <c r="V267" s="41"/>
-      <c r="W267" s="41"/>
-      <c r="X267" s="41"/>
-      <c r="Y267" s="41"/>
-      <c r="Z267" s="41"/>
-      <c r="AA267" s="41"/>
-      <c r="AB267" s="41"/>
-      <c r="AC267" s="42"/>
-    </row>
-    <row r="268" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B268" t="s">
-        <v>133</v>
-      </c>
-      <c r="H268" s="39"/>
-      <c r="I268" s="41"/>
-      <c r="J268" s="41"/>
-      <c r="K268" s="41"/>
-      <c r="L268" s="41"/>
-      <c r="M268" s="41"/>
-      <c r="N268" s="41"/>
-      <c r="O268" s="41"/>
-      <c r="P268" s="41"/>
-      <c r="Q268" s="41"/>
-      <c r="R268" s="41"/>
-      <c r="S268" s="41"/>
-      <c r="T268" s="41"/>
-      <c r="U268" s="41"/>
-      <c r="V268" s="41"/>
-      <c r="W268" s="41"/>
-      <c r="X268" s="41"/>
-      <c r="Y268" s="41"/>
-      <c r="Z268" s="41"/>
-      <c r="AA268" s="41"/>
-      <c r="AB268" s="41"/>
-      <c r="AC268" s="42"/>
-    </row>
-    <row r="269" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B269" t="s">
-        <v>123</v>
-      </c>
-      <c r="H269" s="39"/>
-      <c r="I269" s="41"/>
-      <c r="J269" s="41"/>
-      <c r="K269" s="41"/>
-      <c r="L269" s="41"/>
-      <c r="M269" s="41"/>
-      <c r="N269" s="41"/>
-      <c r="O269" s="41"/>
-      <c r="P269" s="41"/>
-      <c r="Q269" s="41"/>
-      <c r="R269" s="41"/>
-      <c r="S269" s="41"/>
-      <c r="T269" s="41"/>
-      <c r="U269" s="41"/>
-      <c r="V269" s="41"/>
-      <c r="W269" s="41"/>
-      <c r="X269" s="41"/>
-      <c r="Y269" s="41"/>
-      <c r="Z269" s="41"/>
-      <c r="AA269" s="41"/>
-      <c r="AB269" s="41"/>
-      <c r="AC269" s="42"/>
-    </row>
-    <row r="270" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B270" t="s">
-        <v>132</v>
-      </c>
-      <c r="H270" s="39"/>
-      <c r="I270" s="41"/>
-      <c r="J270" s="41"/>
-      <c r="K270" s="41"/>
-      <c r="L270" s="41"/>
-      <c r="M270" s="41"/>
-      <c r="N270" s="41"/>
-      <c r="O270" s="41"/>
-      <c r="P270" s="41"/>
-      <c r="Q270" s="41"/>
-      <c r="R270" s="41"/>
-      <c r="S270" s="41"/>
-      <c r="T270" s="41"/>
-      <c r="U270" s="41"/>
-      <c r="V270" s="41"/>
-      <c r="W270" s="41"/>
-      <c r="X270" s="41"/>
-      <c r="Y270" s="41"/>
-      <c r="Z270" s="41"/>
-      <c r="AA270" s="41"/>
-      <c r="AB270" s="41"/>
-      <c r="AC270" s="42"/>
-    </row>
-    <row r="271" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B271" t="s">
-        <v>124</v>
-      </c>
-      <c r="H271" s="39"/>
-      <c r="I271" s="41"/>
-      <c r="J271" s="41"/>
-      <c r="K271" s="41"/>
-      <c r="L271" s="41"/>
-      <c r="M271" s="41"/>
-      <c r="N271" s="41"/>
-      <c r="O271" s="41"/>
-      <c r="P271" s="41"/>
-      <c r="Q271" s="41"/>
-      <c r="R271" s="41"/>
-      <c r="S271" s="41"/>
-      <c r="T271" s="41"/>
-      <c r="U271" s="41"/>
-      <c r="V271" s="41"/>
-      <c r="W271" s="41"/>
-      <c r="X271" s="41"/>
-      <c r="Y271" s="41"/>
-      <c r="Z271" s="41"/>
-      <c r="AA271" s="41"/>
-      <c r="AB271" s="41"/>
-      <c r="AC271" s="42"/>
-    </row>
-    <row r="272" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H272" s="39"/>
-      <c r="I272" s="41"/>
-      <c r="J272" s="41"/>
-      <c r="K272" s="41"/>
-      <c r="L272" s="41"/>
-      <c r="M272" s="41"/>
-      <c r="N272" s="41"/>
-      <c r="O272" s="41"/>
-      <c r="P272" s="41"/>
-      <c r="Q272" s="41"/>
-      <c r="R272" s="41"/>
-      <c r="S272" s="41"/>
-      <c r="T272" s="41"/>
-      <c r="U272" s="41"/>
-      <c r="V272" s="41"/>
-      <c r="W272" s="41"/>
-      <c r="X272" s="41"/>
-      <c r="Y272" s="41"/>
-      <c r="Z272" s="41"/>
-      <c r="AA272" s="41"/>
-      <c r="AB272" s="41"/>
-      <c r="AC272" s="42"/>
-    </row>
-    <row r="273" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H273" s="39"/>
-      <c r="I273" s="41"/>
-      <c r="J273" s="41"/>
-      <c r="K273" s="41"/>
-      <c r="L273" s="41"/>
-      <c r="M273" s="41"/>
-      <c r="N273" s="41"/>
-      <c r="O273" s="41"/>
-      <c r="P273" s="41"/>
-      <c r="Q273" s="41"/>
-      <c r="R273" s="41"/>
-      <c r="S273" s="41"/>
-      <c r="T273" s="41"/>
-      <c r="U273" s="41"/>
-      <c r="V273" s="41"/>
-      <c r="W273" s="41"/>
-      <c r="X273" s="41"/>
-      <c r="Y273" s="41"/>
-      <c r="Z273" s="41"/>
-      <c r="AA273" s="41"/>
-      <c r="AB273" s="41"/>
-      <c r="AC273" s="42"/>
-    </row>
-    <row r="274" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="H274" s="39"/>
-      <c r="I274" s="41"/>
-      <c r="J274" s="41"/>
-      <c r="K274" s="41"/>
-      <c r="L274" s="41"/>
-      <c r="M274" s="41"/>
-      <c r="N274" s="41"/>
-      <c r="O274" s="41"/>
-      <c r="P274" s="41"/>
-      <c r="Q274" s="41"/>
-      <c r="R274" s="41"/>
-      <c r="S274" s="41"/>
-      <c r="T274" s="41"/>
-      <c r="U274" s="41"/>
-      <c r="V274" s="41"/>
-      <c r="W274" s="41"/>
-      <c r="X274" s="41"/>
-      <c r="Y274" s="41"/>
-      <c r="Z274" s="41"/>
-      <c r="AA274" s="41"/>
-      <c r="AB274" s="41"/>
-      <c r="AC274" s="42"/>
-    </row>
-    <row r="275" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B275" t="s">
+    <row r="281" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B281" t="s">
         <v>125</v>
       </c>
-      <c r="H275" s="39"/>
-      <c r="I275" s="41"/>
-      <c r="J275" s="41"/>
-      <c r="K275" s="41"/>
-      <c r="L275" s="41"/>
-      <c r="M275" s="41"/>
-      <c r="N275" s="41"/>
-      <c r="O275" s="41"/>
-      <c r="P275" s="41"/>
-      <c r="Q275" s="41"/>
-      <c r="R275" s="41"/>
-      <c r="S275" s="41"/>
-      <c r="T275" s="41"/>
-      <c r="U275" s="41"/>
-      <c r="V275" s="41"/>
-      <c r="W275" s="41"/>
-      <c r="X275" s="41"/>
-      <c r="Y275" s="41"/>
-      <c r="Z275" s="41"/>
-      <c r="AA275" s="41"/>
-      <c r="AB275" s="41"/>
-      <c r="AC275" s="42"/>
-    </row>
-    <row r="276" spans="2:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B276" t="s">
-        <v>128</v>
-      </c>
-      <c r="H276" s="43"/>
-      <c r="I276" s="44"/>
-      <c r="J276" s="44"/>
-      <c r="K276" s="44"/>
-      <c r="L276" s="44"/>
-      <c r="M276" s="44"/>
-      <c r="N276" s="44"/>
-      <c r="O276" s="44"/>
-      <c r="P276" s="44"/>
-      <c r="Q276" s="44"/>
-      <c r="R276" s="44"/>
-      <c r="S276" s="44"/>
-      <c r="T276" s="44"/>
-      <c r="U276" s="44"/>
-      <c r="V276" s="44"/>
-      <c r="W276" s="44"/>
-      <c r="X276" s="44"/>
-      <c r="Y276" s="44"/>
-      <c r="Z276" s="44"/>
-      <c r="AA276" s="44"/>
-      <c r="AB276" s="44"/>
-      <c r="AC276" s="45"/>
-    </row>
-    <row r="278" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B278" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="280" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B280" t="s">
+    </row>
+    <row r="283" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B283" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="281" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B281" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="283" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B283" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/各種資料/contact 7().xlsx
+++ b/各種資料/contact 7().xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guest04\Desktop\高橋研三\03_knowledge\各種資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2CC9A7-CA51-469E-8D60-7A8E136B6F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C14652-CED3-43CD-98A9-9DE65B4A598E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47610" yWindow="0" windowWidth="18030" windowHeight="16305" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44595" yWindow="540" windowWidth="16980" windowHeight="14805" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="① インストール" sheetId="1" r:id="rId1"/>
@@ -1737,7 +1737,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1945,10 +1945,10 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -5510,6 +5510,50 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>281</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>560457</xdr:colOff>
+      <xdr:row>326</xdr:row>
+      <xdr:rowOff>122899</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B73422FA-9AF6-D215-4AA4-3091835A1C4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9867900" y="46577250"/>
+          <a:ext cx="12142857" cy="7409524"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6291,7 +6335,7 @@
       <c r="K7" s="4"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="50" t="s">
         <v>171</v>
       </c>
       <c r="C8" s="4"/>
@@ -6305,7 +6349,7 @@
       <c r="K8" s="4"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="50" t="s">
         <v>170</v>
       </c>
       <c r="C9" s="4"/>
@@ -6908,60 +6952,274 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M17" s="50" t="s">
+    <row r="17" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M17" s="51" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="18" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M18" t="s">
+      <c r="N17" s="51"/>
+      <c r="O17" s="51"/>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="51"/>
+      <c r="R17" s="51"/>
+      <c r="S17" s="51"/>
+      <c r="T17" s="51"/>
+      <c r="U17" s="51"/>
+      <c r="V17" s="51"/>
+      <c r="W17" s="51"/>
+    </row>
+    <row r="18" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M18" s="51" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="20" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M20" t="s">
+      <c r="N18" s="51"/>
+      <c r="O18" s="51"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="51"/>
+      <c r="R18" s="51"/>
+      <c r="S18" s="51"/>
+      <c r="T18" s="51"/>
+      <c r="U18" s="51"/>
+      <c r="V18" s="51"/>
+      <c r="W18" s="51"/>
+    </row>
+    <row r="19" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M19" s="51"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="51"/>
+      <c r="P19" s="51"/>
+      <c r="Q19" s="51"/>
+      <c r="R19" s="51"/>
+      <c r="S19" s="51"/>
+      <c r="T19" s="51"/>
+      <c r="U19" s="51"/>
+      <c r="V19" s="51"/>
+      <c r="W19" s="51"/>
+    </row>
+    <row r="20" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M20" s="51" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="22" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M22" t="s">
+      <c r="N20" s="51"/>
+      <c r="O20" s="51"/>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="51"/>
+      <c r="R20" s="51"/>
+      <c r="S20" s="51"/>
+      <c r="T20" s="51"/>
+      <c r="U20" s="51"/>
+      <c r="V20" s="51"/>
+      <c r="W20" s="51"/>
+    </row>
+    <row r="21" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M21" s="51"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="51"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="51"/>
+      <c r="R21" s="51"/>
+      <c r="S21" s="51"/>
+      <c r="T21" s="51"/>
+      <c r="U21" s="51"/>
+      <c r="V21" s="51"/>
+      <c r="W21" s="51"/>
+    </row>
+    <row r="22" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M22" s="51" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="23" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M23" t="s">
+      <c r="N22" s="51"/>
+      <c r="O22" s="51"/>
+      <c r="P22" s="51"/>
+      <c r="Q22" s="51"/>
+      <c r="R22" s="51"/>
+      <c r="S22" s="51"/>
+      <c r="T22" s="51"/>
+      <c r="U22" s="51"/>
+      <c r="V22" s="51"/>
+      <c r="W22" s="51"/>
+    </row>
+    <row r="23" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M23" s="51" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="24" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M24" t="s">
+      <c r="N23" s="51"/>
+      <c r="O23" s="51"/>
+      <c r="P23" s="51"/>
+      <c r="Q23" s="51"/>
+      <c r="R23" s="51"/>
+      <c r="S23" s="51"/>
+      <c r="T23" s="51"/>
+      <c r="U23" s="51"/>
+      <c r="V23" s="51"/>
+      <c r="W23" s="51"/>
+    </row>
+    <row r="24" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M24" s="51" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="28" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="M28" t="s">
+      <c r="N24" s="51"/>
+      <c r="O24" s="51"/>
+      <c r="P24" s="51"/>
+      <c r="Q24" s="51"/>
+      <c r="R24" s="51"/>
+      <c r="S24" s="51"/>
+      <c r="T24" s="51"/>
+      <c r="U24" s="51"/>
+      <c r="V24" s="51"/>
+      <c r="W24" s="51"/>
+    </row>
+    <row r="25" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M25" s="51"/>
+      <c r="N25" s="51"/>
+      <c r="O25" s="51"/>
+      <c r="P25" s="51"/>
+      <c r="Q25" s="51"/>
+      <c r="R25" s="51"/>
+      <c r="S25" s="51"/>
+      <c r="T25" s="51"/>
+      <c r="U25" s="51"/>
+      <c r="V25" s="51"/>
+      <c r="W25" s="51"/>
+    </row>
+    <row r="26" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M26" s="51"/>
+      <c r="N26" s="51"/>
+      <c r="O26" s="51"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="51"/>
+      <c r="R26" s="51"/>
+      <c r="S26" s="51"/>
+      <c r="T26" s="51"/>
+      <c r="U26" s="51"/>
+      <c r="V26" s="51"/>
+      <c r="W26" s="51"/>
+    </row>
+    <row r="27" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M27" s="51"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="51"/>
+      <c r="P27" s="51"/>
+      <c r="Q27" s="51"/>
+      <c r="R27" s="51"/>
+      <c r="S27" s="51"/>
+      <c r="T27" s="51"/>
+      <c r="U27" s="51"/>
+      <c r="V27" s="51"/>
+      <c r="W27" s="51"/>
+    </row>
+    <row r="28" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M28" s="51" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="29" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="N29" t="s">
+      <c r="N28" s="51"/>
+      <c r="O28" s="51"/>
+      <c r="P28" s="51"/>
+      <c r="Q28" s="51"/>
+      <c r="R28" s="51"/>
+      <c r="S28" s="51"/>
+      <c r="T28" s="51"/>
+      <c r="U28" s="51"/>
+      <c r="V28" s="51"/>
+      <c r="W28" s="51"/>
+    </row>
+    <row r="29" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M29" s="51"/>
+      <c r="N29" s="51" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="30" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="N30" t="s">
+      <c r="O29" s="51"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="51"/>
+      <c r="R29" s="51"/>
+      <c r="S29" s="51"/>
+      <c r="T29" s="51"/>
+      <c r="U29" s="51"/>
+      <c r="V29" s="51"/>
+      <c r="W29" s="51"/>
+    </row>
+    <row r="30" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M30" s="51"/>
+      <c r="N30" s="51" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="32" spans="13:14" x14ac:dyDescent="0.2">
-      <c r="N32" t="s">
+      <c r="O30" s="51"/>
+      <c r="P30" s="51"/>
+      <c r="Q30" s="51"/>
+      <c r="R30" s="51"/>
+      <c r="S30" s="51"/>
+      <c r="T30" s="51"/>
+      <c r="U30" s="51"/>
+      <c r="V30" s="51"/>
+      <c r="W30" s="51"/>
+    </row>
+    <row r="31" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M31" s="51"/>
+      <c r="N31" s="51"/>
+      <c r="O31" s="51"/>
+      <c r="P31" s="51"/>
+      <c r="Q31" s="51"/>
+      <c r="R31" s="51"/>
+      <c r="S31" s="51"/>
+      <c r="T31" s="51"/>
+      <c r="U31" s="51"/>
+      <c r="V31" s="51"/>
+      <c r="W31" s="51"/>
+    </row>
+    <row r="32" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M32" s="51"/>
+      <c r="N32" s="51" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="34" spans="13:13" x14ac:dyDescent="0.2">
-      <c r="M34" t="s">
+      <c r="O32" s="51"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="51"/>
+      <c r="R32" s="51"/>
+      <c r="S32" s="51"/>
+      <c r="T32" s="51"/>
+      <c r="U32" s="51"/>
+      <c r="V32" s="51"/>
+      <c r="W32" s="51"/>
+    </row>
+    <row r="33" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M33" s="51"/>
+      <c r="N33" s="51"/>
+      <c r="O33" s="51"/>
+      <c r="P33" s="51"/>
+      <c r="Q33" s="51"/>
+      <c r="R33" s="51"/>
+      <c r="S33" s="51"/>
+      <c r="T33" s="51"/>
+      <c r="U33" s="51"/>
+      <c r="V33" s="51"/>
+      <c r="W33" s="51"/>
+    </row>
+    <row r="34" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M34" s="51" t="s">
         <v>177</v>
       </c>
+      <c r="N34" s="51"/>
+      <c r="O34" s="51"/>
+      <c r="P34" s="51"/>
+      <c r="Q34" s="51"/>
+      <c r="R34" s="51"/>
+      <c r="S34" s="51"/>
+      <c r="T34" s="51"/>
+      <c r="U34" s="51"/>
+      <c r="V34" s="51"/>
+      <c r="W34" s="51"/>
+    </row>
+    <row r="35" spans="13:23" x14ac:dyDescent="0.2">
+      <c r="M35" s="51"/>
+      <c r="N35" s="51"/>
+      <c r="O35" s="51"/>
+      <c r="P35" s="51"/>
+      <c r="Q35" s="51"/>
+      <c r="R35" s="51"/>
+      <c r="S35" s="51"/>
+      <c r="T35" s="51"/>
+      <c r="U35" s="51"/>
+      <c r="V35" s="51"/>
+      <c r="W35" s="51"/>
     </row>
     <row r="49" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="2:15" x14ac:dyDescent="0.2">

--- a/各種資料/contact 7().xlsx
+++ b/各種資料/contact 7().xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guest04\Desktop\高橋研三\03_knowledge\各種資料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\50_knowledge\各種資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C14652-CED3-43CD-98A9-9DE65B4A598E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44595" yWindow="540" windowWidth="16980" windowHeight="14805" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4785" yWindow="540" windowWidth="20490" windowHeight="14505" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="① インストール" sheetId="1" r:id="rId1"/>
@@ -5846,14 +5846,14 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K6"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5867,8 +5867,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
@@ -5882,7 +5882,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -5896,7 +5896,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5909,7 +5909,7 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:T61"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
@@ -5917,8 +5917,8 @@
     <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:20" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5932,8 +5932,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
@@ -5968,23 +5968,23 @@
       </c>
       <c r="T5" s="39"/>
     </row>
-    <row r="6" spans="2:20" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:20" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="P6" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="2:20" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="2:20" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="2:20" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="2:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:20" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="8" spans="2:20" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="2:20" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="10" spans="2:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="22" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="11" spans="2:20" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:20" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="23"/>
     </row>
-    <row r="12" spans="2:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:20" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
@@ -5998,8 +5998,8 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B14" s="5" t="s">
         <v>7</v>
       </c>
@@ -6013,7 +6013,7 @@
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
@@ -6027,8 +6027,8 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:20" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="17" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
@@ -6042,8 +6042,8 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="2:11" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -6057,7 +6057,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
@@ -6071,7 +6071,7 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
         <v>12</v>
       </c>
@@ -6085,7 +6085,7 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B22" s="18" t="s">
         <v>163</v>
       </c>
@@ -6099,7 +6099,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -6111,7 +6111,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
         <v>13</v>
       </c>
@@ -6125,16 +6125,16 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>14</v>
       </c>
@@ -6148,8 +6148,8 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="7" t="s">
         <v>15</v>
       </c>
@@ -6163,8 +6163,8 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B34" s="3" t="s">
         <v>16</v>
       </c>
@@ -6178,7 +6178,7 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B35" s="18" t="s">
         <v>168</v>
       </c>
@@ -6192,7 +6192,7 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B36" s="3" t="s">
         <v>17</v>
       </c>
@@ -6206,22 +6206,22 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="38" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="2:16" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="9" t="s">
         <v>24</v>
       </c>
@@ -6240,7 +6240,7 @@
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
     </row>
-    <row r="61" spans="2:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="2:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6255,15 +6255,15 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K83"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
     <col min="3" max="15" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
@@ -6277,8 +6277,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:11" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="2:11" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="10" t="s">
         <v>26</v>
       </c>
@@ -6292,7 +6292,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" s="5" t="s">
         <v>27</v>
       </c>
@@ -6306,7 +6306,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B6" s="18" t="s">
         <v>169</v>
       </c>
@@ -6320,7 +6320,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
         <v>28</v>
       </c>
@@ -6334,7 +6334,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B8" s="50" t="s">
         <v>171</v>
       </c>
@@ -6348,7 +6348,7 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B9" s="50" t="s">
         <v>170</v>
       </c>
@@ -6362,7 +6362,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
@@ -6376,8 +6376,8 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="12" spans="2:11" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="2:11" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="13" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="7" t="s">
         <v>30</v>
       </c>
@@ -6391,17 +6391,17 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="19" spans="2:11" ht="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" ht="18.75" x14ac:dyDescent="0.2">
       <c r="B19" s="19" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B21" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="20" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" ht="19.5" x14ac:dyDescent="0.15">
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
@@ -6415,7 +6415,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B24" s="5" t="s">
         <v>19</v>
       </c>
@@ -6429,7 +6429,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B25" s="3" t="s">
         <v>20</v>
       </c>
@@ -6443,7 +6443,7 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B26" s="18" t="s">
         <v>53</v>
       </c>
@@ -6457,7 +6457,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B27" s="3" t="s">
         <v>21</v>
       </c>
@@ -6471,7 +6471,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B28" s="3" t="s">
         <v>17</v>
       </c>
@@ -6485,7 +6485,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B29" s="3" t="s">
         <v>22</v>
       </c>
@@ -6499,7 +6499,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="32" spans="2:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" ht="16.5" x14ac:dyDescent="0.15">
       <c r="B32" s="7" t="s">
         <v>23</v>
       </c>
@@ -6513,42 +6513,42 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="36" spans="2:2" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B36" s="20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B38" s="16" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B39" s="16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B40" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B41" s="16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B42" s="16" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="2:2" ht="23.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" ht="23.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="21" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B83" t="s">
         <v>61</v>
       </c>
@@ -6566,15 +6566,15 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B1:K16"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="13" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="8.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>31</v>
       </c>
@@ -6588,8 +6588,8 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="11" t="s">
         <v>32</v>
       </c>
@@ -6601,7 +6601,7 @@
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
         <v>33</v>
       </c>
@@ -6615,7 +6615,7 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
         <v>34</v>
       </c>
@@ -6629,7 +6629,7 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -6641,7 +6641,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B8" s="3" t="s">
         <v>35</v>
       </c>
@@ -6655,7 +6655,7 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B9" s="3" t="s">
         <v>36</v>
       </c>
@@ -6669,7 +6669,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -6681,7 +6681,7 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B11" s="3" t="s">
         <v>37</v>
       </c>
@@ -6695,8 +6695,8 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="13" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="13" t="s">
         <v>38</v>
       </c>
@@ -6708,7 +6708,7 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B15" s="15" t="s">
         <v>39</v>
       </c>
@@ -6722,7 +6722,7 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="2:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6736,9 +6736,9 @@
     <tabColor rgb="FF2E86AB"/>
   </sheetPr>
   <dimension ref="B3:E38"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>40</v>
       </c>
@@ -6746,17 +6746,17 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B38" t="s">
         <v>43</v>
       </c>
@@ -6771,45 +6771,45 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E4DE1B-CEE6-4D06-B682-4A9E3F05719A}">
   <dimension ref="B2:P147"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B27" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="16:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="16:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="16:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P38" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="16:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P39" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B74" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B75" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B111" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="147" spans="16:16" x14ac:dyDescent="0.2">
+    <row r="147" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P147" t="s">
         <v>49</v>
       </c>
@@ -6824,65 +6824,65 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A893AC6-FB79-450E-8D17-FE484C32412D}">
   <dimension ref="B2:L75"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B27" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="19" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" ht="18.75" x14ac:dyDescent="0.2">
       <c r="B31" s="25" t="s">
         <v>66</v>
       </c>
       <c r="C31" s="26"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B32" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B33" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B37" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.15">
       <c r="L44" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.15">
       <c r="L45" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.15">
       <c r="L47" s="24" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B74" t="s">
         <v>74</v>
       </c>
@@ -6890,7 +6890,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>75</v>
       </c>
@@ -6908,13 +6908,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F487261-4C57-4DE5-9D5F-EC7B6550A8CC}">
   <dimension ref="B1:AC283"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="12.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.375" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B1" s="31" t="s">
         <v>113</v>
       </c>
@@ -6924,17 +6924,17 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B4" s="16" t="s">
         <v>92</v>
       </c>
@@ -6942,17 +6942,17 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M17" s="51" t="s">
         <v>157</v>
       </c>
@@ -6967,7 +6967,7 @@
       <c r="V17" s="51"/>
       <c r="W17" s="51"/>
     </row>
-    <row r="18" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M18" s="51" t="s">
         <v>158</v>
       </c>
@@ -6982,7 +6982,7 @@
       <c r="V18" s="51"/>
       <c r="W18" s="51"/>
     </row>
-    <row r="19" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M19" s="51"/>
       <c r="N19" s="51"/>
       <c r="O19" s="51"/>
@@ -6995,7 +6995,7 @@
       <c r="V19" s="51"/>
       <c r="W19" s="51"/>
     </row>
-    <row r="20" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M20" s="51" t="s">
         <v>159</v>
       </c>
@@ -7010,7 +7010,7 @@
       <c r="V20" s="51"/>
       <c r="W20" s="51"/>
     </row>
-    <row r="21" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M21" s="51"/>
       <c r="N21" s="51"/>
       <c r="O21" s="51"/>
@@ -7023,7 +7023,7 @@
       <c r="V21" s="51"/>
       <c r="W21" s="51"/>
     </row>
-    <row r="22" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M22" s="51" t="s">
         <v>160</v>
       </c>
@@ -7038,7 +7038,7 @@
       <c r="V22" s="51"/>
       <c r="W22" s="51"/>
     </row>
-    <row r="23" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M23" s="51" t="s">
         <v>161</v>
       </c>
@@ -7053,7 +7053,7 @@
       <c r="V23" s="51"/>
       <c r="W23" s="51"/>
     </row>
-    <row r="24" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M24" s="51" t="s">
         <v>162</v>
       </c>
@@ -7068,7 +7068,7 @@
       <c r="V24" s="51"/>
       <c r="W24" s="51"/>
     </row>
-    <row r="25" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M25" s="51"/>
       <c r="N25" s="51"/>
       <c r="O25" s="51"/>
@@ -7081,7 +7081,7 @@
       <c r="V25" s="51"/>
       <c r="W25" s="51"/>
     </row>
-    <row r="26" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M26" s="51"/>
       <c r="N26" s="51"/>
       <c r="O26" s="51"/>
@@ -7094,7 +7094,7 @@
       <c r="V26" s="51"/>
       <c r="W26" s="51"/>
     </row>
-    <row r="27" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M27" s="51"/>
       <c r="N27" s="51"/>
       <c r="O27" s="51"/>
@@ -7107,7 +7107,7 @@
       <c r="V27" s="51"/>
       <c r="W27" s="51"/>
     </row>
-    <row r="28" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M28" s="51" t="s">
         <v>173</v>
       </c>
@@ -7122,7 +7122,7 @@
       <c r="V28" s="51"/>
       <c r="W28" s="51"/>
     </row>
-    <row r="29" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M29" s="51"/>
       <c r="N29" s="51" t="s">
         <v>174</v>
@@ -7137,7 +7137,7 @@
       <c r="V29" s="51"/>
       <c r="W29" s="51"/>
     </row>
-    <row r="30" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M30" s="51"/>
       <c r="N30" s="51" t="s">
         <v>175</v>
@@ -7152,7 +7152,7 @@
       <c r="V30" s="51"/>
       <c r="W30" s="51"/>
     </row>
-    <row r="31" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M31" s="51"/>
       <c r="N31" s="51"/>
       <c r="O31" s="51"/>
@@ -7165,7 +7165,7 @@
       <c r="V31" s="51"/>
       <c r="W31" s="51"/>
     </row>
-    <row r="32" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M32" s="51"/>
       <c r="N32" s="51" t="s">
         <v>176</v>
@@ -7180,7 +7180,7 @@
       <c r="V32" s="51"/>
       <c r="W32" s="51"/>
     </row>
-    <row r="33" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M33" s="51"/>
       <c r="N33" s="51"/>
       <c r="O33" s="51"/>
@@ -7193,7 +7193,7 @@
       <c r="V33" s="51"/>
       <c r="W33" s="51"/>
     </row>
-    <row r="34" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M34" s="51" t="s">
         <v>177</v>
       </c>
@@ -7208,7 +7208,7 @@
       <c r="V34" s="51"/>
       <c r="W34" s="51"/>
     </row>
-    <row r="35" spans="13:23" x14ac:dyDescent="0.2">
+    <row r="35" spans="13:23" x14ac:dyDescent="0.15">
       <c r="M35" s="51"/>
       <c r="N35" s="51"/>
       <c r="O35" s="51"/>
@@ -7221,8 +7221,8 @@
       <c r="V35" s="51"/>
       <c r="W35" s="51"/>
     </row>
-    <row r="49" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:15" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B50" s="45" t="s">
         <v>95</v>
       </c>
@@ -7238,13 +7238,13 @@
       <c r="L50" s="36"/>
       <c r="M50" s="37"/>
     </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B51" s="38" t="s">
         <v>91</v>
       </c>
       <c r="M51" s="40"/>
     </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B52" s="38" t="s">
         <v>96</v>
       </c>
@@ -7253,27 +7253,27 @@
       </c>
       <c r="M52" s="40"/>
     </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B53" s="38" t="s">
         <v>112</v>
       </c>
       <c r="M53" s="40"/>
     </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B54" s="38"/>
       <c r="M54" s="40"/>
     </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B55" s="38" t="s">
         <v>114</v>
       </c>
       <c r="M55" s="40"/>
     </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B56" s="38"/>
       <c r="M56" s="40"/>
     </row>
-    <row r="57" spans="2:15" ht="30" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:15" ht="30.75" x14ac:dyDescent="0.3">
       <c r="B57" s="38"/>
       <c r="M57" s="40"/>
       <c r="N57" s="47" t="s">
@@ -7283,111 +7283,111 @@
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B58" s="38"/>
       <c r="M58" s="40"/>
     </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B59" s="38"/>
       <c r="M59" s="40"/>
     </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B60" s="38"/>
       <c r="M60" s="40"/>
     </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B61" s="38"/>
       <c r="M61" s="40"/>
     </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B62" s="38"/>
       <c r="M62" s="40"/>
     </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B63" s="38"/>
       <c r="M63" s="40"/>
     </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B64" s="38"/>
       <c r="M64" s="40"/>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="38"/>
       <c r="M65" s="40"/>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B66" s="38"/>
       <c r="M66" s="40"/>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="38"/>
       <c r="M67" s="40"/>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="38"/>
       <c r="M68" s="40"/>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B69" s="38"/>
       <c r="M69" s="40"/>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="38"/>
       <c r="M70" s="40"/>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="38"/>
       <c r="M71" s="40"/>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="38"/>
       <c r="M72" s="40"/>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B73" s="38"/>
       <c r="M73" s="40"/>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B74" s="38"/>
       <c r="M74" s="40"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="38"/>
       <c r="M75" s="40"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B76" s="38"/>
       <c r="M76" s="40"/>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B77" s="38"/>
       <c r="M77" s="40"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B78" s="38"/>
       <c r="M78" s="40"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B79" s="38"/>
       <c r="M79" s="40"/>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B80" s="38"/>
       <c r="M80" s="40"/>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B81" s="38"/>
       <c r="M81" s="40"/>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B82" s="38"/>
       <c r="M82" s="40"/>
     </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B83" s="38"/>
       <c r="M83" s="40"/>
     </row>
-    <row r="84" spans="2:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B84" s="41"/>
       <c r="C84" s="42"/>
       <c r="D84" s="42"/>
@@ -7401,42 +7401,42 @@
       <c r="L84" s="42"/>
       <c r="M84" s="43"/>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B89" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B90" s="16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B91" s="16" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="92" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B92" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B93" s="16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="98" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:3" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B98" s="17" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B101" s="16" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="103" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B103" s="28" t="s">
         <v>83</v>
       </c>
@@ -7444,7 +7444,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="104" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B104" s="27" t="s">
         <v>85</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="105" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B105" s="27" t="s">
         <v>87</v>
       </c>
@@ -7460,13 +7460,13 @@
         <v>88</v>
       </c>
     </row>
-    <row r="114" spans="2:4" ht="19" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:4" ht="18.75" x14ac:dyDescent="0.2">
       <c r="B114" s="25" t="s">
         <v>99</v>
       </c>
       <c r="C114" s="26"/>
     </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B115" t="s">
         <v>98</v>
       </c>
@@ -7474,83 +7474,83 @@
         <v>115</v>
       </c>
     </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B118" s="16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B131" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="154" spans="9:10" x14ac:dyDescent="0.2">
+    <row r="154" spans="9:10" x14ac:dyDescent="0.15">
       <c r="J154" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="155" spans="9:10" x14ac:dyDescent="0.2">
+    <row r="155" spans="9:10" x14ac:dyDescent="0.15">
       <c r="J155" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="158" spans="9:10" x14ac:dyDescent="0.2">
+    <row r="158" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I158" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="173" spans="9:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="9:9" x14ac:dyDescent="0.15">
       <c r="I173" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="175" spans="9:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="9:9" x14ac:dyDescent="0.15">
       <c r="I175" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="176" spans="9:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="9:9" x14ac:dyDescent="0.15">
       <c r="I176" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="178" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:17" x14ac:dyDescent="0.15">
       <c r="I178" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="179" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:17" x14ac:dyDescent="0.15">
       <c r="I179" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="181" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:17" x14ac:dyDescent="0.15">
       <c r="I181" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="183" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:17" x14ac:dyDescent="0.15">
       <c r="I183" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="184" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:17" x14ac:dyDescent="0.15">
       <c r="I184" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="188" spans="2:17" ht="16" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:17" ht="15" x14ac:dyDescent="0.25">
       <c r="I188" s="34" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="189" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:17" x14ac:dyDescent="0.15">
       <c r="I189" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="190" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="191" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B191" s="29" t="s">
         <v>109</v>
       </c>
@@ -7564,14 +7564,14 @@
       <c r="P191" s="36"/>
       <c r="Q191" s="37"/>
     </row>
-    <row r="192" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:17" x14ac:dyDescent="0.15">
       <c r="I192" s="38"/>
       <c r="J192" s="39" t="s">
         <v>134</v>
       </c>
       <c r="Q192" s="40"/>
     </row>
-    <row r="193" spans="9:17" x14ac:dyDescent="0.2">
+    <row r="193" spans="9:17" x14ac:dyDescent="0.15">
       <c r="I193" s="38"/>
       <c r="J193" t="s">
         <v>132</v>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="Q193" s="40"/>
     </row>
-    <row r="194" spans="9:17" x14ac:dyDescent="0.2">
+    <row r="194" spans="9:17" x14ac:dyDescent="0.15">
       <c r="I194" s="38"/>
       <c r="K194" t="s">
         <v>133</v>
@@ -7591,22 +7591,22 @@
       </c>
       <c r="Q194" s="40"/>
     </row>
-    <row r="195" spans="9:17" x14ac:dyDescent="0.2">
+    <row r="195" spans="9:17" x14ac:dyDescent="0.15">
       <c r="I195" s="38"/>
       <c r="M195" s="39" t="s">
         <v>172</v>
       </c>
       <c r="Q195" s="40"/>
     </row>
-    <row r="196" spans="9:17" x14ac:dyDescent="0.2">
+    <row r="196" spans="9:17" x14ac:dyDescent="0.15">
       <c r="I196" s="38"/>
       <c r="Q196" s="40"/>
     </row>
-    <row r="197" spans="9:17" x14ac:dyDescent="0.2">
+    <row r="197" spans="9:17" x14ac:dyDescent="0.15">
       <c r="I197" s="38"/>
       <c r="Q197" s="40"/>
     </row>
-    <row r="198" spans="9:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="9:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="I198" s="41"/>
       <c r="J198" s="42"/>
       <c r="K198" s="42"/>
@@ -7617,57 +7617,57 @@
       <c r="P198" s="42"/>
       <c r="Q198" s="43"/>
     </row>
-    <row r="202" spans="9:17" x14ac:dyDescent="0.2">
+    <row r="202" spans="9:17" x14ac:dyDescent="0.15">
       <c r="K202" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="203" spans="9:17" x14ac:dyDescent="0.2">
+    <row r="203" spans="9:17" x14ac:dyDescent="0.15">
       <c r="J203" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B221" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B223" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B224" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="226" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B226" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="227" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B227" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="229" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B229" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="230" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H230" s="16" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="231" spans="2:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B231" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="232" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B232" t="s">
         <v>108</v>
       </c>
@@ -7694,7 +7694,7 @@
       <c r="AB232" s="36"/>
       <c r="AC232" s="37"/>
     </row>
-    <row r="233" spans="2:29" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:29" ht="17.25" x14ac:dyDescent="0.2">
       <c r="B233" s="29" t="s">
         <v>91</v>
       </c>
@@ -7705,28 +7705,28 @@
       <c r="J233" s="26"/>
       <c r="AC233" s="40"/>
     </row>
-    <row r="234" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B234" s="30" t="s">
         <v>110</v>
       </c>
       <c r="H234" s="38"/>
       <c r="AC234" s="40"/>
     </row>
-    <row r="235" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B235" t="s">
         <v>91</v>
       </c>
       <c r="H235" s="38"/>
       <c r="AC235" s="40"/>
     </row>
-    <row r="236" spans="2:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B236" t="s">
         <v>111</v>
       </c>
       <c r="H236" s="38"/>
       <c r="AC236" s="40"/>
     </row>
-    <row r="237" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H237" s="38"/>
       <c r="I237" s="35"/>
       <c r="J237" s="36"/>
@@ -7736,7 +7736,7 @@
       <c r="N237" s="37"/>
       <c r="AC237" s="40"/>
     </row>
-    <row r="238" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H238" s="38"/>
       <c r="I238" s="44" t="s">
         <v>137</v>
@@ -7746,7 +7746,7 @@
       <c r="N238" s="40"/>
       <c r="AC238" s="40"/>
     </row>
-    <row r="239" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H239" s="38"/>
       <c r="I239" s="38" t="s">
         <v>138</v>
@@ -7754,7 +7754,7 @@
       <c r="N239" s="40"/>
       <c r="AC239" s="40"/>
     </row>
-    <row r="240" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H240" s="38"/>
       <c r="I240" s="38" t="s">
         <v>139</v>
@@ -7762,13 +7762,13 @@
       <c r="N240" s="40"/>
       <c r="AC240" s="40"/>
     </row>
-    <row r="241" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="241" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H241" s="38"/>
       <c r="I241" s="38"/>
       <c r="N241" s="40"/>
       <c r="AC241" s="40"/>
     </row>
-    <row r="242" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="242" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H242" s="38"/>
       <c r="I242" s="44" t="s">
         <v>140</v>
@@ -7780,7 +7780,7 @@
       <c r="N242" s="40"/>
       <c r="AC242" s="40"/>
     </row>
-    <row r="243" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="243" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H243" s="38"/>
       <c r="I243" s="38" t="s">
         <v>141</v>
@@ -7788,7 +7788,7 @@
       <c r="N243" s="40"/>
       <c r="AC243" s="40"/>
     </row>
-    <row r="244" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="244" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H244" s="38"/>
       <c r="I244" s="38" t="s">
         <v>142</v>
@@ -7796,7 +7796,7 @@
       <c r="N244" s="40"/>
       <c r="AC244" s="40"/>
     </row>
-    <row r="245" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="245" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H245" s="38"/>
       <c r="I245" s="38" t="s">
         <v>144</v>
@@ -7804,13 +7804,13 @@
       <c r="N245" s="40"/>
       <c r="AC245" s="40"/>
     </row>
-    <row r="246" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="246" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H246" s="38"/>
       <c r="I246" s="38"/>
       <c r="N246" s="40"/>
       <c r="AC246" s="40"/>
     </row>
-    <row r="247" spans="8:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="8:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="H247" s="38"/>
       <c r="I247" s="41"/>
       <c r="J247" s="42"/>
@@ -7820,11 +7820,11 @@
       <c r="N247" s="43"/>
       <c r="AC247" s="40"/>
     </row>
-    <row r="248" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="248" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H248" s="38"/>
       <c r="AC248" s="40"/>
     </row>
-    <row r="249" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="249" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H249" s="38"/>
       <c r="P249" s="16" t="s">
         <v>152</v>
@@ -7838,7 +7838,7 @@
       <c r="W249" s="16"/>
       <c r="AC249" s="40"/>
     </row>
-    <row r="250" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="250" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H250" s="38"/>
       <c r="P250" s="16" t="s">
         <v>153</v>
@@ -7852,7 +7852,7 @@
       <c r="W250" s="16"/>
       <c r="AC250" s="40"/>
     </row>
-    <row r="251" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="251" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H251" s="38"/>
       <c r="I251" s="26" t="s">
         <v>151</v>
@@ -7861,11 +7861,11 @@
       <c r="K251" s="26"/>
       <c r="AC251" s="40"/>
     </row>
-    <row r="252" spans="8:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="8:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="H252" s="38"/>
       <c r="AC252" s="40"/>
     </row>
-    <row r="253" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="253" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H253" s="38"/>
       <c r="I253" s="45" t="s">
         <v>145</v>
@@ -7877,7 +7877,7 @@
       <c r="N253" s="37"/>
       <c r="AC253" s="40"/>
     </row>
-    <row r="254" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="254" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H254" s="38"/>
       <c r="I254" s="38" t="s">
         <v>146</v>
@@ -7885,7 +7885,7 @@
       <c r="N254" s="40"/>
       <c r="AC254" s="40"/>
     </row>
-    <row r="255" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="255" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H255" s="38"/>
       <c r="I255" s="38" t="s">
         <v>147</v>
@@ -7893,13 +7893,13 @@
       <c r="N255" s="40"/>
       <c r="AC255" s="40"/>
     </row>
-    <row r="256" spans="8:29" x14ac:dyDescent="0.2">
+    <row r="256" spans="8:29" x14ac:dyDescent="0.15">
       <c r="H256" s="38"/>
       <c r="I256" s="38"/>
       <c r="N256" s="40"/>
       <c r="AC256" s="40"/>
     </row>
-    <row r="257" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="257" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H257" s="38"/>
       <c r="I257" s="44" t="s">
         <v>148</v>
@@ -7909,7 +7909,7 @@
       <c r="N257" s="40"/>
       <c r="AC257" s="40"/>
     </row>
-    <row r="258" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="258" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H258" s="38"/>
       <c r="I258" s="38" t="s">
         <v>149</v>
@@ -7917,7 +7917,7 @@
       <c r="N258" s="40"/>
       <c r="AC258" s="40"/>
     </row>
-    <row r="259" spans="2:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="H259" s="38"/>
       <c r="I259" s="41" t="s">
         <v>150</v>
@@ -7929,15 +7929,15 @@
       <c r="N259" s="43"/>
       <c r="AC259" s="40"/>
     </row>
-    <row r="260" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="260" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H260" s="38"/>
       <c r="AC260" s="40"/>
     </row>
-    <row r="261" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="261" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H261" s="38"/>
       <c r="AC261" s="40"/>
     </row>
-    <row r="262" spans="2:29" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="2:29" ht="24" x14ac:dyDescent="0.25">
       <c r="B262" s="32" t="s">
         <v>129</v>
       </c>
@@ -7953,80 +7953,80 @@
       <c r="L262" s="33"/>
       <c r="AC262" s="40"/>
     </row>
-    <row r="263" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="263" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H263" s="38"/>
       <c r="AC263" s="40"/>
     </row>
-    <row r="264" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="264" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B264" t="s">
         <v>117</v>
       </c>
       <c r="H264" s="38"/>
       <c r="AC264" s="40"/>
     </row>
-    <row r="265" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="265" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B265" t="s">
         <v>122</v>
       </c>
       <c r="H265" s="38"/>
       <c r="AC265" s="40"/>
     </row>
-    <row r="266" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="266" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H266" s="38"/>
       <c r="AC266" s="40"/>
     </row>
-    <row r="267" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="267" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H267" s="38"/>
       <c r="AC267" s="40"/>
     </row>
-    <row r="268" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="268" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B268" t="s">
         <v>128</v>
       </c>
       <c r="H268" s="38"/>
       <c r="AC268" s="40"/>
     </row>
-    <row r="269" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="269" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B269" t="s">
         <v>118</v>
       </c>
       <c r="H269" s="38"/>
       <c r="AC269" s="40"/>
     </row>
-    <row r="270" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="270" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B270" t="s">
         <v>127</v>
       </c>
       <c r="H270" s="38"/>
       <c r="AC270" s="40"/>
     </row>
-    <row r="271" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="271" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B271" t="s">
         <v>119</v>
       </c>
       <c r="H271" s="38"/>
       <c r="AC271" s="40"/>
     </row>
-    <row r="272" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="272" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H272" s="38"/>
       <c r="AC272" s="40"/>
     </row>
-    <row r="273" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="273" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H273" s="38"/>
       <c r="AC273" s="40"/>
     </row>
-    <row r="274" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="274" spans="2:29" x14ac:dyDescent="0.15">
       <c r="H274" s="38"/>
       <c r="AC274" s="40"/>
     </row>
-    <row r="275" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="275" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B275" t="s">
         <v>120</v>
       </c>
       <c r="H275" s="38"/>
       <c r="AC275" s="40"/>
     </row>
-    <row r="276" spans="2:29" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:29" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B276" t="s">
         <v>123</v>
       </c>
@@ -8053,22 +8053,22 @@
       <c r="AB276" s="42"/>
       <c r="AC276" s="43"/>
     </row>
-    <row r="278" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="278" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B278" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="280" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="280" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B280" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="281" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="281" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B281" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="283" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="283" spans="2:29" x14ac:dyDescent="0.15">
       <c r="B283" t="s">
         <v>126</v>
       </c>
